--- a/outputs/XPBL2625WE/EXPRESS BERLIN XPBL2625WE.xlsx
+++ b/outputs/XPBL2625WE/EXPRESS BERLIN XPBL2625WE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24394\Desktop\CodeX\Space Control\outputs\XPBL2625WE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137BD2F3-A994-40A4-BA65-2740DEA50CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E57873-23E2-4B12-87CC-5A8AF35B9688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3312" yWindow="3312" windowWidth="23040" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,19 +862,79 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -886,82 +946,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -969,7 +969,7 @@
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
       <font>
         <b/>
@@ -979,6 +979,18 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -999,6 +1011,18 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1233,7 +1257,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="81"/>
@@ -1242,7 +1266,7 @@
       <c r="E1" s="81"/>
       <c r="F1" s="81"/>
       <c r="G1" s="81"/>
-      <c r="H1" s="102" t="s">
+      <c r="H1" s="89" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="81"/>
@@ -1272,21 +1296,21 @@
       <c r="AG1" s="81"/>
       <c r="AH1" s="81"/>
       <c r="AI1" s="81"/>
-      <c r="AJ1" s="96"/>
+      <c r="AJ1" s="82"/>
     </row>
     <row r="2" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="101" t="s">
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -1305,10 +1329,10 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
-      <c r="AA2" s="101" t="s">
+      <c r="AA2" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="89"/>
+      <c r="AB2" s="80"/>
       <c r="AC2" s="5">
         <v>0</v>
       </c>
@@ -1329,75 +1353,75 @@
       <c r="AJ2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="81"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="80" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="92" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="81"/>
-      <c r="F3" s="80" t="s">
+      <c r="F3" s="92" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="81"/>
-      <c r="H3" s="80" t="s">
+      <c r="H3" s="92" t="s">
         <v>11</v>
       </c>
       <c r="I3" s="81"/>
-      <c r="J3" s="80" t="s">
+      <c r="J3" s="92" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="81"/>
-      <c r="L3" s="80" t="s">
+      <c r="L3" s="92" t="s">
         <v>13</v>
       </c>
       <c r="M3" s="81"/>
-      <c r="N3" s="80" t="s">
+      <c r="N3" s="92" t="s">
         <v>14</v>
       </c>
       <c r="O3" s="81"/>
-      <c r="P3" s="80" t="s">
+      <c r="P3" s="92" t="s">
         <v>15</v>
       </c>
       <c r="Q3" s="81"/>
-      <c r="R3" s="80" t="s">
+      <c r="R3" s="92" t="s">
         <v>16</v>
       </c>
       <c r="S3" s="81"/>
-      <c r="T3" s="80" t="s">
+      <c r="T3" s="92" t="s">
         <v>17</v>
       </c>
       <c r="U3" s="81"/>
-      <c r="V3" s="80" t="s">
+      <c r="V3" s="92" t="s">
         <v>18</v>
       </c>
       <c r="W3" s="81"/>
-      <c r="X3" s="80" t="s">
+      <c r="X3" s="92" t="s">
         <v>9</v>
       </c>
       <c r="Y3" s="81"/>
       <c r="Z3" s="1"/>
-      <c r="AA3" s="80" t="s">
+      <c r="AA3" s="92" t="s">
         <v>19</v>
       </c>
       <c r="AB3" s="81"/>
       <c r="AC3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AD3" s="80" t="s">
+      <c r="AD3" s="92" t="s">
         <v>21</v>
       </c>
       <c r="AE3" s="81"/>
-      <c r="AF3" s="80" t="s">
+      <c r="AF3" s="92" t="s">
         <v>22</v>
       </c>
       <c r="AG3" s="81"/>
-      <c r="AH3" s="80" t="s">
+      <c r="AH3" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="AI3" s="96"/>
+      <c r="AI3" s="82"/>
       <c r="AJ3" s="10" t="s">
         <v>24</v>
       </c>
@@ -1406,70 +1430,70 @@
       <c r="A4" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="92" t="s">
+      <c r="B4" s="84"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="91"/>
-      <c r="F4" s="92" t="s">
+      <c r="E4" s="84"/>
+      <c r="F4" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="91"/>
-      <c r="H4" s="92" t="s">
+      <c r="G4" s="84"/>
+      <c r="H4" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="91"/>
-      <c r="J4" s="92" t="s">
+      <c r="I4" s="84"/>
+      <c r="J4" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="91"/>
-      <c r="L4" s="92" t="s">
+      <c r="K4" s="84"/>
+      <c r="L4" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="91"/>
-      <c r="N4" s="92" t="s">
+      <c r="M4" s="84"/>
+      <c r="N4" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="91"/>
-      <c r="P4" s="93" t="s">
+      <c r="O4" s="84"/>
+      <c r="P4" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="92" t="s">
+      <c r="Q4" s="84"/>
+      <c r="R4" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="S4" s="91"/>
-      <c r="T4" s="92" t="s">
+      <c r="S4" s="84"/>
+      <c r="T4" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="U4" s="91"/>
-      <c r="V4" s="92" t="s">
+      <c r="U4" s="84"/>
+      <c r="V4" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="W4" s="91"/>
-      <c r="X4" s="92" t="s">
+      <c r="W4" s="84"/>
+      <c r="X4" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="Y4" s="91"/>
+      <c r="Y4" s="84"/>
       <c r="Z4" s="12"/>
       <c r="AA4" s="90"/>
-      <c r="AB4" s="91"/>
+      <c r="AB4" s="84"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="90"/>
-      <c r="AE4" s="91"/>
+      <c r="AE4" s="84"/>
       <c r="AF4" s="90"/>
-      <c r="AG4" s="91"/>
+      <c r="AG4" s="84"/>
       <c r="AH4" s="90"/>
-      <c r="AI4" s="100"/>
+      <c r="AI4" s="91"/>
       <c r="AJ4" s="14"/>
     </row>
     <row r="5" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="96"/>
       <c r="D5" s="15" t="s">
         <v>38</v>
       </c>
@@ -1567,10 +1591,10 @@
       <c r="AJ5" s="19"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="86"/>
+      <c r="B6" s="77"/>
       <c r="C6" s="22" t="s">
         <v>46</v>
       </c>
@@ -1630,8 +1654,8 @@
       <c r="AJ6" s="29"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="86"/>
+      <c r="A7" s="78"/>
+      <c r="B7" s="77"/>
       <c r="C7" s="22" t="s">
         <v>47</v>
       </c>
@@ -1679,8 +1703,8 @@
       <c r="AJ7" s="29"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="87"/>
-      <c r="B8" s="86"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="22" t="s">
         <v>48</v>
       </c>
@@ -1728,8 +1752,8 @@
       <c r="AJ8" s="29"/>
     </row>
     <row r="9" spans="1:36" ht="18" customHeight="1">
-      <c r="A9" s="87"/>
-      <c r="B9" s="86"/>
+      <c r="A9" s="78"/>
+      <c r="B9" s="77"/>
       <c r="C9" s="22" t="s">
         <v>49</v>
       </c>
@@ -1777,8 +1801,8 @@
       <c r="AJ9" s="29"/>
     </row>
     <row r="10" spans="1:36" ht="18" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="86"/>
+      <c r="A10" s="78"/>
+      <c r="B10" s="77"/>
       <c r="C10" s="22" t="s">
         <v>50</v>
       </c>
@@ -1883,34 +1907,34 @@
       <c r="C12" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="84"/>
-      <c r="O12" s="76"/>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="76"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="76"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="76"/>
-      <c r="V12" s="84"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="76"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="73"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="73"/>
+      <c r="T12" s="74"/>
+      <c r="U12" s="73"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="73"/>
+      <c r="X12" s="74"/>
+      <c r="Y12" s="73"/>
       <c r="Z12" s="36"/>
-      <c r="AA12" s="84">
+      <c r="AA12" s="74">
         <f>D12+F12+H12+J12+L12+N12+P12+R12+T12+V12+X12</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="76"/>
+      <c r="AB12" s="73"/>
       <c r="AC12" s="35"/>
       <c r="AD12" s="35">
         <f>0+AA12-(0)</f>
@@ -1936,8 +1960,8 @@
       <c r="AJ12" s="41"/>
     </row>
     <row r="13" spans="1:36" ht="18" customHeight="1">
-      <c r="A13" s="72"/>
-      <c r="B13" s="73"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="42" t="s">
         <v>20</v>
       </c>
@@ -2054,10 +2078,10 @@
       <c r="AJ13" s="47"/>
     </row>
     <row r="14" spans="1:36" ht="18" customHeight="1">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="86"/>
+      <c r="B14" s="77"/>
       <c r="C14" s="22" t="s">
         <v>46</v>
       </c>
@@ -2117,8 +2141,8 @@
       <c r="AJ14" s="29"/>
     </row>
     <row r="15" spans="1:36" ht="18" customHeight="1">
-      <c r="A15" s="87"/>
-      <c r="B15" s="86"/>
+      <c r="A15" s="78"/>
+      <c r="B15" s="77"/>
       <c r="C15" s="22" t="s">
         <v>47</v>
       </c>
@@ -2166,8 +2190,8 @@
       <c r="AJ15" s="29"/>
     </row>
     <row r="16" spans="1:36" ht="18" customHeight="1">
-      <c r="A16" s="87"/>
-      <c r="B16" s="86"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="22" t="s">
         <v>48</v>
       </c>
@@ -2215,8 +2239,8 @@
       <c r="AJ16" s="29"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="87"/>
-      <c r="B17" s="86"/>
+      <c r="A17" s="78"/>
+      <c r="B17" s="77"/>
       <c r="C17" s="22" t="s">
         <v>49</v>
       </c>
@@ -2264,8 +2288,8 @@
       <c r="AJ17" s="29"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="87"/>
-      <c r="B18" s="86"/>
+      <c r="A18" s="78"/>
+      <c r="B18" s="77"/>
       <c r="C18" s="22" t="s">
         <v>50</v>
       </c>
@@ -2378,34 +2402,34 @@
       <c r="C20" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="84"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="76"/>
-      <c r="N20" s="84"/>
-      <c r="O20" s="76"/>
-      <c r="P20" s="84"/>
-      <c r="Q20" s="76"/>
-      <c r="R20" s="84"/>
-      <c r="S20" s="76"/>
-      <c r="T20" s="84"/>
-      <c r="U20" s="76"/>
-      <c r="V20" s="84"/>
-      <c r="W20" s="76"/>
-      <c r="X20" s="84"/>
-      <c r="Y20" s="76"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="74"/>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="74"/>
+      <c r="S20" s="73"/>
+      <c r="T20" s="74"/>
+      <c r="U20" s="73"/>
+      <c r="V20" s="74"/>
+      <c r="W20" s="73"/>
+      <c r="X20" s="74"/>
+      <c r="Y20" s="73"/>
       <c r="Z20" s="36"/>
-      <c r="AA20" s="84">
+      <c r="AA20" s="74">
         <f>D20+F20+H20+J20+L20+N20+P20+R20+T20+V20+X20</f>
         <v>0</v>
       </c>
-      <c r="AB20" s="76"/>
+      <c r="AB20" s="73"/>
       <c r="AC20" s="35"/>
       <c r="AD20" s="35">
         <f>AD12+AA20-(D103)</f>
@@ -2431,8 +2455,8 @@
       <c r="AJ20" s="41"/>
     </row>
     <row r="21" spans="1:36" ht="18" customHeight="1">
-      <c r="A21" s="72"/>
-      <c r="B21" s="73"/>
+      <c r="A21" s="87"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="42" t="s">
         <v>20</v>
       </c>
@@ -2549,10 +2573,10 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="18" customHeight="1">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="86"/>
+      <c r="B22" s="77"/>
       <c r="C22" s="22" t="s">
         <v>46</v>
       </c>
@@ -2612,8 +2636,8 @@
       <c r="AJ22" s="29"/>
     </row>
     <row r="23" spans="1:36" ht="18" customHeight="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="86"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="77"/>
       <c r="C23" s="22" t="s">
         <v>47</v>
       </c>
@@ -2661,8 +2685,8 @@
       <c r="AJ23" s="29"/>
     </row>
     <row r="24" spans="1:36" ht="18" customHeight="1">
-      <c r="A24" s="87"/>
-      <c r="B24" s="86"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="77"/>
       <c r="C24" s="22" t="s">
         <v>48</v>
       </c>
@@ -2710,8 +2734,8 @@
       <c r="AJ24" s="29"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="87"/>
-      <c r="B25" s="86"/>
+      <c r="A25" s="78"/>
+      <c r="B25" s="77"/>
       <c r="C25" s="22" t="s">
         <v>49</v>
       </c>
@@ -2759,8 +2783,8 @@
       <c r="AJ25" s="29"/>
     </row>
     <row r="26" spans="1:36" ht="18" customHeight="1">
-      <c r="A26" s="87"/>
-      <c r="B26" s="86"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="77"/>
       <c r="C26" s="22" t="s">
         <v>50</v>
       </c>
@@ -2873,34 +2897,34 @@
       <c r="C28" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="84"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="84"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="84"/>
-      <c r="O28" s="76"/>
-      <c r="P28" s="84"/>
-      <c r="Q28" s="76"/>
-      <c r="R28" s="84"/>
-      <c r="S28" s="76"/>
-      <c r="T28" s="84"/>
-      <c r="U28" s="76"/>
-      <c r="V28" s="84"/>
-      <c r="W28" s="76"/>
-      <c r="X28" s="84"/>
-      <c r="Y28" s="76"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="73"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="73"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="73"/>
+      <c r="T28" s="74"/>
+      <c r="U28" s="73"/>
+      <c r="V28" s="74"/>
+      <c r="W28" s="73"/>
+      <c r="X28" s="74"/>
+      <c r="Y28" s="73"/>
       <c r="Z28" s="36"/>
-      <c r="AA28" s="84">
+      <c r="AA28" s="74">
         <f>D28+F28+H28+J28+L28+N28+P28+R28+T28+V28+X28</f>
         <v>0</v>
       </c>
-      <c r="AB28" s="76"/>
+      <c r="AB28" s="73"/>
       <c r="AC28" s="35"/>
       <c r="AD28" s="35">
         <f>AD20+AA28-(F103)</f>
@@ -2926,8 +2950,8 @@
       <c r="AJ28" s="41"/>
     </row>
     <row r="29" spans="1:36" ht="18" customHeight="1">
-      <c r="A29" s="72"/>
-      <c r="B29" s="73"/>
+      <c r="A29" s="87"/>
+      <c r="B29" s="88"/>
       <c r="C29" s="42" t="s">
         <v>20</v>
       </c>
@@ -3044,10 +3068,10 @@
       <c r="AJ29" s="47"/>
     </row>
     <row r="30" spans="1:36" ht="18" customHeight="1">
-      <c r="A30" s="85" t="s">
+      <c r="A30" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="86"/>
+      <c r="B30" s="77"/>
       <c r="C30" s="22" t="s">
         <v>46</v>
       </c>
@@ -3107,8 +3131,8 @@
       <c r="AJ30" s="29"/>
     </row>
     <row r="31" spans="1:36" ht="18" customHeight="1">
-      <c r="A31" s="87"/>
-      <c r="B31" s="86"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="22" t="s">
         <v>47</v>
       </c>
@@ -3156,8 +3180,8 @@
       <c r="AJ31" s="29"/>
     </row>
     <row r="32" spans="1:36" ht="18" customHeight="1">
-      <c r="A32" s="87"/>
-      <c r="B32" s="86"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="77"/>
       <c r="C32" s="22" t="s">
         <v>48</v>
       </c>
@@ -3205,8 +3229,8 @@
       <c r="AJ32" s="29"/>
     </row>
     <row r="33" spans="1:36" ht="18" customHeight="1">
-      <c r="A33" s="87"/>
-      <c r="B33" s="86"/>
+      <c r="A33" s="78"/>
+      <c r="B33" s="77"/>
       <c r="C33" s="22" t="s">
         <v>49</v>
       </c>
@@ -3254,8 +3278,8 @@
       <c r="AJ33" s="29"/>
     </row>
     <row r="34" spans="1:36" ht="18" customHeight="1">
-      <c r="A34" s="87"/>
-      <c r="B34" s="86"/>
+      <c r="A34" s="78"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="22" t="s">
         <v>50</v>
       </c>
@@ -3368,34 +3392,34 @@
       <c r="C36" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="84"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="84"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="84"/>
-      <c r="K36" s="76"/>
-      <c r="L36" s="84"/>
-      <c r="M36" s="76"/>
-      <c r="N36" s="84"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="84"/>
-      <c r="Q36" s="76"/>
-      <c r="R36" s="84"/>
-      <c r="S36" s="76"/>
-      <c r="T36" s="84"/>
-      <c r="U36" s="76"/>
-      <c r="V36" s="84"/>
-      <c r="W36" s="76"/>
-      <c r="X36" s="84"/>
-      <c r="Y36" s="76"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="74"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="74"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="73"/>
+      <c r="P36" s="74"/>
+      <c r="Q36" s="73"/>
+      <c r="R36" s="74"/>
+      <c r="S36" s="73"/>
+      <c r="T36" s="74"/>
+      <c r="U36" s="73"/>
+      <c r="V36" s="74"/>
+      <c r="W36" s="73"/>
+      <c r="X36" s="74"/>
+      <c r="Y36" s="73"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="84">
+      <c r="AA36" s="74">
         <f>D36+F36+H36+J36+L36+N36+P36+R36+T36+V36+X36</f>
         <v>0</v>
       </c>
-      <c r="AB36" s="76"/>
+      <c r="AB36" s="73"/>
       <c r="AC36" s="35"/>
       <c r="AD36" s="35">
         <f>AD28+AA36-(H103)</f>
@@ -3421,8 +3445,8 @@
       <c r="AJ36" s="41"/>
     </row>
     <row r="37" spans="1:36" ht="18" customHeight="1">
-      <c r="A37" s="72"/>
-      <c r="B37" s="73"/>
+      <c r="A37" s="87"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="42" t="s">
         <v>20</v>
       </c>
@@ -3539,10 +3563,10 @@
       <c r="AJ37" s="47"/>
     </row>
     <row r="38" spans="1:36" ht="18" customHeight="1">
-      <c r="A38" s="85" t="s">
+      <c r="A38" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="86"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="22" t="s">
         <v>46</v>
       </c>
@@ -3602,8 +3626,8 @@
       <c r="AJ38" s="29"/>
     </row>
     <row r="39" spans="1:36" ht="18" customHeight="1">
-      <c r="A39" s="87"/>
-      <c r="B39" s="86"/>
+      <c r="A39" s="78"/>
+      <c r="B39" s="77"/>
       <c r="C39" s="22" t="s">
         <v>47</v>
       </c>
@@ -3651,8 +3675,8 @@
       <c r="AJ39" s="29"/>
     </row>
     <row r="40" spans="1:36" ht="18" customHeight="1">
-      <c r="A40" s="87"/>
-      <c r="B40" s="86"/>
+      <c r="A40" s="78"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="22" t="s">
         <v>48</v>
       </c>
@@ -3700,8 +3724,8 @@
       <c r="AJ40" s="29"/>
     </row>
     <row r="41" spans="1:36" ht="18" customHeight="1">
-      <c r="A41" s="87"/>
-      <c r="B41" s="86"/>
+      <c r="A41" s="78"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="22" t="s">
         <v>49</v>
       </c>
@@ -3749,8 +3773,8 @@
       <c r="AJ41" s="29"/>
     </row>
     <row r="42" spans="1:36" ht="18" customHeight="1">
-      <c r="A42" s="87"/>
-      <c r="B42" s="86"/>
+      <c r="A42" s="78"/>
+      <c r="B42" s="77"/>
       <c r="C42" s="22" t="s">
         <v>50</v>
       </c>
@@ -3863,34 +3887,34 @@
       <c r="C44" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="84"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="84"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="84"/>
-      <c r="I44" s="76"/>
-      <c r="J44" s="84"/>
-      <c r="K44" s="76"/>
-      <c r="L44" s="84"/>
-      <c r="M44" s="76"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="76"/>
-      <c r="P44" s="84"/>
-      <c r="Q44" s="76"/>
-      <c r="R44" s="84"/>
-      <c r="S44" s="76"/>
-      <c r="T44" s="84"/>
-      <c r="U44" s="76"/>
-      <c r="V44" s="84"/>
-      <c r="W44" s="76"/>
-      <c r="X44" s="84"/>
-      <c r="Y44" s="76"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="73"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="73"/>
+      <c r="P44" s="74"/>
+      <c r="Q44" s="73"/>
+      <c r="R44" s="74"/>
+      <c r="S44" s="73"/>
+      <c r="T44" s="74"/>
+      <c r="U44" s="73"/>
+      <c r="V44" s="74"/>
+      <c r="W44" s="73"/>
+      <c r="X44" s="74"/>
+      <c r="Y44" s="73"/>
       <c r="Z44" s="36"/>
-      <c r="AA44" s="84">
+      <c r="AA44" s="74">
         <f>D44+F44+H44+J44+L44+N44+P44+R44+T44+V44+X44</f>
         <v>0</v>
       </c>
-      <c r="AB44" s="76"/>
+      <c r="AB44" s="73"/>
       <c r="AC44" s="35"/>
       <c r="AD44" s="35">
         <f>AD36+AA44-(J103)</f>
@@ -3916,8 +3940,8 @@
       <c r="AJ44" s="41"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
-      <c r="A45" s="72"/>
-      <c r="B45" s="73"/>
+      <c r="A45" s="87"/>
+      <c r="B45" s="88"/>
       <c r="C45" s="42" t="s">
         <v>20</v>
       </c>
@@ -4034,10 +4058,10 @@
       <c r="AJ45" s="47"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="86"/>
+      <c r="B46" s="77"/>
       <c r="C46" s="22" t="s">
         <v>46</v>
       </c>
@@ -4097,8 +4121,8 @@
       <c r="AJ46" s="29"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
-      <c r="A47" s="87"/>
-      <c r="B47" s="86"/>
+      <c r="A47" s="78"/>
+      <c r="B47" s="77"/>
       <c r="C47" s="22" t="s">
         <v>47</v>
       </c>
@@ -4146,8 +4170,8 @@
       <c r="AJ47" s="29"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
-      <c r="A48" s="87"/>
-      <c r="B48" s="86"/>
+      <c r="A48" s="78"/>
+      <c r="B48" s="77"/>
       <c r="C48" s="22" t="s">
         <v>48</v>
       </c>
@@ -4195,8 +4219,8 @@
       <c r="AJ48" s="29"/>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
-      <c r="A49" s="87"/>
-      <c r="B49" s="86"/>
+      <c r="A49" s="78"/>
+      <c r="B49" s="77"/>
       <c r="C49" s="22" t="s">
         <v>49</v>
       </c>
@@ -4244,8 +4268,8 @@
       <c r="AJ49" s="29"/>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
-      <c r="A50" s="87"/>
-      <c r="B50" s="86"/>
+      <c r="A50" s="78"/>
+      <c r="B50" s="77"/>
       <c r="C50" s="22" t="s">
         <v>50</v>
       </c>
@@ -4358,34 +4382,34 @@
       <c r="C52" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="84"/>
-      <c r="E52" s="76"/>
-      <c r="F52" s="84"/>
-      <c r="G52" s="76"/>
-      <c r="H52" s="84"/>
-      <c r="I52" s="76"/>
-      <c r="J52" s="84"/>
-      <c r="K52" s="76"/>
-      <c r="L52" s="84"/>
-      <c r="M52" s="76"/>
-      <c r="N52" s="84"/>
-      <c r="O52" s="76"/>
-      <c r="P52" s="84"/>
-      <c r="Q52" s="76"/>
-      <c r="R52" s="84"/>
-      <c r="S52" s="76"/>
-      <c r="T52" s="84"/>
-      <c r="U52" s="76"/>
-      <c r="V52" s="84"/>
-      <c r="W52" s="76"/>
-      <c r="X52" s="84"/>
-      <c r="Y52" s="76"/>
+      <c r="D52" s="74"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="74"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="73"/>
+      <c r="J52" s="74"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="74"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="73"/>
+      <c r="P52" s="74"/>
+      <c r="Q52" s="73"/>
+      <c r="R52" s="74"/>
+      <c r="S52" s="73"/>
+      <c r="T52" s="74"/>
+      <c r="U52" s="73"/>
+      <c r="V52" s="74"/>
+      <c r="W52" s="73"/>
+      <c r="X52" s="74"/>
+      <c r="Y52" s="73"/>
       <c r="Z52" s="36"/>
-      <c r="AA52" s="84">
+      <c r="AA52" s="74">
         <f>D52+F52+H52+J52+L52+N52+P52+R52+T52+V52+X52</f>
         <v>0</v>
       </c>
-      <c r="AB52" s="76"/>
+      <c r="AB52" s="73"/>
       <c r="AC52" s="35"/>
       <c r="AD52" s="35">
         <f>AD44+AA52-(L103)</f>
@@ -4411,8 +4435,8 @@
       <c r="AJ52" s="41"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
-      <c r="A53" s="72"/>
-      <c r="B53" s="73"/>
+      <c r="A53" s="87"/>
+      <c r="B53" s="88"/>
       <c r="C53" s="42" t="s">
         <v>20</v>
       </c>
@@ -4529,10 +4553,10 @@
       <c r="AJ53" s="47"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="85" t="s">
+      <c r="A54" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="86"/>
+      <c r="B54" s="77"/>
       <c r="C54" s="22" t="s">
         <v>46</v>
       </c>
@@ -4592,8 +4616,8 @@
       <c r="AJ54" s="29"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="87"/>
-      <c r="B55" s="86"/>
+      <c r="A55" s="78"/>
+      <c r="B55" s="77"/>
       <c r="C55" s="22" t="s">
         <v>47</v>
       </c>
@@ -4641,8 +4665,8 @@
       <c r="AJ55" s="29"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="87"/>
-      <c r="B56" s="86"/>
+      <c r="A56" s="78"/>
+      <c r="B56" s="77"/>
       <c r="C56" s="22" t="s">
         <v>48</v>
       </c>
@@ -4690,8 +4714,8 @@
       <c r="AJ56" s="29"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="87"/>
-      <c r="B57" s="86"/>
+      <c r="A57" s="78"/>
+      <c r="B57" s="77"/>
       <c r="C57" s="22" t="s">
         <v>49</v>
       </c>
@@ -4739,8 +4763,8 @@
       <c r="AJ57" s="29"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
-      <c r="A58" s="87"/>
-      <c r="B58" s="86"/>
+      <c r="A58" s="78"/>
+      <c r="B58" s="77"/>
       <c r="C58" s="22" t="s">
         <v>50</v>
       </c>
@@ -4853,34 +4877,34 @@
       <c r="C60" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D60" s="84"/>
-      <c r="E60" s="76"/>
-      <c r="F60" s="84"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="84"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="84"/>
-      <c r="K60" s="76"/>
-      <c r="L60" s="84"/>
-      <c r="M60" s="76"/>
-      <c r="N60" s="84"/>
-      <c r="O60" s="76"/>
-      <c r="P60" s="84"/>
-      <c r="Q60" s="76"/>
-      <c r="R60" s="84"/>
-      <c r="S60" s="76"/>
-      <c r="T60" s="84"/>
-      <c r="U60" s="76"/>
-      <c r="V60" s="84"/>
-      <c r="W60" s="76"/>
-      <c r="X60" s="84"/>
-      <c r="Y60" s="76"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="73"/>
+      <c r="F60" s="74"/>
+      <c r="G60" s="73"/>
+      <c r="H60" s="74"/>
+      <c r="I60" s="73"/>
+      <c r="J60" s="74"/>
+      <c r="K60" s="73"/>
+      <c r="L60" s="74"/>
+      <c r="M60" s="73"/>
+      <c r="N60" s="74"/>
+      <c r="O60" s="73"/>
+      <c r="P60" s="74"/>
+      <c r="Q60" s="73"/>
+      <c r="R60" s="74"/>
+      <c r="S60" s="73"/>
+      <c r="T60" s="74"/>
+      <c r="U60" s="73"/>
+      <c r="V60" s="74"/>
+      <c r="W60" s="73"/>
+      <c r="X60" s="74"/>
+      <c r="Y60" s="73"/>
       <c r="Z60" s="36"/>
-      <c r="AA60" s="84">
+      <c r="AA60" s="74">
         <f>D60+F60+H60+J60+L60+N60+P60+R60+T60+V60+X60</f>
         <v>0</v>
       </c>
-      <c r="AB60" s="76"/>
+      <c r="AB60" s="73"/>
       <c r="AC60" s="35"/>
       <c r="AD60" s="35">
         <f>AD52+AA60-(N103)</f>
@@ -4906,8 +4930,8 @@
       <c r="AJ60" s="41"/>
     </row>
     <row r="61" spans="1:36" ht="18" customHeight="1">
-      <c r="A61" s="72"/>
-      <c r="B61" s="73"/>
+      <c r="A61" s="87"/>
+      <c r="B61" s="88"/>
       <c r="C61" s="42" t="s">
         <v>20</v>
       </c>
@@ -5024,10 +5048,10 @@
       <c r="AJ61" s="47"/>
     </row>
     <row r="62" spans="1:36" ht="18" customHeight="1">
-      <c r="A62" s="85" t="s">
+      <c r="A62" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="B62" s="86"/>
+      <c r="B62" s="77"/>
       <c r="C62" s="22" t="s">
         <v>46</v>
       </c>
@@ -5087,8 +5111,8 @@
       <c r="AJ62" s="29"/>
     </row>
     <row r="63" spans="1:36" ht="18" customHeight="1">
-      <c r="A63" s="87"/>
-      <c r="B63" s="86"/>
+      <c r="A63" s="78"/>
+      <c r="B63" s="77"/>
       <c r="C63" s="22" t="s">
         <v>47</v>
       </c>
@@ -5136,8 +5160,8 @@
       <c r="AJ63" s="29"/>
     </row>
     <row r="64" spans="1:36" ht="18" customHeight="1">
-      <c r="A64" s="87"/>
-      <c r="B64" s="86"/>
+      <c r="A64" s="78"/>
+      <c r="B64" s="77"/>
       <c r="C64" s="22" t="s">
         <v>48</v>
       </c>
@@ -5185,8 +5209,8 @@
       <c r="AJ64" s="29"/>
     </row>
     <row r="65" spans="1:36" ht="18" customHeight="1">
-      <c r="A65" s="87"/>
-      <c r="B65" s="86"/>
+      <c r="A65" s="78"/>
+      <c r="B65" s="77"/>
       <c r="C65" s="22" t="s">
         <v>49</v>
       </c>
@@ -5234,8 +5258,8 @@
       <c r="AJ65" s="29"/>
     </row>
     <row r="66" spans="1:36" ht="18" customHeight="1">
-      <c r="A66" s="87"/>
-      <c r="B66" s="86"/>
+      <c r="A66" s="78"/>
+      <c r="B66" s="77"/>
       <c r="C66" s="22" t="s">
         <v>50</v>
       </c>
@@ -5348,34 +5372,34 @@
       <c r="C68" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D68" s="84"/>
-      <c r="E68" s="76"/>
-      <c r="F68" s="84"/>
-      <c r="G68" s="76"/>
-      <c r="H68" s="84"/>
-      <c r="I68" s="76"/>
-      <c r="J68" s="84"/>
-      <c r="K68" s="76"/>
-      <c r="L68" s="84"/>
-      <c r="M68" s="76"/>
-      <c r="N68" s="84"/>
-      <c r="O68" s="76"/>
-      <c r="P68" s="84"/>
-      <c r="Q68" s="76"/>
-      <c r="R68" s="84"/>
-      <c r="S68" s="76"/>
-      <c r="T68" s="84"/>
-      <c r="U68" s="76"/>
-      <c r="V68" s="84"/>
-      <c r="W68" s="76"/>
-      <c r="X68" s="84"/>
-      <c r="Y68" s="76"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="74"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="74"/>
+      <c r="I68" s="73"/>
+      <c r="J68" s="74"/>
+      <c r="K68" s="73"/>
+      <c r="L68" s="74"/>
+      <c r="M68" s="73"/>
+      <c r="N68" s="74"/>
+      <c r="O68" s="73"/>
+      <c r="P68" s="74"/>
+      <c r="Q68" s="73"/>
+      <c r="R68" s="74"/>
+      <c r="S68" s="73"/>
+      <c r="T68" s="74"/>
+      <c r="U68" s="73"/>
+      <c r="V68" s="74"/>
+      <c r="W68" s="73"/>
+      <c r="X68" s="74"/>
+      <c r="Y68" s="73"/>
       <c r="Z68" s="36"/>
-      <c r="AA68" s="84">
+      <c r="AA68" s="74">
         <f>D68+F68+H68+J68+L68+N68+P68+R68+T68+V68+X68</f>
         <v>0</v>
       </c>
-      <c r="AB68" s="76"/>
+      <c r="AB68" s="73"/>
       <c r="AC68" s="35"/>
       <c r="AD68" s="35">
         <f>AD60+AA68-(P103)</f>
@@ -5401,8 +5425,8 @@
       <c r="AJ68" s="41"/>
     </row>
     <row r="69" spans="1:36" ht="18" customHeight="1">
-      <c r="A69" s="72"/>
-      <c r="B69" s="73"/>
+      <c r="A69" s="87"/>
+      <c r="B69" s="88"/>
       <c r="C69" s="42" t="s">
         <v>20</v>
       </c>
@@ -5519,10 +5543,10 @@
       <c r="AJ69" s="47"/>
     </row>
     <row r="70" spans="1:36" ht="18" customHeight="1">
-      <c r="A70" s="85" t="s">
+      <c r="A70" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="86"/>
+      <c r="B70" s="77"/>
       <c r="C70" s="22" t="s">
         <v>46</v>
       </c>
@@ -5582,8 +5606,8 @@
       <c r="AJ70" s="29"/>
     </row>
     <row r="71" spans="1:36" ht="18" customHeight="1">
-      <c r="A71" s="87"/>
-      <c r="B71" s="86"/>
+      <c r="A71" s="78"/>
+      <c r="B71" s="77"/>
       <c r="C71" s="22" t="s">
         <v>47</v>
       </c>
@@ -5631,8 +5655,8 @@
       <c r="AJ71" s="29"/>
     </row>
     <row r="72" spans="1:36" ht="18" customHeight="1">
-      <c r="A72" s="87"/>
-      <c r="B72" s="86"/>
+      <c r="A72" s="78"/>
+      <c r="B72" s="77"/>
       <c r="C72" s="22" t="s">
         <v>48</v>
       </c>
@@ -5680,8 +5704,8 @@
       <c r="AJ72" s="29"/>
     </row>
     <row r="73" spans="1:36" ht="18" customHeight="1">
-      <c r="A73" s="87"/>
-      <c r="B73" s="86"/>
+      <c r="A73" s="78"/>
+      <c r="B73" s="77"/>
       <c r="C73" s="22" t="s">
         <v>49</v>
       </c>
@@ -5729,8 +5753,8 @@
       <c r="AJ73" s="29"/>
     </row>
     <row r="74" spans="1:36" ht="18" customHeight="1">
-      <c r="A74" s="87"/>
-      <c r="B74" s="86"/>
+      <c r="A74" s="78"/>
+      <c r="B74" s="77"/>
       <c r="C74" s="22" t="s">
         <v>50</v>
       </c>
@@ -5843,34 +5867,34 @@
       <c r="C76" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D76" s="84"/>
-      <c r="E76" s="76"/>
-      <c r="F76" s="84"/>
-      <c r="G76" s="76"/>
-      <c r="H76" s="84"/>
-      <c r="I76" s="76"/>
-      <c r="J76" s="84"/>
-      <c r="K76" s="76"/>
-      <c r="L76" s="84"/>
-      <c r="M76" s="76"/>
-      <c r="N76" s="84"/>
-      <c r="O76" s="76"/>
-      <c r="P76" s="84"/>
-      <c r="Q76" s="76"/>
-      <c r="R76" s="84"/>
-      <c r="S76" s="76"/>
-      <c r="T76" s="84"/>
-      <c r="U76" s="76"/>
-      <c r="V76" s="84"/>
-      <c r="W76" s="76"/>
-      <c r="X76" s="84"/>
-      <c r="Y76" s="76"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="73"/>
+      <c r="J76" s="74"/>
+      <c r="K76" s="73"/>
+      <c r="L76" s="74"/>
+      <c r="M76" s="73"/>
+      <c r="N76" s="74"/>
+      <c r="O76" s="73"/>
+      <c r="P76" s="74"/>
+      <c r="Q76" s="73"/>
+      <c r="R76" s="74"/>
+      <c r="S76" s="73"/>
+      <c r="T76" s="74"/>
+      <c r="U76" s="73"/>
+      <c r="V76" s="74"/>
+      <c r="W76" s="73"/>
+      <c r="X76" s="74"/>
+      <c r="Y76" s="73"/>
       <c r="Z76" s="36"/>
-      <c r="AA76" s="84">
+      <c r="AA76" s="74">
         <f>D76+F76+H76+J76+L76+N76+P76+R76+T76+V76+X76</f>
         <v>0</v>
       </c>
-      <c r="AB76" s="76"/>
+      <c r="AB76" s="73"/>
       <c r="AC76" s="35"/>
       <c r="AD76" s="35">
         <f>AD68+AA76-(R103)</f>
@@ -5896,8 +5920,8 @@
       <c r="AJ76" s="41"/>
     </row>
     <row r="77" spans="1:36" ht="18" customHeight="1">
-      <c r="A77" s="72"/>
-      <c r="B77" s="73"/>
+      <c r="A77" s="87"/>
+      <c r="B77" s="88"/>
       <c r="C77" s="42" t="s">
         <v>20</v>
       </c>
@@ -6014,10 +6038,10 @@
       <c r="AJ77" s="47"/>
     </row>
     <row r="78" spans="1:36" ht="18" customHeight="1">
-      <c r="A78" s="85" t="s">
+      <c r="A78" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="B78" s="86"/>
+      <c r="B78" s="77"/>
       <c r="C78" s="22" t="s">
         <v>46</v>
       </c>
@@ -6077,8 +6101,8 @@
       <c r="AJ78" s="29"/>
     </row>
     <row r="79" spans="1:36" ht="18" customHeight="1">
-      <c r="A79" s="87"/>
-      <c r="B79" s="86"/>
+      <c r="A79" s="78"/>
+      <c r="B79" s="77"/>
       <c r="C79" s="22" t="s">
         <v>47</v>
       </c>
@@ -6126,8 +6150,8 @@
       <c r="AJ79" s="29"/>
     </row>
     <row r="80" spans="1:36" ht="18" customHeight="1">
-      <c r="A80" s="87"/>
-      <c r="B80" s="86"/>
+      <c r="A80" s="78"/>
+      <c r="B80" s="77"/>
       <c r="C80" s="22" t="s">
         <v>48</v>
       </c>
@@ -6175,8 +6199,8 @@
       <c r="AJ80" s="29"/>
     </row>
     <row r="81" spans="1:36" ht="18" customHeight="1">
-      <c r="A81" s="87"/>
-      <c r="B81" s="86"/>
+      <c r="A81" s="78"/>
+      <c r="B81" s="77"/>
       <c r="C81" s="22" t="s">
         <v>49</v>
       </c>
@@ -6224,8 +6248,8 @@
       <c r="AJ81" s="29"/>
     </row>
     <row r="82" spans="1:36" ht="18" customHeight="1">
-      <c r="A82" s="87"/>
-      <c r="B82" s="86"/>
+      <c r="A82" s="78"/>
+      <c r="B82" s="77"/>
       <c r="C82" s="22" t="s">
         <v>50</v>
       </c>
@@ -6338,34 +6362,34 @@
       <c r="C84" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D84" s="84"/>
-      <c r="E84" s="76"/>
-      <c r="F84" s="84"/>
-      <c r="G84" s="76"/>
-      <c r="H84" s="84"/>
-      <c r="I84" s="76"/>
-      <c r="J84" s="84"/>
-      <c r="K84" s="76"/>
-      <c r="L84" s="84"/>
-      <c r="M84" s="76"/>
-      <c r="N84" s="84"/>
-      <c r="O84" s="76"/>
-      <c r="P84" s="84"/>
-      <c r="Q84" s="76"/>
-      <c r="R84" s="84"/>
-      <c r="S84" s="76"/>
-      <c r="T84" s="84"/>
-      <c r="U84" s="76"/>
-      <c r="V84" s="84"/>
-      <c r="W84" s="76"/>
-      <c r="X84" s="84"/>
-      <c r="Y84" s="76"/>
+      <c r="D84" s="74"/>
+      <c r="E84" s="73"/>
+      <c r="F84" s="74"/>
+      <c r="G84" s="73"/>
+      <c r="H84" s="74"/>
+      <c r="I84" s="73"/>
+      <c r="J84" s="74"/>
+      <c r="K84" s="73"/>
+      <c r="L84" s="74"/>
+      <c r="M84" s="73"/>
+      <c r="N84" s="74"/>
+      <c r="O84" s="73"/>
+      <c r="P84" s="74"/>
+      <c r="Q84" s="73"/>
+      <c r="R84" s="74"/>
+      <c r="S84" s="73"/>
+      <c r="T84" s="74"/>
+      <c r="U84" s="73"/>
+      <c r="V84" s="74"/>
+      <c r="W84" s="73"/>
+      <c r="X84" s="74"/>
+      <c r="Y84" s="73"/>
       <c r="Z84" s="36"/>
-      <c r="AA84" s="84">
+      <c r="AA84" s="74">
         <f>D84+F84+H84+J84+L84+N84+P84+R84+T84+V84+X84</f>
         <v>0</v>
       </c>
-      <c r="AB84" s="76"/>
+      <c r="AB84" s="73"/>
       <c r="AC84" s="35"/>
       <c r="AD84" s="35">
         <f>AD76+AA84-(T103)</f>
@@ -6391,8 +6415,8 @@
       <c r="AJ84" s="41"/>
     </row>
     <row r="85" spans="1:36" ht="18" customHeight="1">
-      <c r="A85" s="72"/>
-      <c r="B85" s="73"/>
+      <c r="A85" s="87"/>
+      <c r="B85" s="88"/>
       <c r="C85" s="42" t="s">
         <v>20</v>
       </c>
@@ -6509,10 +6533,10 @@
       <c r="AJ85" s="47"/>
     </row>
     <row r="86" spans="1:36" ht="18" customHeight="1">
-      <c r="A86" s="85" t="s">
+      <c r="A86" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="B86" s="86"/>
+      <c r="B86" s="77"/>
       <c r="C86" s="22" t="s">
         <v>46</v>
       </c>
@@ -6572,8 +6596,8 @@
       <c r="AJ86" s="29"/>
     </row>
     <row r="87" spans="1:36" ht="18" customHeight="1">
-      <c r="A87" s="87"/>
-      <c r="B87" s="86"/>
+      <c r="A87" s="78"/>
+      <c r="B87" s="77"/>
       <c r="C87" s="22" t="s">
         <v>47</v>
       </c>
@@ -6621,8 +6645,8 @@
       <c r="AJ87" s="29"/>
     </row>
     <row r="88" spans="1:36" ht="18" customHeight="1">
-      <c r="A88" s="87"/>
-      <c r="B88" s="86"/>
+      <c r="A88" s="78"/>
+      <c r="B88" s="77"/>
       <c r="C88" s="22" t="s">
         <v>48</v>
       </c>
@@ -6670,8 +6694,8 @@
       <c r="AJ88" s="29"/>
     </row>
     <row r="89" spans="1:36" ht="18" customHeight="1">
-      <c r="A89" s="87"/>
-      <c r="B89" s="86"/>
+      <c r="A89" s="78"/>
+      <c r="B89" s="77"/>
       <c r="C89" s="22" t="s">
         <v>49</v>
       </c>
@@ -6719,8 +6743,8 @@
       <c r="AJ89" s="29"/>
     </row>
     <row r="90" spans="1:36" ht="18" customHeight="1">
-      <c r="A90" s="87"/>
-      <c r="B90" s="86"/>
+      <c r="A90" s="78"/>
+      <c r="B90" s="77"/>
       <c r="C90" s="22" t="s">
         <v>50</v>
       </c>
@@ -6833,34 +6857,34 @@
       <c r="C92" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D92" s="84"/>
-      <c r="E92" s="76"/>
-      <c r="F92" s="84"/>
-      <c r="G92" s="76"/>
-      <c r="H92" s="84"/>
-      <c r="I92" s="76"/>
-      <c r="J92" s="84"/>
-      <c r="K92" s="76"/>
-      <c r="L92" s="84"/>
-      <c r="M92" s="76"/>
-      <c r="N92" s="84"/>
-      <c r="O92" s="76"/>
-      <c r="P92" s="84"/>
-      <c r="Q92" s="76"/>
-      <c r="R92" s="84"/>
-      <c r="S92" s="76"/>
-      <c r="T92" s="84"/>
-      <c r="U92" s="76"/>
-      <c r="V92" s="84"/>
-      <c r="W92" s="76"/>
-      <c r="X92" s="84"/>
-      <c r="Y92" s="76"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="73"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="73"/>
+      <c r="H92" s="74"/>
+      <c r="I92" s="73"/>
+      <c r="J92" s="74"/>
+      <c r="K92" s="73"/>
+      <c r="L92" s="74"/>
+      <c r="M92" s="73"/>
+      <c r="N92" s="74"/>
+      <c r="O92" s="73"/>
+      <c r="P92" s="74"/>
+      <c r="Q92" s="73"/>
+      <c r="R92" s="74"/>
+      <c r="S92" s="73"/>
+      <c r="T92" s="74"/>
+      <c r="U92" s="73"/>
+      <c r="V92" s="74"/>
+      <c r="W92" s="73"/>
+      <c r="X92" s="74"/>
+      <c r="Y92" s="73"/>
       <c r="Z92" s="36"/>
-      <c r="AA92" s="84">
+      <c r="AA92" s="74">
         <f>D92+F92+H92+J92+L92+N92+P92+R92+T92+V92+X92</f>
         <v>0</v>
       </c>
-      <c r="AB92" s="76"/>
+      <c r="AB92" s="73"/>
       <c r="AC92" s="35"/>
       <c r="AD92" s="35">
         <f>AD84+AA92-(V103)</f>
@@ -6886,8 +6910,8 @@
       <c r="AJ92" s="41"/>
     </row>
     <row r="93" spans="1:36" ht="18" customHeight="1">
-      <c r="A93" s="72"/>
-      <c r="B93" s="73"/>
+      <c r="A93" s="87"/>
+      <c r="B93" s="88"/>
       <c r="C93" s="42" t="s">
         <v>20</v>
       </c>
@@ -7701,67 +7725,67 @@
       <c r="C100" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D100" s="84">
+      <c r="D100" s="74">
         <f>D12+D20+D28+D36+D44+D52+D60+D68+D76+D84+D92</f>
         <v>0</v>
       </c>
-      <c r="E100" s="76"/>
-      <c r="F100" s="84">
+      <c r="E100" s="73"/>
+      <c r="F100" s="74">
         <f>F12+F20+F28+F36+F44+F52+F60+F68+F76+F84+F92</f>
         <v>0</v>
       </c>
-      <c r="G100" s="76"/>
-      <c r="H100" s="84">
+      <c r="G100" s="73"/>
+      <c r="H100" s="74">
         <f>H12+H20+H28+H36+H44+H52+H60+H68+H76+H84+H92</f>
         <v>0</v>
       </c>
-      <c r="I100" s="76"/>
-      <c r="J100" s="84">
+      <c r="I100" s="73"/>
+      <c r="J100" s="74">
         <f>J12+J20+J28+J36+J44+J52+J60+J68+J76+J84+J92</f>
         <v>0</v>
       </c>
-      <c r="K100" s="76"/>
-      <c r="L100" s="84">
+      <c r="K100" s="73"/>
+      <c r="L100" s="74">
         <f>L12+L20+L28+L36+L44+L52+L60+L68+L76+L84+L92</f>
         <v>0</v>
       </c>
-      <c r="M100" s="76"/>
-      <c r="N100" s="84">
+      <c r="M100" s="73"/>
+      <c r="N100" s="74">
         <f>N12+N20+N28+N36+N44+N52+N60+N68+N76+N84+N92</f>
         <v>0</v>
       </c>
-      <c r="O100" s="76"/>
-      <c r="P100" s="84">
+      <c r="O100" s="73"/>
+      <c r="P100" s="74">
         <f>P12+P20+P28+P36+P44+P52+P60+P68+P76+P84+P92</f>
         <v>0</v>
       </c>
-      <c r="Q100" s="76"/>
-      <c r="R100" s="84">
+      <c r="Q100" s="73"/>
+      <c r="R100" s="74">
         <f>R12+R20+R28+R36+R44+R52+R60+R68+R76+R84+R92</f>
         <v>0</v>
       </c>
-      <c r="S100" s="76"/>
-      <c r="T100" s="84">
+      <c r="S100" s="73"/>
+      <c r="T100" s="74">
         <f>T12+T20+T28+T36+T44+T52+T60+T68+T76+T84+T92</f>
         <v>0</v>
       </c>
-      <c r="U100" s="76"/>
-      <c r="V100" s="84">
+      <c r="U100" s="73"/>
+      <c r="V100" s="74">
         <f>V12+V20+V28+V36+V44+V52+V60+V68+V76+V84+V92</f>
         <v>0</v>
       </c>
-      <c r="W100" s="76"/>
-      <c r="X100" s="84">
+      <c r="W100" s="73"/>
+      <c r="X100" s="74">
         <f>X12+X20+X28+X36+X44+X52+X60+X68+X76+X84+X92</f>
         <v>0</v>
       </c>
-      <c r="Y100" s="76"/>
+      <c r="Y100" s="73"/>
       <c r="Z100" s="36"/>
-      <c r="AA100" s="84">
+      <c r="AA100" s="74">
         <f>D100+F100+H100+J100+L100+N100+P100+R100+T100+V100+X100</f>
         <v>0</v>
       </c>
-      <c r="AB100" s="76"/>
+      <c r="AB100" s="73"/>
       <c r="AC100" s="35"/>
       <c r="AD100" s="35"/>
       <c r="AE100" s="37"/>
@@ -7772,8 +7796,8 @@
       <c r="AJ100" s="41"/>
     </row>
     <row r="101" spans="1:36" ht="18" customHeight="1">
-      <c r="A101" s="72"/>
-      <c r="B101" s="73"/>
+      <c r="A101" s="87"/>
+      <c r="B101" s="88"/>
       <c r="C101" s="42" t="s">
         <v>20</v>
       </c>
@@ -7887,69 +7911,69 @@
       <c r="AJ101" s="56"/>
     </row>
     <row r="102" spans="1:36" ht="18" customHeight="1">
-      <c r="A102" s="77" t="s">
+      <c r="A102" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="B102" s="78"/>
-      <c r="C102" s="79"/>
-      <c r="D102" s="75">
+      <c r="B102" s="98"/>
+      <c r="C102" s="99"/>
+      <c r="D102" s="72">
         <f>D94+E94*2+D95+E95*2+D96+E96*2+D97+E97*2+D98+E98*2+D99+E99*2</f>
         <v>0</v>
       </c>
-      <c r="E102" s="76"/>
-      <c r="F102" s="75">
+      <c r="E102" s="73"/>
+      <c r="F102" s="72">
         <f>F94+G94*2+F95+G95*2+F96+G96*2+F97+G97*2+F98+G98*2+F99+G99*2</f>
         <v>0</v>
       </c>
-      <c r="G102" s="76"/>
-      <c r="H102" s="75">
+      <c r="G102" s="73"/>
+      <c r="H102" s="72">
         <f>H94+I94*2+H95+I95*2+H96+I96*2+H97+I97*2+H98+I98*2+H99+I99*2</f>
         <v>0</v>
       </c>
-      <c r="I102" s="76"/>
-      <c r="J102" s="75">
+      <c r="I102" s="73"/>
+      <c r="J102" s="72">
         <f>J94+K94*2+J95+K95*2+J96+K96*2+J97+K97*2+J98+K98*2+J99+K99*2</f>
         <v>0</v>
       </c>
-      <c r="K102" s="76"/>
-      <c r="L102" s="75">
+      <c r="K102" s="73"/>
+      <c r="L102" s="72">
         <f>L94+M94*2+L95+M95*2+L96+M96*2+L97+M97*2+L98+M98*2+L99+M99*2</f>
         <v>0</v>
       </c>
-      <c r="M102" s="76"/>
-      <c r="N102" s="75">
+      <c r="M102" s="73"/>
+      <c r="N102" s="72">
         <f>N94+O94*2+N95+O95*2+N96+O96*2+N97+O97*2+N98+O98*2+N99+O99*2</f>
         <v>0</v>
       </c>
-      <c r="O102" s="76"/>
-      <c r="P102" s="75">
+      <c r="O102" s="73"/>
+      <c r="P102" s="72">
         <f>P94+Q94*2+P95+Q95*2+P96+Q96*2+P97+Q97*2+P98+Q98*2+P99+Q99*2</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="76"/>
-      <c r="R102" s="75">
+      <c r="Q102" s="73"/>
+      <c r="R102" s="72">
         <f>R94+S94*2+R95+S95*2+R96+S96*2+R97+S97*2+R98+S98*2+R99+S99*2</f>
         <v>0</v>
       </c>
-      <c r="S102" s="76"/>
-      <c r="T102" s="75">
+      <c r="S102" s="73"/>
+      <c r="T102" s="72">
         <f>T94+U94*2+T95+U95*2+T96+U96*2+T97+U97*2+T98+U98*2+T99+U99*2</f>
         <v>0</v>
       </c>
-      <c r="U102" s="76"/>
-      <c r="V102" s="75">
+      <c r="U102" s="73"/>
+      <c r="V102" s="72">
         <f>V94+W94*2+V95+W95*2+V96+W96*2+V97+W97*2+V98+W98*2+V99+W99*2</f>
         <v>0</v>
       </c>
-      <c r="W102" s="76"/>
-      <c r="X102" s="75">
+      <c r="W102" s="73"/>
+      <c r="X102" s="72">
         <f>X94+Y94*2+X95+Y95*2+X96+Y96*2+X97+Y97*2+X98+Y98*2+X99+Y99*2</f>
         <v>0</v>
       </c>
-      <c r="Y102" s="76"/>
+      <c r="Y102" s="73"/>
       <c r="Z102" s="36"/>
-      <c r="AA102" s="75"/>
-      <c r="AB102" s="76"/>
+      <c r="AA102" s="72"/>
+      <c r="AB102" s="73"/>
       <c r="AC102" s="57"/>
       <c r="AD102" s="57"/>
       <c r="AE102" s="58"/>
@@ -7960,69 +7984,69 @@
       <c r="AJ102" s="60"/>
     </row>
     <row r="103" spans="1:36" ht="18" customHeight="1">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="B103" s="78"/>
-      <c r="C103" s="79"/>
-      <c r="D103" s="94">
+      <c r="B103" s="98"/>
+      <c r="C103" s="99"/>
+      <c r="D103" s="75">
         <f>D100</f>
         <v>0</v>
       </c>
-      <c r="E103" s="76"/>
-      <c r="F103" s="94">
+      <c r="E103" s="73"/>
+      <c r="F103" s="75">
         <f>F100</f>
         <v>0</v>
       </c>
-      <c r="G103" s="76"/>
-      <c r="H103" s="94">
+      <c r="G103" s="73"/>
+      <c r="H103" s="75">
         <f>H100</f>
         <v>0</v>
       </c>
-      <c r="I103" s="76"/>
-      <c r="J103" s="94">
+      <c r="I103" s="73"/>
+      <c r="J103" s="75">
         <f>J100</f>
         <v>0</v>
       </c>
-      <c r="K103" s="76"/>
-      <c r="L103" s="94">
+      <c r="K103" s="73"/>
+      <c r="L103" s="75">
         <f>L100</f>
         <v>0</v>
       </c>
-      <c r="M103" s="76"/>
-      <c r="N103" s="94">
+      <c r="M103" s="73"/>
+      <c r="N103" s="75">
         <f>N100</f>
         <v>0</v>
       </c>
-      <c r="O103" s="76"/>
-      <c r="P103" s="94">
+      <c r="O103" s="73"/>
+      <c r="P103" s="75">
         <f>P100</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="76"/>
-      <c r="R103" s="94">
+      <c r="Q103" s="73"/>
+      <c r="R103" s="75">
         <f>R100</f>
         <v>0</v>
       </c>
-      <c r="S103" s="76"/>
-      <c r="T103" s="94">
+      <c r="S103" s="73"/>
+      <c r="T103" s="75">
         <f>T100</f>
         <v>0</v>
       </c>
-      <c r="U103" s="76"/>
-      <c r="V103" s="94">
+      <c r="U103" s="73"/>
+      <c r="V103" s="75">
         <f>V100</f>
         <v>0</v>
       </c>
-      <c r="W103" s="76"/>
-      <c r="X103" s="94">
+      <c r="W103" s="73"/>
+      <c r="X103" s="75">
         <f>X100</f>
         <v>0</v>
       </c>
-      <c r="Y103" s="76"/>
+      <c r="Y103" s="73"/>
       <c r="Z103" s="36"/>
-      <c r="AA103" s="94"/>
-      <c r="AB103" s="76"/>
+      <c r="AA103" s="75"/>
+      <c r="AB103" s="73"/>
       <c r="AC103" s="61"/>
       <c r="AD103" s="61"/>
       <c r="AE103" s="62"/>
@@ -8109,69 +8133,69 @@
       <c r="AJ105" s="67"/>
     </row>
     <row r="106" spans="1:36" ht="18" customHeight="1">
-      <c r="A106" s="77" t="s">
+      <c r="A106" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="B106" s="78"/>
-      <c r="C106" s="79"/>
-      <c r="D106" s="75">
+      <c r="B106" s="98"/>
+      <c r="C106" s="99"/>
+      <c r="D106" s="72">
         <f>D101+E101+AA21+AB21</f>
         <v>0</v>
       </c>
-      <c r="E106" s="76"/>
-      <c r="F106" s="75">
+      <c r="E106" s="73"/>
+      <c r="F106" s="72">
         <f>F101+G101+AA29+AB29</f>
         <v>0</v>
       </c>
-      <c r="G106" s="76"/>
-      <c r="H106" s="75">
+      <c r="G106" s="73"/>
+      <c r="H106" s="72">
         <f>H101+I101+AA37+AB37</f>
         <v>0</v>
       </c>
-      <c r="I106" s="76"/>
-      <c r="J106" s="75">
+      <c r="I106" s="73"/>
+      <c r="J106" s="72">
         <f>J101+K101+AA45+AB45</f>
         <v>0</v>
       </c>
-      <c r="K106" s="76"/>
-      <c r="L106" s="75">
+      <c r="K106" s="73"/>
+      <c r="L106" s="72">
         <f>L101+M101+AA53+AB53</f>
         <v>0</v>
       </c>
-      <c r="M106" s="76"/>
-      <c r="N106" s="75">
+      <c r="M106" s="73"/>
+      <c r="N106" s="72">
         <f>N101+O101+AA61+AB61</f>
         <v>0</v>
       </c>
-      <c r="O106" s="76"/>
-      <c r="P106" s="75">
+      <c r="O106" s="73"/>
+      <c r="P106" s="72">
         <f>P101+Q101+AA69+AB69</f>
         <v>0</v>
       </c>
-      <c r="Q106" s="76"/>
-      <c r="R106" s="75">
+      <c r="Q106" s="73"/>
+      <c r="R106" s="72">
         <f>R101+S101+AA77+AB77</f>
         <v>0</v>
       </c>
-      <c r="S106" s="76"/>
-      <c r="T106" s="75">
+      <c r="S106" s="73"/>
+      <c r="T106" s="72">
         <f>T101+U101+AA85+AB85</f>
         <v>0</v>
       </c>
-      <c r="U106" s="76"/>
-      <c r="V106" s="75">
+      <c r="U106" s="73"/>
+      <c r="V106" s="72">
         <f>V101+W101+AA93+AB93</f>
         <v>0</v>
       </c>
-      <c r="W106" s="76"/>
-      <c r="X106" s="75">
+      <c r="W106" s="73"/>
+      <c r="X106" s="72">
         <f>X101+Y101+0</f>
         <v>0</v>
       </c>
-      <c r="Y106" s="76"/>
+      <c r="Y106" s="73"/>
       <c r="Z106" s="36"/>
-      <c r="AA106" s="75"/>
-      <c r="AB106" s="76"/>
+      <c r="AA106" s="72"/>
+      <c r="AB106" s="73"/>
       <c r="AC106" s="57"/>
       <c r="AD106" s="57"/>
       <c r="AE106" s="58"/>
@@ -8182,69 +8206,69 @@
       <c r="AJ106" s="60"/>
     </row>
     <row r="107" spans="1:36" ht="18" customHeight="1">
-      <c r="A107" s="77" t="s">
+      <c r="A107" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="B107" s="78"/>
-      <c r="C107" s="79"/>
-      <c r="D107" s="75">
+      <c r="B107" s="98"/>
+      <c r="C107" s="99"/>
+      <c r="D107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,D3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,D3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="E107" s="76"/>
-      <c r="F107" s="75">
+      <c r="E107" s="73"/>
+      <c r="F107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,F3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,F3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="G107" s="76"/>
-      <c r="H107" s="75">
+      <c r="G107" s="73"/>
+      <c r="H107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,H3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,H3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="I107" s="76"/>
-      <c r="J107" s="75">
+      <c r="I107" s="73"/>
+      <c r="J107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,J3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,J3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="K107" s="76"/>
-      <c r="L107" s="75">
+      <c r="K107" s="73"/>
+      <c r="L107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,L3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,L3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="M107" s="76"/>
-      <c r="N107" s="75">
+      <c r="M107" s="73"/>
+      <c r="N107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,N3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,N3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="O107" s="76"/>
-      <c r="P107" s="75">
+      <c r="O107" s="73"/>
+      <c r="P107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,P3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,P3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="Q107" s="76"/>
-      <c r="R107" s="75">
+      <c r="Q107" s="73"/>
+      <c r="R107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,R3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,R3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="S107" s="76"/>
-      <c r="T107" s="75">
+      <c r="S107" s="73"/>
+      <c r="T107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,T3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,T3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="U107" s="76"/>
-      <c r="V107" s="75">
+      <c r="U107" s="73"/>
+      <c r="V107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,V3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,V3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="W107" s="76"/>
-      <c r="X107" s="75">
+      <c r="W107" s="73"/>
+      <c r="X107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,X3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,X3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="Y107" s="76"/>
+      <c r="Y107" s="73"/>
       <c r="Z107" s="36"/>
-      <c r="AA107" s="75"/>
-      <c r="AB107" s="76"/>
+      <c r="AA107" s="72"/>
+      <c r="AB107" s="73"/>
       <c r="AC107" s="57"/>
       <c r="AD107" s="57"/>
       <c r="AE107" s="58"/>
@@ -8255,36 +8279,36 @@
       <c r="AJ107" s="60"/>
     </row>
     <row r="108" spans="1:36" ht="18" customHeight="1">
-      <c r="A108" s="77" t="s">
+      <c r="A108" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="B108" s="78"/>
-      <c r="C108" s="79"/>
-      <c r="D108" s="75"/>
-      <c r="E108" s="76"/>
-      <c r="F108" s="75"/>
-      <c r="G108" s="76"/>
-      <c r="H108" s="75"/>
-      <c r="I108" s="76"/>
-      <c r="J108" s="75"/>
-      <c r="K108" s="76"/>
-      <c r="L108" s="75"/>
-      <c r="M108" s="76"/>
-      <c r="N108" s="75"/>
-      <c r="O108" s="76"/>
-      <c r="P108" s="75"/>
-      <c r="Q108" s="76"/>
-      <c r="R108" s="75"/>
-      <c r="S108" s="76"/>
-      <c r="T108" s="75"/>
-      <c r="U108" s="76"/>
-      <c r="V108" s="75"/>
-      <c r="W108" s="76"/>
-      <c r="X108" s="75"/>
-      <c r="Y108" s="76"/>
+      <c r="B108" s="98"/>
+      <c r="C108" s="99"/>
+      <c r="D108" s="72"/>
+      <c r="E108" s="73"/>
+      <c r="F108" s="72"/>
+      <c r="G108" s="73"/>
+      <c r="H108" s="72"/>
+      <c r="I108" s="73"/>
+      <c r="J108" s="72"/>
+      <c r="K108" s="73"/>
+      <c r="L108" s="72"/>
+      <c r="M108" s="73"/>
+      <c r="N108" s="72"/>
+      <c r="O108" s="73"/>
+      <c r="P108" s="72"/>
+      <c r="Q108" s="73"/>
+      <c r="R108" s="72"/>
+      <c r="S108" s="73"/>
+      <c r="T108" s="72"/>
+      <c r="U108" s="73"/>
+      <c r="V108" s="72"/>
+      <c r="W108" s="73"/>
+      <c r="X108" s="72"/>
+      <c r="Y108" s="73"/>
       <c r="Z108" s="36"/>
-      <c r="AA108" s="75"/>
-      <c r="AB108" s="76"/>
+      <c r="AA108" s="72"/>
+      <c r="AB108" s="73"/>
       <c r="AC108" s="57"/>
       <c r="AD108" s="57"/>
       <c r="AE108" s="58"/>
@@ -8295,69 +8319,69 @@
       <c r="AJ108" s="60"/>
     </row>
     <row r="109" spans="1:36" ht="18" customHeight="1">
-      <c r="A109" s="72" t="s">
+      <c r="A109" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="B109" s="73"/>
-      <c r="C109" s="74"/>
-      <c r="D109" s="82">
+      <c r="B109" s="88"/>
+      <c r="C109" s="102"/>
+      <c r="D109" s="85">
         <f>D108-D107</f>
         <v>0</v>
       </c>
-      <c r="E109" s="83"/>
-      <c r="F109" s="82">
+      <c r="E109" s="86"/>
+      <c r="F109" s="85">
         <f>F108-F107</f>
         <v>0</v>
       </c>
-      <c r="G109" s="83"/>
-      <c r="H109" s="82">
+      <c r="G109" s="86"/>
+      <c r="H109" s="85">
         <f>H108-H107</f>
         <v>0</v>
       </c>
-      <c r="I109" s="83"/>
-      <c r="J109" s="82">
+      <c r="I109" s="86"/>
+      <c r="J109" s="85">
         <f>J108-J107</f>
         <v>0</v>
       </c>
-      <c r="K109" s="83"/>
-      <c r="L109" s="82">
+      <c r="K109" s="86"/>
+      <c r="L109" s="85">
         <f>L108-L107</f>
         <v>0</v>
       </c>
-      <c r="M109" s="83"/>
-      <c r="N109" s="82">
+      <c r="M109" s="86"/>
+      <c r="N109" s="85">
         <f>N108-N107</f>
         <v>0</v>
       </c>
-      <c r="O109" s="83"/>
-      <c r="P109" s="82">
+      <c r="O109" s="86"/>
+      <c r="P109" s="85">
         <f>P108-P107</f>
         <v>0</v>
       </c>
-      <c r="Q109" s="83"/>
-      <c r="R109" s="82">
+      <c r="Q109" s="86"/>
+      <c r="R109" s="85">
         <f>R108-R107</f>
         <v>0</v>
       </c>
-      <c r="S109" s="83"/>
-      <c r="T109" s="82">
+      <c r="S109" s="86"/>
+      <c r="T109" s="85">
         <f>T108-T107</f>
         <v>0</v>
       </c>
-      <c r="U109" s="83"/>
-      <c r="V109" s="82">
+      <c r="U109" s="86"/>
+      <c r="V109" s="85">
         <f>V108-V107</f>
         <v>0</v>
       </c>
-      <c r="W109" s="83"/>
-      <c r="X109" s="82">
+      <c r="W109" s="86"/>
+      <c r="X109" s="85">
         <f>X108-X107</f>
         <v>0</v>
       </c>
-      <c r="Y109" s="83"/>
+      <c r="Y109" s="86"/>
       <c r="Z109" s="68"/>
-      <c r="AA109" s="82"/>
-      <c r="AB109" s="83"/>
+      <c r="AA109" s="85"/>
+      <c r="AB109" s="86"/>
       <c r="AC109" s="52"/>
       <c r="AD109" s="52"/>
       <c r="AE109" s="53"/>
@@ -8369,85 +8393,170 @@
     </row>
   </sheetData>
   <mergeCells count="284">
-    <mergeCell ref="AA44:AB44"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="J109:K109"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="A62:B66"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="T106:U106"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="H100:I100"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="L100:M100"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="A14:B18"/>
+    <mergeCell ref="AA76:AB76"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="L108:M108"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="N108:O108"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="R103:S103"/>
+    <mergeCell ref="T103:U103"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="V106:W106"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="X103:Y103"/>
+    <mergeCell ref="R109:S109"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="T109:U109"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="L84:M84"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N84:O84"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="X109:Y109"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="D109:E109"/>
+    <mergeCell ref="V109:W109"/>
+    <mergeCell ref="R107:S107"/>
+    <mergeCell ref="T107:U107"/>
+    <mergeCell ref="V76:W76"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="X107:Y107"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="R108:S108"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="T108:U108"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="T92:U92"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="A54:B58"/>
+    <mergeCell ref="AA60:AB60"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H108:I108"/>
+    <mergeCell ref="X92:Y92"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="J108:K108"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="A46:B50"/>
+    <mergeCell ref="N103:O103"/>
+    <mergeCell ref="AA68:AB68"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="AA84:AB84"/>
+    <mergeCell ref="R106:S106"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="R100:S100"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="T100:U100"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="D4:E4"/>
     <mergeCell ref="J100:K100"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="V84:W84"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="L103:M103"/>
-    <mergeCell ref="N106:O106"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="A70:B74"/>
-    <mergeCell ref="A86:B90"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="A22:B26"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N76:O76"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="V100:W100"/>
-    <mergeCell ref="N100:O100"/>
-    <mergeCell ref="AA1:AJ1"/>
-    <mergeCell ref="L102:M102"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="V108:W108"/>
-    <mergeCell ref="X108:Y108"/>
-    <mergeCell ref="L109:M109"/>
-    <mergeCell ref="AA108:AB108"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="H1:Y1"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="AA109:AB109"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="AA92:AB92"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="L107:M107"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="L106:M106"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="N102:O102"/>
-    <mergeCell ref="AA107:AB107"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="A78:B82"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="X68:Y68"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="H109:I109"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="X76:Y76"/>
-    <mergeCell ref="V103:W103"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="A38:B42"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="N109:O109"/>
+    <mergeCell ref="AA52:AB52"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="AA36:AB36"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="V60:W60"/>
+    <mergeCell ref="X106:Y106"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="R102:S102"/>
+    <mergeCell ref="T102:U102"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="R44:S44"/>
     <mergeCell ref="AF4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="AA103:AB103"/>
@@ -8472,196 +8581,114 @@
     <mergeCell ref="X100:Y100"/>
     <mergeCell ref="X84:Y84"/>
     <mergeCell ref="H92:I92"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="N109:O109"/>
-    <mergeCell ref="AA52:AB52"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="J84:K84"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="AA36:AB36"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="V60:W60"/>
-    <mergeCell ref="X106:Y106"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="R102:S102"/>
-    <mergeCell ref="T102:U102"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="AA107:AB107"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="A78:B82"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="X68:Y68"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="H109:I109"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="X76:Y76"/>
+    <mergeCell ref="V103:W103"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="X60:Y60"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="A38:B42"/>
+    <mergeCell ref="AA1:AJ1"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="V108:W108"/>
+    <mergeCell ref="X108:Y108"/>
+    <mergeCell ref="L109:M109"/>
+    <mergeCell ref="AA108:AB108"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="H1:Y1"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="AA109:AB109"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="AA92:AB92"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="L107:M107"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="L106:M106"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="F108:G108"/>
     <mergeCell ref="D36:E36"/>
+    <mergeCell ref="P84:Q84"/>
     <mergeCell ref="J60:K60"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="A46:B50"/>
-    <mergeCell ref="N103:O103"/>
-    <mergeCell ref="AA68:AB68"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="AA84:AB84"/>
-    <mergeCell ref="R106:S106"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="R100:S100"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="P84:Q84"/>
     <mergeCell ref="V102:W102"/>
     <mergeCell ref="A30:B34"/>
     <mergeCell ref="R84:S84"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="V84:W84"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="N102:O102"/>
+    <mergeCell ref="L103:M103"/>
+    <mergeCell ref="N106:O106"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="A70:B74"/>
+    <mergeCell ref="A86:B90"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="A22:B26"/>
     <mergeCell ref="AA106:AB106"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N76:O76"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="V100:W100"/>
+    <mergeCell ref="N100:O100"/>
     <mergeCell ref="F103:G103"/>
     <mergeCell ref="AA100:AB100"/>
     <mergeCell ref="AA102:AB102"/>
     <mergeCell ref="X102:Y102"/>
+    <mergeCell ref="D20:E20"/>
     <mergeCell ref="D100:E100"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="X107:Y107"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="R108:S108"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="T108:U108"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="T92:U92"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="A54:B58"/>
-    <mergeCell ref="AA60:AB60"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="T109:U109"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="L84:M84"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="N84:O84"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="X109:Y109"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="D109:E109"/>
-    <mergeCell ref="V109:W109"/>
-    <mergeCell ref="R107:S107"/>
-    <mergeCell ref="T107:U107"/>
-    <mergeCell ref="V76:W76"/>
-    <mergeCell ref="H108:I108"/>
-    <mergeCell ref="X92:Y92"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="J108:K108"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="F68:G68"/>
     <mergeCell ref="D84:E84"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="L108:M108"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="N108:O108"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="R103:S103"/>
-    <mergeCell ref="T103:U103"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="V106:W106"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="X103:Y103"/>
-    <mergeCell ref="T100:U100"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="T106:U106"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="H100:I100"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="L100:M100"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="J106:K106"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="J109:K109"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="A62:B66"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="A14:B18"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="AA76:AB76"/>
-    <mergeCell ref="R109:S109"/>
+    <mergeCell ref="AA44:AB44"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="J28:K28"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="AF6:AG101">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH6:AI101">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8687,7 +8714,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="81"/>
@@ -8696,7 +8723,7 @@
       <c r="E1" s="81"/>
       <c r="F1" s="81"/>
       <c r="G1" s="81"/>
-      <c r="H1" s="102" t="s">
+      <c r="H1" s="89" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="81"/>
@@ -8721,7 +8748,7 @@
       <c r="AB1" s="81"/>
       <c r="AC1" s="81"/>
       <c r="AD1" s="69"/>
-      <c r="AE1" s="104"/>
+      <c r="AE1" s="105"/>
       <c r="AF1" s="81"/>
       <c r="AG1" s="81"/>
       <c r="AH1" s="81"/>
@@ -8730,23 +8757,23 @@
       <c r="AK1" s="81"/>
       <c r="AL1" s="81"/>
       <c r="AM1" s="81"/>
-      <c r="AN1" s="96"/>
+      <c r="AN1" s="82"/>
     </row>
     <row r="2" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A2" s="88" t="str">
+      <c r="A2" s="101" t="str">
         <f>WB!A2</f>
         <v>Service Lane : CGX/0005</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="101" t="str">
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="79" t="str">
         <f>WB!D2</f>
         <v>EXPRESS BERLIN / XPBL2625WE</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -8769,10 +8796,10 @@
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
-      <c r="AE2" s="101" t="s">
+      <c r="AE2" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="AF2" s="89"/>
+      <c r="AF2" s="80"/>
       <c r="AG2" s="5">
         <f>WB!AC2</f>
         <v>0</v>
@@ -8798,83 +8825,83 @@
       <c r="AN2" s="7"/>
     </row>
     <row r="3" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="81"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="80" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="92" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="81"/>
-      <c r="F3" s="80" t="s">
+      <c r="F3" s="92" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="81"/>
-      <c r="H3" s="80" t="s">
+      <c r="H3" s="92" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="81"/>
-      <c r="J3" s="80" t="s">
+      <c r="J3" s="92" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="81"/>
-      <c r="L3" s="80" t="s">
+      <c r="L3" s="92" t="s">
         <v>10</v>
       </c>
       <c r="M3" s="81"/>
-      <c r="N3" s="80" t="s">
+      <c r="N3" s="92" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="81"/>
-      <c r="P3" s="80" t="s">
+      <c r="P3" s="92" t="s">
         <v>12</v>
       </c>
       <c r="Q3" s="81"/>
-      <c r="R3" s="80" t="s">
+      <c r="R3" s="92" t="s">
         <v>13</v>
       </c>
       <c r="S3" s="81"/>
-      <c r="T3" s="80" t="s">
+      <c r="T3" s="92" t="s">
         <v>14</v>
       </c>
       <c r="U3" s="81"/>
-      <c r="V3" s="80" t="s">
+      <c r="V3" s="92" t="s">
         <v>15</v>
       </c>
       <c r="W3" s="81"/>
-      <c r="X3" s="80" t="s">
+      <c r="X3" s="92" t="s">
         <v>16</v>
       </c>
       <c r="Y3" s="81"/>
-      <c r="Z3" s="80" t="s">
+      <c r="Z3" s="92" t="s">
         <v>17</v>
       </c>
       <c r="AA3" s="81"/>
-      <c r="AB3" s="80" t="s">
+      <c r="AB3" s="92" t="s">
         <v>18</v>
       </c>
       <c r="AC3" s="81"/>
       <c r="AD3" s="69"/>
-      <c r="AE3" s="80" t="s">
+      <c r="AE3" s="92" t="s">
         <v>19</v>
       </c>
       <c r="AF3" s="81"/>
       <c r="AG3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AH3" s="80" t="s">
+      <c r="AH3" s="92" t="s">
         <v>21</v>
       </c>
       <c r="AI3" s="81"/>
-      <c r="AJ3" s="80" t="s">
+      <c r="AJ3" s="92" t="s">
         <v>22</v>
       </c>
       <c r="AK3" s="81"/>
-      <c r="AL3" s="80" t="s">
+      <c r="AL3" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="AM3" s="96"/>
+      <c r="AM3" s="82"/>
       <c r="AN3" s="10" t="s">
         <v>24</v>
       </c>
@@ -8883,78 +8910,78 @@
       <c r="A4" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="92" t="s">
+      <c r="B4" s="84"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="91"/>
-      <c r="F4" s="92" t="s">
+      <c r="E4" s="84"/>
+      <c r="F4" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="91"/>
-      <c r="H4" s="92" t="s">
+      <c r="G4" s="84"/>
+      <c r="H4" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="91"/>
-      <c r="J4" s="92" t="s">
+      <c r="I4" s="84"/>
+      <c r="J4" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="91"/>
-      <c r="L4" s="92" t="s">
+      <c r="K4" s="84"/>
+      <c r="L4" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="M4" s="91"/>
-      <c r="N4" s="92" t="s">
+      <c r="M4" s="84"/>
+      <c r="N4" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="91"/>
-      <c r="P4" s="92" t="s">
+      <c r="O4" s="84"/>
+      <c r="P4" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="92" t="s">
+      <c r="Q4" s="84"/>
+      <c r="R4" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="S4" s="91"/>
-      <c r="T4" s="92" t="s">
+      <c r="S4" s="84"/>
+      <c r="T4" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="U4" s="91"/>
-      <c r="V4" s="93" t="s">
+      <c r="U4" s="84"/>
+      <c r="V4" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="W4" s="91"/>
-      <c r="X4" s="92" t="s">
+      <c r="W4" s="84"/>
+      <c r="X4" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="Y4" s="91"/>
-      <c r="Z4" s="92" t="s">
+      <c r="Y4" s="84"/>
+      <c r="Z4" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" s="91"/>
-      <c r="AB4" s="92" t="s">
+      <c r="AA4" s="84"/>
+      <c r="AB4" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AC4" s="91"/>
+      <c r="AC4" s="84"/>
       <c r="AD4" s="70"/>
       <c r="AE4" s="90"/>
-      <c r="AF4" s="91"/>
+      <c r="AF4" s="84"/>
       <c r="AG4" s="11"/>
       <c r="AH4" s="90"/>
-      <c r="AI4" s="91"/>
+      <c r="AI4" s="84"/>
       <c r="AJ4" s="90"/>
-      <c r="AK4" s="91"/>
+      <c r="AK4" s="84"/>
       <c r="AL4" s="90"/>
-      <c r="AM4" s="100"/>
+      <c r="AM4" s="91"/>
       <c r="AN4" s="14"/>
     </row>
     <row r="5" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="96"/>
       <c r="D5" s="15" t="s">
         <v>38</v>
       </c>
@@ -9064,10 +9091,10 @@
       <c r="AN5" s="19"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="86"/>
+      <c r="B6" s="77"/>
       <c r="C6" s="22" t="s">
         <v>46</v>
       </c>
@@ -9131,8 +9158,8 @@
       <c r="AN6" s="29"/>
     </row>
     <row r="7" spans="1:40" ht="18" customHeight="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="86"/>
+      <c r="A7" s="78"/>
+      <c r="B7" s="77"/>
       <c r="C7" s="22" t="s">
         <v>47</v>
       </c>
@@ -9184,8 +9211,8 @@
       <c r="AN7" s="29"/>
     </row>
     <row r="8" spans="1:40" ht="18" customHeight="1">
-      <c r="A8" s="87"/>
-      <c r="B8" s="86"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="22" t="s">
         <v>48</v>
       </c>
@@ -9237,8 +9264,8 @@
       <c r="AN8" s="29"/>
     </row>
     <row r="9" spans="1:40" ht="18" customHeight="1">
-      <c r="A9" s="87"/>
-      <c r="B9" s="86"/>
+      <c r="A9" s="78"/>
+      <c r="B9" s="77"/>
       <c r="C9" s="22" t="s">
         <v>49</v>
       </c>
@@ -9290,8 +9317,8 @@
       <c r="AN9" s="29"/>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="86"/>
+      <c r="A10" s="78"/>
+      <c r="B10" s="77"/>
       <c r="C10" s="22" t="s">
         <v>50</v>
       </c>
@@ -9404,38 +9431,38 @@
       <c r="C12" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="76"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="73"/>
       <c r="N12" s="103"/>
-      <c r="O12" s="76"/>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="76"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="76"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="76"/>
-      <c r="V12" s="84"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="76"/>
-      <c r="Z12" s="84"/>
-      <c r="AA12" s="76"/>
-      <c r="AB12" s="84"/>
-      <c r="AC12" s="76"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="73"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="73"/>
+      <c r="T12" s="74"/>
+      <c r="U12" s="73"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="73"/>
+      <c r="X12" s="74"/>
+      <c r="Y12" s="73"/>
+      <c r="Z12" s="74"/>
+      <c r="AA12" s="73"/>
+      <c r="AB12" s="74"/>
+      <c r="AC12" s="73"/>
       <c r="AD12" s="66"/>
-      <c r="AE12" s="84">
+      <c r="AE12" s="74">
         <f>D12+F12+H12+J12+L12+N12+P12+R12+T12+V12+X12+Z12+AB12</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="76"/>
+      <c r="AF12" s="73"/>
       <c r="AG12" s="35"/>
       <c r="AH12" s="35">
         <f>0+AE12-(0)</f>
@@ -9461,8 +9488,8 @@
       <c r="AN12" s="41"/>
     </row>
     <row r="13" spans="1:40" ht="18" customHeight="1">
-      <c r="A13" s="72"/>
-      <c r="B13" s="73"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="42" t="s">
         <v>20</v>
       </c>
@@ -9595,10 +9622,10 @@
       <c r="AN13" s="47"/>
     </row>
     <row r="14" spans="1:40" ht="18" customHeight="1">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="86"/>
+      <c r="B14" s="77"/>
       <c r="C14" s="22" t="s">
         <v>46</v>
       </c>
@@ -9662,8 +9689,8 @@
       <c r="AN14" s="29"/>
     </row>
     <row r="15" spans="1:40" ht="18" customHeight="1">
-      <c r="A15" s="87"/>
-      <c r="B15" s="86"/>
+      <c r="A15" s="78"/>
+      <c r="B15" s="77"/>
       <c r="C15" s="22" t="s">
         <v>47</v>
       </c>
@@ -9715,8 +9742,8 @@
       <c r="AN15" s="29"/>
     </row>
     <row r="16" spans="1:40" ht="18" customHeight="1">
-      <c r="A16" s="87"/>
-      <c r="B16" s="86"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="22" t="s">
         <v>48</v>
       </c>
@@ -9768,8 +9795,8 @@
       <c r="AN16" s="29"/>
     </row>
     <row r="17" spans="1:40" ht="18" customHeight="1">
-      <c r="A17" s="87"/>
-      <c r="B17" s="86"/>
+      <c r="A17" s="78"/>
+      <c r="B17" s="77"/>
       <c r="C17" s="22" t="s">
         <v>49</v>
       </c>
@@ -9821,8 +9848,8 @@
       <c r="AN17" s="29"/>
     </row>
     <row r="18" spans="1:40" ht="18" customHeight="1">
-      <c r="A18" s="87"/>
-      <c r="B18" s="86"/>
+      <c r="A18" s="78"/>
+      <c r="B18" s="77"/>
       <c r="C18" s="22" t="s">
         <v>50</v>
       </c>
@@ -9943,38 +9970,38 @@
       <c r="C20" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="84"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="76"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="73"/>
       <c r="N20" s="103"/>
-      <c r="O20" s="76"/>
-      <c r="P20" s="84"/>
-      <c r="Q20" s="76"/>
-      <c r="R20" s="84"/>
-      <c r="S20" s="76"/>
-      <c r="T20" s="84"/>
-      <c r="U20" s="76"/>
-      <c r="V20" s="84"/>
-      <c r="W20" s="76"/>
-      <c r="X20" s="84"/>
-      <c r="Y20" s="76"/>
-      <c r="Z20" s="84"/>
-      <c r="AA20" s="76"/>
-      <c r="AB20" s="84"/>
-      <c r="AC20" s="76"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="74"/>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="74"/>
+      <c r="S20" s="73"/>
+      <c r="T20" s="74"/>
+      <c r="U20" s="73"/>
+      <c r="V20" s="74"/>
+      <c r="W20" s="73"/>
+      <c r="X20" s="74"/>
+      <c r="Y20" s="73"/>
+      <c r="Z20" s="74"/>
+      <c r="AA20" s="73"/>
+      <c r="AB20" s="74"/>
+      <c r="AC20" s="73"/>
       <c r="AD20" s="66"/>
-      <c r="AE20" s="84">
+      <c r="AE20" s="74">
         <f>D20+F20+H20+J20+L20+N20+P20+R20+T20+V20+X20+Z20+AB20</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="76"/>
+      <c r="AF20" s="73"/>
       <c r="AG20" s="35"/>
       <c r="AH20" s="35">
         <f>AH12+AE20-(D55)</f>
@@ -10000,8 +10027,8 @@
       <c r="AN20" s="41"/>
     </row>
     <row r="21" spans="1:40" ht="18" customHeight="1">
-      <c r="A21" s="72"/>
-      <c r="B21" s="73"/>
+      <c r="A21" s="87"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="42" t="s">
         <v>20</v>
       </c>
@@ -10134,10 +10161,10 @@
       <c r="AN21" s="47"/>
     </row>
     <row r="22" spans="1:40" ht="18" customHeight="1">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="86"/>
+      <c r="B22" s="77"/>
       <c r="C22" s="22" t="s">
         <v>46</v>
       </c>
@@ -10201,8 +10228,8 @@
       <c r="AN22" s="29"/>
     </row>
     <row r="23" spans="1:40" ht="18" customHeight="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="86"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="77"/>
       <c r="C23" s="22" t="s">
         <v>47</v>
       </c>
@@ -10254,8 +10281,8 @@
       <c r="AN23" s="29"/>
     </row>
     <row r="24" spans="1:40" ht="18" customHeight="1">
-      <c r="A24" s="87"/>
-      <c r="B24" s="86"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="77"/>
       <c r="C24" s="22" t="s">
         <v>48</v>
       </c>
@@ -10307,8 +10334,8 @@
       <c r="AN24" s="29"/>
     </row>
     <row r="25" spans="1:40" ht="18" customHeight="1">
-      <c r="A25" s="87"/>
-      <c r="B25" s="86"/>
+      <c r="A25" s="78"/>
+      <c r="B25" s="77"/>
       <c r="C25" s="22" t="s">
         <v>49</v>
       </c>
@@ -10360,8 +10387,8 @@
       <c r="AN25" s="29"/>
     </row>
     <row r="26" spans="1:40" ht="18" customHeight="1">
-      <c r="A26" s="87"/>
-      <c r="B26" s="86"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="77"/>
       <c r="C26" s="22" t="s">
         <v>50</v>
       </c>
@@ -10482,38 +10509,38 @@
       <c r="C28" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="84"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="84"/>
-      <c r="M28" s="76"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="73"/>
       <c r="N28" s="103"/>
-      <c r="O28" s="76"/>
-      <c r="P28" s="84"/>
-      <c r="Q28" s="76"/>
-      <c r="R28" s="84"/>
-      <c r="S28" s="76"/>
-      <c r="T28" s="84"/>
-      <c r="U28" s="76"/>
-      <c r="V28" s="84"/>
-      <c r="W28" s="76"/>
-      <c r="X28" s="84"/>
-      <c r="Y28" s="76"/>
-      <c r="Z28" s="84"/>
-      <c r="AA28" s="76"/>
-      <c r="AB28" s="84"/>
-      <c r="AC28" s="76"/>
+      <c r="O28" s="73"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="73"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="73"/>
+      <c r="T28" s="74"/>
+      <c r="U28" s="73"/>
+      <c r="V28" s="74"/>
+      <c r="W28" s="73"/>
+      <c r="X28" s="74"/>
+      <c r="Y28" s="73"/>
+      <c r="Z28" s="74"/>
+      <c r="AA28" s="73"/>
+      <c r="AB28" s="74"/>
+      <c r="AC28" s="73"/>
       <c r="AD28" s="66"/>
-      <c r="AE28" s="84">
+      <c r="AE28" s="74">
         <f>D28+F28+H28+J28+L28+N28+P28+R28+T28+V28+X28+Z28+AB28</f>
         <v>0</v>
       </c>
-      <c r="AF28" s="76"/>
+      <c r="AF28" s="73"/>
       <c r="AG28" s="35"/>
       <c r="AH28" s="35">
         <f>AH20+AE28-(F55)</f>
@@ -10539,8 +10566,8 @@
       <c r="AN28" s="41"/>
     </row>
     <row r="29" spans="1:40" ht="18" customHeight="1">
-      <c r="A29" s="72"/>
-      <c r="B29" s="73"/>
+      <c r="A29" s="87"/>
+      <c r="B29" s="88"/>
       <c r="C29" s="42" t="s">
         <v>20</v>
       </c>
@@ -10673,10 +10700,10 @@
       <c r="AN29" s="47"/>
     </row>
     <row r="30" spans="1:40" ht="18" customHeight="1">
-      <c r="A30" s="85" t="s">
+      <c r="A30" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="86"/>
+      <c r="B30" s="77"/>
       <c r="C30" s="22" t="s">
         <v>46</v>
       </c>
@@ -10740,8 +10767,8 @@
       <c r="AN30" s="29"/>
     </row>
     <row r="31" spans="1:40" ht="18" customHeight="1">
-      <c r="A31" s="87"/>
-      <c r="B31" s="86"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="22" t="s">
         <v>47</v>
       </c>
@@ -10793,8 +10820,8 @@
       <c r="AN31" s="29"/>
     </row>
     <row r="32" spans="1:40" ht="18" customHeight="1">
-      <c r="A32" s="87"/>
-      <c r="B32" s="86"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="77"/>
       <c r="C32" s="22" t="s">
         <v>48</v>
       </c>
@@ -10846,8 +10873,8 @@
       <c r="AN32" s="29"/>
     </row>
     <row r="33" spans="1:40" ht="18" customHeight="1">
-      <c r="A33" s="87"/>
-      <c r="B33" s="86"/>
+      <c r="A33" s="78"/>
+      <c r="B33" s="77"/>
       <c r="C33" s="22" t="s">
         <v>49</v>
       </c>
@@ -10899,8 +10926,8 @@
       <c r="AN33" s="29"/>
     </row>
     <row r="34" spans="1:40" ht="18" customHeight="1">
-      <c r="A34" s="87"/>
-      <c r="B34" s="86"/>
+      <c r="A34" s="78"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="22" t="s">
         <v>50</v>
       </c>
@@ -11021,38 +11048,38 @@
       <c r="C36" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="84"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="84"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="84"/>
-      <c r="K36" s="76"/>
-      <c r="L36" s="84"/>
-      <c r="M36" s="76"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="74"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="74"/>
+      <c r="M36" s="73"/>
       <c r="N36" s="103"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="84"/>
-      <c r="Q36" s="76"/>
-      <c r="R36" s="84"/>
-      <c r="S36" s="76"/>
-      <c r="T36" s="84"/>
-      <c r="U36" s="76"/>
-      <c r="V36" s="84"/>
-      <c r="W36" s="76"/>
-      <c r="X36" s="84"/>
-      <c r="Y36" s="76"/>
-      <c r="Z36" s="84"/>
-      <c r="AA36" s="76"/>
-      <c r="AB36" s="84"/>
-      <c r="AC36" s="76"/>
+      <c r="O36" s="73"/>
+      <c r="P36" s="74"/>
+      <c r="Q36" s="73"/>
+      <c r="R36" s="74"/>
+      <c r="S36" s="73"/>
+      <c r="T36" s="74"/>
+      <c r="U36" s="73"/>
+      <c r="V36" s="74"/>
+      <c r="W36" s="73"/>
+      <c r="X36" s="74"/>
+      <c r="Y36" s="73"/>
+      <c r="Z36" s="74"/>
+      <c r="AA36" s="73"/>
+      <c r="AB36" s="74"/>
+      <c r="AC36" s="73"/>
       <c r="AD36" s="66"/>
-      <c r="AE36" s="84">
+      <c r="AE36" s="74">
         <f>D36+F36+H36+J36+L36+N36+P36+R36+T36+V36+X36+Z36+AB36</f>
         <v>0</v>
       </c>
-      <c r="AF36" s="76"/>
+      <c r="AF36" s="73"/>
       <c r="AG36" s="35"/>
       <c r="AH36" s="35">
         <f>AH28+AE36-(H55)</f>
@@ -11078,8 +11105,8 @@
       <c r="AN36" s="41"/>
     </row>
     <row r="37" spans="1:40" ht="18" customHeight="1">
-      <c r="A37" s="72"/>
-      <c r="B37" s="73"/>
+      <c r="A37" s="87"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="42" t="s">
         <v>20</v>
       </c>
@@ -11212,10 +11239,10 @@
       <c r="AN37" s="47"/>
     </row>
     <row r="38" spans="1:40" ht="18" customHeight="1">
-      <c r="A38" s="85" t="s">
+      <c r="A38" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="86"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="22" t="s">
         <v>46</v>
       </c>
@@ -11279,8 +11306,8 @@
       <c r="AN38" s="29"/>
     </row>
     <row r="39" spans="1:40" ht="18" customHeight="1">
-      <c r="A39" s="87"/>
-      <c r="B39" s="86"/>
+      <c r="A39" s="78"/>
+      <c r="B39" s="77"/>
       <c r="C39" s="22" t="s">
         <v>47</v>
       </c>
@@ -11332,8 +11359,8 @@
       <c r="AN39" s="29"/>
     </row>
     <row r="40" spans="1:40" ht="18" customHeight="1">
-      <c r="A40" s="87"/>
-      <c r="B40" s="86"/>
+      <c r="A40" s="78"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="22" t="s">
         <v>48</v>
       </c>
@@ -11385,8 +11412,8 @@
       <c r="AN40" s="29"/>
     </row>
     <row r="41" spans="1:40" ht="18" customHeight="1">
-      <c r="A41" s="87"/>
-      <c r="B41" s="86"/>
+      <c r="A41" s="78"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="22" t="s">
         <v>49</v>
       </c>
@@ -11438,8 +11465,8 @@
       <c r="AN41" s="29"/>
     </row>
     <row r="42" spans="1:40" ht="18" customHeight="1">
-      <c r="A42" s="87"/>
-      <c r="B42" s="86"/>
+      <c r="A42" s="78"/>
+      <c r="B42" s="77"/>
       <c r="C42" s="22" t="s">
         <v>50</v>
       </c>
@@ -11560,38 +11587,38 @@
       <c r="C44" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="84"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="84"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="84"/>
-      <c r="I44" s="76"/>
-      <c r="J44" s="84"/>
-      <c r="K44" s="76"/>
-      <c r="L44" s="84"/>
-      <c r="M44" s="76"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="73"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="73"/>
       <c r="N44" s="103"/>
-      <c r="O44" s="76"/>
-      <c r="P44" s="84"/>
-      <c r="Q44" s="76"/>
-      <c r="R44" s="84"/>
-      <c r="S44" s="76"/>
-      <c r="T44" s="84"/>
-      <c r="U44" s="76"/>
-      <c r="V44" s="84"/>
-      <c r="W44" s="76"/>
-      <c r="X44" s="84"/>
-      <c r="Y44" s="76"/>
-      <c r="Z44" s="84"/>
-      <c r="AA44" s="76"/>
-      <c r="AB44" s="84"/>
-      <c r="AC44" s="76"/>
+      <c r="O44" s="73"/>
+      <c r="P44" s="74"/>
+      <c r="Q44" s="73"/>
+      <c r="R44" s="74"/>
+      <c r="S44" s="73"/>
+      <c r="T44" s="74"/>
+      <c r="U44" s="73"/>
+      <c r="V44" s="74"/>
+      <c r="W44" s="73"/>
+      <c r="X44" s="74"/>
+      <c r="Y44" s="73"/>
+      <c r="Z44" s="74"/>
+      <c r="AA44" s="73"/>
+      <c r="AB44" s="74"/>
+      <c r="AC44" s="73"/>
       <c r="AD44" s="66"/>
-      <c r="AE44" s="84">
+      <c r="AE44" s="74">
         <f>D44+F44+H44+J44+L44+N44+P44+R44+T44+V44+X44+Z44+AB44</f>
         <v>0</v>
       </c>
-      <c r="AF44" s="76"/>
+      <c r="AF44" s="73"/>
       <c r="AG44" s="35"/>
       <c r="AH44" s="35">
         <f>AH36+AE44-(J55)</f>
@@ -11617,8 +11644,8 @@
       <c r="AN44" s="41"/>
     </row>
     <row r="45" spans="1:40" ht="18" customHeight="1">
-      <c r="A45" s="72"/>
-      <c r="B45" s="73"/>
+      <c r="A45" s="87"/>
+      <c r="B45" s="88"/>
       <c r="C45" s="42" t="s">
         <v>20</v>
       </c>
@@ -12544,77 +12571,77 @@
       <c r="C52" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="84">
+      <c r="D52" s="74">
         <f>D12+D20+D28+D36+D44</f>
         <v>0</v>
       </c>
-      <c r="E52" s="76"/>
-      <c r="F52" s="84">
+      <c r="E52" s="73"/>
+      <c r="F52" s="74">
         <f>F12+F20+F28+F36+F44</f>
         <v>0</v>
       </c>
-      <c r="G52" s="76"/>
-      <c r="H52" s="84">
+      <c r="G52" s="73"/>
+      <c r="H52" s="74">
         <f>H12+H20+H28+H36+H44</f>
         <v>0</v>
       </c>
-      <c r="I52" s="76"/>
-      <c r="J52" s="84">
+      <c r="I52" s="73"/>
+      <c r="J52" s="74">
         <f>J12+J20+J28+J36+J44</f>
         <v>0</v>
       </c>
-      <c r="K52" s="76"/>
-      <c r="L52" s="84">
+      <c r="K52" s="73"/>
+      <c r="L52" s="74">
         <f>L12+L20+L28+L36+L44</f>
         <v>0</v>
       </c>
-      <c r="M52" s="76"/>
-      <c r="N52" s="105">
+      <c r="M52" s="73"/>
+      <c r="N52" s="104">
         <f>N12+N20+N28+N36+N44</f>
         <v>0</v>
       </c>
-      <c r="O52" s="76"/>
-      <c r="P52" s="84">
+      <c r="O52" s="73"/>
+      <c r="P52" s="74">
         <f>P12+P20+P28+P36+P44</f>
         <v>0</v>
       </c>
-      <c r="Q52" s="76"/>
-      <c r="R52" s="84">
+      <c r="Q52" s="73"/>
+      <c r="R52" s="74">
         <f>R12+R20+R28+R36+R44</f>
         <v>0</v>
       </c>
-      <c r="S52" s="76"/>
-      <c r="T52" s="84">
+      <c r="S52" s="73"/>
+      <c r="T52" s="74">
         <f>T12+T20+T28+T36+T44</f>
         <v>0</v>
       </c>
-      <c r="U52" s="76"/>
-      <c r="V52" s="84">
+      <c r="U52" s="73"/>
+      <c r="V52" s="74">
         <f>V12+V20+V28+V36+V44</f>
         <v>0</v>
       </c>
-      <c r="W52" s="76"/>
-      <c r="X52" s="84">
+      <c r="W52" s="73"/>
+      <c r="X52" s="74">
         <f>X12+X20+X28+X36+X44</f>
         <v>0</v>
       </c>
-      <c r="Y52" s="76"/>
-      <c r="Z52" s="84">
+      <c r="Y52" s="73"/>
+      <c r="Z52" s="74">
         <f>Z12+Z20+Z28+Z36+Z44</f>
         <v>0</v>
       </c>
-      <c r="AA52" s="76"/>
-      <c r="AB52" s="84">
+      <c r="AA52" s="73"/>
+      <c r="AB52" s="74">
         <f>AB12+AB20+AB28+AB36+AB44</f>
         <v>0</v>
       </c>
-      <c r="AC52" s="76"/>
+      <c r="AC52" s="73"/>
       <c r="AD52" s="66"/>
-      <c r="AE52" s="84">
+      <c r="AE52" s="74">
         <f>D52+F52+H52+J52+L52+N52+P52+R52+T52+V52+X52+Z52+AB52</f>
         <v>0</v>
       </c>
-      <c r="AF52" s="76"/>
+      <c r="AF52" s="73"/>
       <c r="AG52" s="35"/>
       <c r="AH52" s="35"/>
       <c r="AI52" s="37"/>
@@ -12625,8 +12652,8 @@
       <c r="AN52" s="41"/>
     </row>
     <row r="53" spans="1:40" ht="18" customHeight="1">
-      <c r="A53" s="72"/>
-      <c r="B53" s="73"/>
+      <c r="A53" s="87"/>
+      <c r="B53" s="88"/>
       <c r="C53" s="42" t="s">
         <v>20</v>
       </c>
@@ -12756,79 +12783,79 @@
       <c r="AN53" s="56"/>
     </row>
     <row r="54" spans="1:40" ht="18" customHeight="1">
-      <c r="A54" s="77" t="s">
+      <c r="A54" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="78"/>
-      <c r="C54" s="79"/>
-      <c r="D54" s="75">
+      <c r="B54" s="98"/>
+      <c r="C54" s="99"/>
+      <c r="D54" s="72">
         <f>D46+E46*2+D47+E47*2+D48+E48*2+D49+E49*2+D50+E50*2+D51+E51*2</f>
         <v>0</v>
       </c>
-      <c r="E54" s="76"/>
-      <c r="F54" s="75">
+      <c r="E54" s="73"/>
+      <c r="F54" s="72">
         <f>F46+G46*2+F47+G47*2+F48+G48*2+F49+G49*2+F50+G50*2+F51+G51*2</f>
         <v>0</v>
       </c>
-      <c r="G54" s="76"/>
-      <c r="H54" s="75">
+      <c r="G54" s="73"/>
+      <c r="H54" s="72">
         <f>H46+I46*2+H47+I47*2+H48+I48*2+H49+I49*2+H50+I50*2+H51+I51*2</f>
         <v>0</v>
       </c>
-      <c r="I54" s="76"/>
-      <c r="J54" s="75">
+      <c r="I54" s="73"/>
+      <c r="J54" s="72">
         <f>J46+K46*2+J47+K47*2+J48+K48*2+J49+K49*2+J50+K50*2+J51+K51*2</f>
         <v>0</v>
       </c>
-      <c r="K54" s="76"/>
-      <c r="L54" s="75">
+      <c r="K54" s="73"/>
+      <c r="L54" s="72">
         <f>L46+M46*2+L47+M47*2+L48+M48*2+L49+M49*2+L50+M50*2+L51+M51*2</f>
         <v>0</v>
       </c>
-      <c r="M54" s="76"/>
-      <c r="N54" s="75">
+      <c r="M54" s="73"/>
+      <c r="N54" s="72">
         <f>N46+O46*2+N47+O47*2+N48+O48*2+N49+O49*2+N50+O50*2+N51+O51*2</f>
         <v>0</v>
       </c>
-      <c r="O54" s="76"/>
-      <c r="P54" s="75">
+      <c r="O54" s="73"/>
+      <c r="P54" s="72">
         <f>P46+Q46*2+P47+Q47*2+P48+Q48*2+P49+Q49*2+P50+Q50*2+P51+Q51*2</f>
         <v>0</v>
       </c>
-      <c r="Q54" s="76"/>
-      <c r="R54" s="75">
+      <c r="Q54" s="73"/>
+      <c r="R54" s="72">
         <f>R46+S46*2+R47+S47*2+R48+S48*2+R49+S49*2+R50+S50*2+R51+S51*2</f>
         <v>0</v>
       </c>
-      <c r="S54" s="76"/>
-      <c r="T54" s="75">
+      <c r="S54" s="73"/>
+      <c r="T54" s="72">
         <f>T46+U46*2+T47+U47*2+T48+U48*2+T49+U49*2+T50+U50*2+T51+U51*2</f>
         <v>0</v>
       </c>
-      <c r="U54" s="76"/>
-      <c r="V54" s="75">
+      <c r="U54" s="73"/>
+      <c r="V54" s="72">
         <f>V46+W46*2+V47+W47*2+V48+W48*2+V49+W49*2+V50+W50*2+V51+W51*2</f>
         <v>0</v>
       </c>
-      <c r="W54" s="76"/>
-      <c r="X54" s="75">
+      <c r="W54" s="73"/>
+      <c r="X54" s="72">
         <f>X46+Y46*2+X47+Y47*2+X48+Y48*2+X49+Y49*2+X50+Y50*2+X51+Y51*2</f>
         <v>0</v>
       </c>
-      <c r="Y54" s="76"/>
-      <c r="Z54" s="75">
+      <c r="Y54" s="73"/>
+      <c r="Z54" s="72">
         <f>Z46+AA46*2+Z47+AA47*2+Z48+AA48*2+Z49+AA49*2+Z50+AA50*2+Z51+AA51*2</f>
         <v>0</v>
       </c>
-      <c r="AA54" s="76"/>
-      <c r="AB54" s="75">
+      <c r="AA54" s="73"/>
+      <c r="AB54" s="72">
         <f>AB46+AC46*2+AB47+AC47*2+AB48+AC48*2+AB49+AC49*2+AB50+AC50*2+AB51+AC51*2</f>
         <v>0</v>
       </c>
-      <c r="AC54" s="76"/>
+      <c r="AC54" s="73"/>
       <c r="AD54" s="71"/>
-      <c r="AE54" s="75"/>
-      <c r="AF54" s="76"/>
+      <c r="AE54" s="72"/>
+      <c r="AF54" s="73"/>
       <c r="AG54" s="57"/>
       <c r="AH54" s="57"/>
       <c r="AI54" s="58"/>
@@ -12839,79 +12866,79 @@
       <c r="AN54" s="60"/>
     </row>
     <row r="55" spans="1:40" ht="18" customHeight="1">
-      <c r="A55" s="77" t="s">
+      <c r="A55" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="78"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="94">
+      <c r="B55" s="98"/>
+      <c r="C55" s="99"/>
+      <c r="D55" s="75">
         <f>D52</f>
         <v>0</v>
       </c>
-      <c r="E55" s="76"/>
-      <c r="F55" s="94">
+      <c r="E55" s="73"/>
+      <c r="F55" s="75">
         <f>F52</f>
         <v>0</v>
       </c>
-      <c r="G55" s="76"/>
-      <c r="H55" s="94">
+      <c r="G55" s="73"/>
+      <c r="H55" s="75">
         <f>H52</f>
         <v>0</v>
       </c>
-      <c r="I55" s="76"/>
-      <c r="J55" s="94">
+      <c r="I55" s="73"/>
+      <c r="J55" s="75">
         <f>J52</f>
         <v>0</v>
       </c>
-      <c r="K55" s="76"/>
-      <c r="L55" s="94">
+      <c r="K55" s="73"/>
+      <c r="L55" s="75">
         <f>L52</f>
         <v>0</v>
       </c>
-      <c r="M55" s="76"/>
-      <c r="N55" s="94">
+      <c r="M55" s="73"/>
+      <c r="N55" s="75">
         <f>N52</f>
         <v>0</v>
       </c>
-      <c r="O55" s="76"/>
-      <c r="P55" s="94">
+      <c r="O55" s="73"/>
+      <c r="P55" s="75">
         <f>P52</f>
         <v>0</v>
       </c>
-      <c r="Q55" s="76"/>
-      <c r="R55" s="94">
+      <c r="Q55" s="73"/>
+      <c r="R55" s="75">
         <f>R52</f>
         <v>0</v>
       </c>
-      <c r="S55" s="76"/>
-      <c r="T55" s="94">
+      <c r="S55" s="73"/>
+      <c r="T55" s="75">
         <f>T52</f>
         <v>0</v>
       </c>
-      <c r="U55" s="76"/>
-      <c r="V55" s="94">
+      <c r="U55" s="73"/>
+      <c r="V55" s="75">
         <f>V52</f>
         <v>0</v>
       </c>
-      <c r="W55" s="76"/>
-      <c r="X55" s="94">
+      <c r="W55" s="73"/>
+      <c r="X55" s="75">
         <f>X52</f>
         <v>0</v>
       </c>
-      <c r="Y55" s="76"/>
-      <c r="Z55" s="94">
+      <c r="Y55" s="73"/>
+      <c r="Z55" s="75">
         <f>Z52</f>
         <v>0</v>
       </c>
-      <c r="AA55" s="76"/>
-      <c r="AB55" s="94">
+      <c r="AA55" s="73"/>
+      <c r="AB55" s="75">
         <f>AB52</f>
         <v>0</v>
       </c>
-      <c r="AC55" s="76"/>
+      <c r="AC55" s="73"/>
       <c r="AD55" s="71"/>
-      <c r="AE55" s="94"/>
-      <c r="AF55" s="76"/>
+      <c r="AE55" s="75"/>
+      <c r="AF55" s="73"/>
       <c r="AG55" s="61"/>
       <c r="AH55" s="61"/>
       <c r="AI55" s="62"/>
@@ -13006,79 +13033,79 @@
       <c r="AN57" s="67"/>
     </row>
     <row r="58" spans="1:40" ht="18" customHeight="1">
-      <c r="A58" s="77" t="s">
+      <c r="A58" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="78"/>
-      <c r="C58" s="79"/>
-      <c r="D58" s="75">
+      <c r="B58" s="98"/>
+      <c r="C58" s="99"/>
+      <c r="D58" s="72">
         <f>D53+E53+AE21+AF21</f>
         <v>0</v>
       </c>
-      <c r="E58" s="76"/>
-      <c r="F58" s="75">
+      <c r="E58" s="73"/>
+      <c r="F58" s="72">
         <f>F53+G53+AE29+AF29</f>
         <v>0</v>
       </c>
-      <c r="G58" s="76"/>
-      <c r="H58" s="75">
+      <c r="G58" s="73"/>
+      <c r="H58" s="72">
         <f>H53+I53+AE37+AF37</f>
         <v>0</v>
       </c>
-      <c r="I58" s="76"/>
-      <c r="J58" s="75">
+      <c r="I58" s="73"/>
+      <c r="J58" s="72">
         <f>J53+K53+AE45+AF45</f>
         <v>0</v>
       </c>
-      <c r="K58" s="76"/>
-      <c r="L58" s="75">
+      <c r="K58" s="73"/>
+      <c r="L58" s="72">
         <f>L53+M53+0</f>
         <v>0</v>
       </c>
-      <c r="M58" s="76"/>
-      <c r="N58" s="75">
+      <c r="M58" s="73"/>
+      <c r="N58" s="72">
         <f>N53+O53+0</f>
         <v>0</v>
       </c>
-      <c r="O58" s="76"/>
-      <c r="P58" s="75">
+      <c r="O58" s="73"/>
+      <c r="P58" s="72">
         <f>P53+Q53+0</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="76"/>
-      <c r="R58" s="75">
+      <c r="Q58" s="73"/>
+      <c r="R58" s="72">
         <f>R53+S53+0</f>
         <v>0</v>
       </c>
-      <c r="S58" s="76"/>
-      <c r="T58" s="75">
+      <c r="S58" s="73"/>
+      <c r="T58" s="72">
         <f>T53+U53+0</f>
         <v>0</v>
       </c>
-      <c r="U58" s="76"/>
-      <c r="V58" s="75">
+      <c r="U58" s="73"/>
+      <c r="V58" s="72">
         <f>V53+W53+0</f>
         <v>0</v>
       </c>
-      <c r="W58" s="76"/>
-      <c r="X58" s="75">
+      <c r="W58" s="73"/>
+      <c r="X58" s="72">
         <f>X53+Y53+0</f>
         <v>0</v>
       </c>
-      <c r="Y58" s="76"/>
-      <c r="Z58" s="75">
+      <c r="Y58" s="73"/>
+      <c r="Z58" s="72">
         <f>Z53+AA53+0</f>
         <v>0</v>
       </c>
-      <c r="AA58" s="76"/>
-      <c r="AB58" s="75">
+      <c r="AA58" s="73"/>
+      <c r="AB58" s="72">
         <f>AB53+AC53+0</f>
         <v>0</v>
       </c>
-      <c r="AC58" s="76"/>
+      <c r="AC58" s="73"/>
       <c r="AD58" s="71"/>
-      <c r="AE58" s="75"/>
-      <c r="AF58" s="76"/>
+      <c r="AE58" s="72"/>
+      <c r="AF58" s="73"/>
       <c r="AG58" s="57"/>
       <c r="AH58" s="57"/>
       <c r="AI58" s="58"/>
@@ -13089,79 +13116,79 @@
       <c r="AN58" s="60"/>
     </row>
     <row r="59" spans="1:40" ht="18" customHeight="1">
-      <c r="A59" s="77" t="s">
+      <c r="A59" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="78"/>
-      <c r="C59" s="79"/>
-      <c r="D59" s="75">
+      <c r="B59" s="98"/>
+      <c r="C59" s="99"/>
+      <c r="D59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,D3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,D3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="E59" s="76"/>
-      <c r="F59" s="75">
+      <c r="E59" s="73"/>
+      <c r="F59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,F3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,F3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="G59" s="76"/>
-      <c r="H59" s="75">
+      <c r="G59" s="73"/>
+      <c r="H59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,H3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,H3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="I59" s="76"/>
-      <c r="J59" s="75">
+      <c r="I59" s="73"/>
+      <c r="J59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,J3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,J3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="K59" s="76"/>
-      <c r="L59" s="75">
+      <c r="K59" s="73"/>
+      <c r="L59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,L3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,L3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="M59" s="76"/>
-      <c r="N59" s="75">
+      <c r="M59" s="73"/>
+      <c r="N59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,N3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,N3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="O59" s="76"/>
-      <c r="P59" s="75">
+      <c r="O59" s="73"/>
+      <c r="P59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,P3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,P3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="76"/>
-      <c r="R59" s="75">
+      <c r="Q59" s="73"/>
+      <c r="R59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,R3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,R3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="S59" s="76"/>
-      <c r="T59" s="75">
+      <c r="S59" s="73"/>
+      <c r="T59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,T3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,T3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="U59" s="76"/>
-      <c r="V59" s="75">
+      <c r="U59" s="73"/>
+      <c r="V59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,V3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,V3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="W59" s="76"/>
-      <c r="X59" s="75">
+      <c r="W59" s="73"/>
+      <c r="X59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,X3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,X3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="Y59" s="76"/>
-      <c r="Z59" s="75">
+      <c r="Y59" s="73"/>
+      <c r="Z59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,Z3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,Z3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="AA59" s="76"/>
-      <c r="AB59" s="75">
+      <c r="AA59" s="73"/>
+      <c r="AB59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,AB3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,AB3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="AC59" s="76"/>
+      <c r="AC59" s="73"/>
       <c r="AD59" s="71"/>
-      <c r="AE59" s="75"/>
-      <c r="AF59" s="76"/>
+      <c r="AE59" s="72"/>
+      <c r="AF59" s="73"/>
       <c r="AG59" s="57"/>
       <c r="AH59" s="57"/>
       <c r="AI59" s="58"/>
@@ -13172,40 +13199,40 @@
       <c r="AN59" s="60"/>
     </row>
     <row r="60" spans="1:40" ht="18" customHeight="1">
-      <c r="A60" s="77" t="s">
+      <c r="A60" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="78"/>
-      <c r="C60" s="79"/>
-      <c r="D60" s="75"/>
-      <c r="E60" s="76"/>
-      <c r="F60" s="75"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="75"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="75"/>
-      <c r="K60" s="76"/>
-      <c r="L60" s="75"/>
-      <c r="M60" s="76"/>
-      <c r="N60" s="75"/>
-      <c r="O60" s="76"/>
-      <c r="P60" s="75"/>
-      <c r="Q60" s="76"/>
-      <c r="R60" s="75"/>
-      <c r="S60" s="76"/>
-      <c r="T60" s="75"/>
-      <c r="U60" s="76"/>
-      <c r="V60" s="75"/>
-      <c r="W60" s="76"/>
-      <c r="X60" s="75"/>
-      <c r="Y60" s="76"/>
-      <c r="Z60" s="75"/>
-      <c r="AA60" s="76"/>
-      <c r="AB60" s="75"/>
-      <c r="AC60" s="76"/>
+      <c r="B60" s="98"/>
+      <c r="C60" s="99"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="73"/>
+      <c r="F60" s="72"/>
+      <c r="G60" s="73"/>
+      <c r="H60" s="72"/>
+      <c r="I60" s="73"/>
+      <c r="J60" s="72"/>
+      <c r="K60" s="73"/>
+      <c r="L60" s="72"/>
+      <c r="M60" s="73"/>
+      <c r="N60" s="72"/>
+      <c r="O60" s="73"/>
+      <c r="P60" s="72"/>
+      <c r="Q60" s="73"/>
+      <c r="R60" s="72"/>
+      <c r="S60" s="73"/>
+      <c r="T60" s="72"/>
+      <c r="U60" s="73"/>
+      <c r="V60" s="72"/>
+      <c r="W60" s="73"/>
+      <c r="X60" s="72"/>
+      <c r="Y60" s="73"/>
+      <c r="Z60" s="72"/>
+      <c r="AA60" s="73"/>
+      <c r="AB60" s="72"/>
+      <c r="AC60" s="73"/>
       <c r="AD60" s="71"/>
-      <c r="AE60" s="75"/>
-      <c r="AF60" s="76"/>
+      <c r="AE60" s="72"/>
+      <c r="AF60" s="73"/>
       <c r="AG60" s="57"/>
       <c r="AH60" s="57"/>
       <c r="AI60" s="58"/>
@@ -13216,79 +13243,79 @@
       <c r="AN60" s="60"/>
     </row>
     <row r="61" spans="1:40" ht="18" customHeight="1">
-      <c r="A61" s="72" t="s">
+      <c r="A61" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="73"/>
-      <c r="C61" s="74"/>
-      <c r="D61" s="82">
+      <c r="B61" s="88"/>
+      <c r="C61" s="102"/>
+      <c r="D61" s="85">
         <f>D60-D59</f>
         <v>0</v>
       </c>
-      <c r="E61" s="83"/>
-      <c r="F61" s="82">
+      <c r="E61" s="86"/>
+      <c r="F61" s="85">
         <f>F60-F59</f>
         <v>0</v>
       </c>
-      <c r="G61" s="83"/>
-      <c r="H61" s="82">
+      <c r="G61" s="86"/>
+      <c r="H61" s="85">
         <f>H60-H59</f>
         <v>0</v>
       </c>
-      <c r="I61" s="83"/>
-      <c r="J61" s="82">
+      <c r="I61" s="86"/>
+      <c r="J61" s="85">
         <f>J60-J59</f>
         <v>0</v>
       </c>
-      <c r="K61" s="83"/>
-      <c r="L61" s="82">
+      <c r="K61" s="86"/>
+      <c r="L61" s="85">
         <f>L60-L59</f>
         <v>0</v>
       </c>
-      <c r="M61" s="83"/>
-      <c r="N61" s="82">
+      <c r="M61" s="86"/>
+      <c r="N61" s="85">
         <f>N60-N59</f>
         <v>0</v>
       </c>
-      <c r="O61" s="83"/>
-      <c r="P61" s="82">
+      <c r="O61" s="86"/>
+      <c r="P61" s="85">
         <f>P60-P59</f>
         <v>0</v>
       </c>
-      <c r="Q61" s="83"/>
-      <c r="R61" s="82">
+      <c r="Q61" s="86"/>
+      <c r="R61" s="85">
         <f>R60-R59</f>
         <v>0</v>
       </c>
-      <c r="S61" s="83"/>
-      <c r="T61" s="82">
+      <c r="S61" s="86"/>
+      <c r="T61" s="85">
         <f>T60-T59</f>
         <v>0</v>
       </c>
-      <c r="U61" s="83"/>
-      <c r="V61" s="82">
+      <c r="U61" s="86"/>
+      <c r="V61" s="85">
         <f>V60-V59</f>
         <v>0</v>
       </c>
-      <c r="W61" s="83"/>
-      <c r="X61" s="82">
+      <c r="W61" s="86"/>
+      <c r="X61" s="85">
         <f>X60-X59</f>
         <v>0</v>
       </c>
-      <c r="Y61" s="83"/>
-      <c r="Z61" s="82">
+      <c r="Y61" s="86"/>
+      <c r="Z61" s="85">
         <f>Z60-Z59</f>
         <v>0</v>
       </c>
-      <c r="AA61" s="83"/>
-      <c r="AB61" s="82">
+      <c r="AA61" s="86"/>
+      <c r="AB61" s="85">
         <f>AB60-AB59</f>
         <v>0</v>
       </c>
-      <c r="AC61" s="83"/>
+      <c r="AC61" s="86"/>
       <c r="AD61" s="54"/>
-      <c r="AE61" s="82"/>
-      <c r="AF61" s="83"/>
+      <c r="AE61" s="85"/>
+      <c r="AF61" s="86"/>
       <c r="AG61" s="52"/>
       <c r="AH61" s="52"/>
       <c r="AI61" s="53"/>
@@ -13300,42 +13327,167 @@
     </row>
   </sheetData>
   <mergeCells count="228">
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="AB58:AC58"/>
-    <mergeCell ref="AE54:AF54"/>
-    <mergeCell ref="V58:W58"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="AE20:AF20"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="AB44:AC44"/>
-    <mergeCell ref="AB59:AC59"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A38:B42"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="AB54:AC54"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="AB20:AC20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="AE55:AF55"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="AE44:AF44"/>
+    <mergeCell ref="X55:Y55"/>
+    <mergeCell ref="V60:W60"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="AE28:AF28"/>
+    <mergeCell ref="V54:W54"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="X61:Y61"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="Z61:AA61"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="Z58:AA58"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="Z44:AA44"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="AB28:AC28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="V55:W55"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="A22:B26"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="AE52:AF52"/>
+    <mergeCell ref="A6:B10"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AE1:AN1"/>
+    <mergeCell ref="H1:AC1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="X58:Y58"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="AB52:AC52"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="A14:B18"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="AE36:AF36"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="AE59:AF59"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="AB36:AC36"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="AB61:AC61"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="AB12:AC12"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="Z60:AA60"/>
+    <mergeCell ref="X60:Y60"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="J61:K61"/>
     <mergeCell ref="D61:E61"/>
     <mergeCell ref="T44:U44"/>
     <mergeCell ref="V44:W44"/>
@@ -13360,183 +13512,61 @@
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="N54:O54"/>
     <mergeCell ref="Z54:AA54"/>
-    <mergeCell ref="AB61:AC61"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="AE60:AF60"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="AB12:AC12"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="Z60:AA60"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="AE36:AF36"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="AE59:AF59"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="AB36:AC36"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="H1:AC1"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="X58:Y58"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="AB52:AC52"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="A14:B18"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="T54:U54"/>
-    <mergeCell ref="A22:B26"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="AE52:AF52"/>
-    <mergeCell ref="A6:B10"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="Z36:AA36"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="AE61:AF61"/>
-    <mergeCell ref="Z58:AA58"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="Z44:AA44"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="AB28:AC28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="V55:W55"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="AE44:AF44"/>
-    <mergeCell ref="X55:Y55"/>
-    <mergeCell ref="V60:W60"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="AE28:AF28"/>
-    <mergeCell ref="V54:W54"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="X61:Y61"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="Z61:AA61"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AE58:AF58"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="AE55:AF55"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="T59:U59"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F52:G52"/>
     <mergeCell ref="A30:B34"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="AB60:AC60"/>
     <mergeCell ref="V20:W20"/>
-    <mergeCell ref="N12:O12"/>
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="AB44:AC44"/>
+    <mergeCell ref="AB59:AC59"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A38:B42"/>
+    <mergeCell ref="AB55:AC55"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="AB54:AC54"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="AB20:AC20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="AB58:AC58"/>
+    <mergeCell ref="AE54:AF54"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="AE20:AF20"/>
+    <mergeCell ref="D58:E58"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="AJ6:AK53">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL6:AM53">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/outputs/XPBL2625WE/EXPRESS BERLIN XPBL2625WE.xlsx
+++ b/outputs/XPBL2625WE/EXPRESS BERLIN XPBL2625WE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24394\Desktop\CodeX\Space Control\outputs\XPBL2625WE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E57873-23E2-4B12-87CC-5A8AF35B9688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D636868C-46F9-448F-BF93-326D3B83B1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3312" yWindow="3312" windowWidth="23040" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -326,7 +326,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -565,6 +565,45 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -647,7 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,7 +706,7 @@
     <xf numFmtId="177" fontId="6" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -742,7 +781,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -769,7 +808,7 @@
     <xf numFmtId="177" fontId="5" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -787,7 +826,7 @@
     <xf numFmtId="177" fontId="5" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -814,43 +853,28 @@
     <xf numFmtId="177" fontId="4" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -859,19 +883,25 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -901,13 +931,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -937,23 +961,20 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1257,60 +1278,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A1" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="89" t="s">
+      <c r="A1" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
       <c r="Z1" s="1"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="82"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="79"/>
     </row>
     <row r="2" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="79" t="s">
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -1329,10 +1350,10 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
-      <c r="AA2" s="79" t="s">
+      <c r="AA2" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="80"/>
+      <c r="AB2" s="77"/>
       <c r="AC2" s="5">
         <v>0</v>
       </c>
@@ -1353,147 +1374,147 @@
       <c r="AJ2" s="7"/>
     </row>
     <row r="3" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="92" t="s">
+      <c r="B3" s="78"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="92" t="s">
+      <c r="E3" s="78"/>
+      <c r="F3" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="81"/>
-      <c r="H3" s="92" t="s">
+      <c r="G3" s="78"/>
+      <c r="H3" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="81"/>
-      <c r="J3" s="92" t="s">
+      <c r="I3" s="78"/>
+      <c r="J3" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="81"/>
-      <c r="L3" s="92" t="s">
+      <c r="K3" s="78"/>
+      <c r="L3" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="81"/>
-      <c r="N3" s="92" t="s">
+      <c r="M3" s="78"/>
+      <c r="N3" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="81"/>
-      <c r="P3" s="92" t="s">
+      <c r="O3" s="78"/>
+      <c r="P3" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="92" t="s">
+      <c r="Q3" s="78"/>
+      <c r="R3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="81"/>
-      <c r="T3" s="92" t="s">
+      <c r="S3" s="78"/>
+      <c r="T3" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="81"/>
-      <c r="V3" s="92" t="s">
+      <c r="U3" s="78"/>
+      <c r="V3" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="81"/>
-      <c r="X3" s="92" t="s">
+      <c r="W3" s="78"/>
+      <c r="X3" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="Y3" s="81"/>
+      <c r="Y3" s="78"/>
       <c r="Z3" s="1"/>
-      <c r="AA3" s="92" t="s">
+      <c r="AA3" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="AB3" s="81"/>
+      <c r="AB3" s="78"/>
       <c r="AC3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AD3" s="92" t="s">
+      <c r="AD3" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="92" t="s">
+      <c r="AE3" s="78"/>
+      <c r="AF3" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="92" t="s">
+      <c r="AG3" s="78"/>
+      <c r="AH3" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="AI3" s="82"/>
+      <c r="AI3" s="79"/>
       <c r="AJ3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="83" t="s">
+      <c r="B4" s="81"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="83" t="s">
+      <c r="E4" s="81"/>
+      <c r="F4" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="83" t="s">
+      <c r="G4" s="81"/>
+      <c r="H4" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="84"/>
-      <c r="J4" s="83" t="s">
+      <c r="I4" s="81"/>
+      <c r="J4" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="84"/>
-      <c r="L4" s="83" t="s">
+      <c r="K4" s="81"/>
+      <c r="L4" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="84"/>
-      <c r="N4" s="83" t="s">
+      <c r="M4" s="81"/>
+      <c r="N4" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="84"/>
-      <c r="P4" s="100" t="s">
+      <c r="O4" s="81"/>
+      <c r="P4" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" s="84"/>
-      <c r="R4" s="83" t="s">
+      <c r="Q4" s="81"/>
+      <c r="R4" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="S4" s="84"/>
-      <c r="T4" s="83" t="s">
+      <c r="S4" s="81"/>
+      <c r="T4" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="U4" s="84"/>
-      <c r="V4" s="83" t="s">
+      <c r="U4" s="81"/>
+      <c r="V4" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="W4" s="84"/>
-      <c r="X4" s="83" t="s">
+      <c r="W4" s="81"/>
+      <c r="X4" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="Y4" s="84"/>
+      <c r="Y4" s="81"/>
       <c r="Z4" s="12"/>
-      <c r="AA4" s="90"/>
-      <c r="AB4" s="84"/>
+      <c r="AA4" s="85"/>
+      <c r="AB4" s="81"/>
       <c r="AC4" s="13"/>
-      <c r="AD4" s="90"/>
-      <c r="AE4" s="84"/>
-      <c r="AF4" s="90"/>
-      <c r="AG4" s="84"/>
-      <c r="AH4" s="90"/>
-      <c r="AI4" s="91"/>
+      <c r="AD4" s="85"/>
+      <c r="AE4" s="81"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="81"/>
+      <c r="AH4" s="85"/>
+      <c r="AI4" s="86"/>
       <c r="AJ4" s="14"/>
     </row>
     <row r="5" spans="1:36" ht="19.95" customHeight="1">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="96"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="91"/>
       <c r="D5" s="15" t="s">
         <v>38</v>
       </c>
@@ -1591,10 +1612,10 @@
       <c r="AJ5" s="19"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="77"/>
+      <c r="B6" s="74"/>
       <c r="C6" s="22" t="s">
         <v>46</v>
       </c>
@@ -1654,8 +1675,8 @@
       <c r="AJ6" s="29"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="78"/>
-      <c r="B7" s="77"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="74"/>
       <c r="C7" s="22" t="s">
         <v>47</v>
       </c>
@@ -1703,8 +1724,8 @@
       <c r="AJ7" s="29"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="78"/>
-      <c r="B8" s="77"/>
+      <c r="A8" s="75"/>
+      <c r="B8" s="74"/>
       <c r="C8" s="22" t="s">
         <v>48</v>
       </c>
@@ -1752,8 +1773,8 @@
       <c r="AJ8" s="29"/>
     </row>
     <row r="9" spans="1:36" ht="18" customHeight="1">
-      <c r="A9" s="78"/>
-      <c r="B9" s="77"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="74"/>
       <c r="C9" s="22" t="s">
         <v>49</v>
       </c>
@@ -1801,8 +1822,8 @@
       <c r="AJ9" s="29"/>
     </row>
     <row r="10" spans="1:36" ht="18" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="77"/>
+      <c r="A10" s="75"/>
+      <c r="B10" s="74"/>
       <c r="C10" s="22" t="s">
         <v>50</v>
       </c>
@@ -1907,34 +1928,34 @@
       <c r="C12" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="73"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="73"/>
-      <c r="R12" s="74"/>
-      <c r="S12" s="73"/>
-      <c r="T12" s="74"/>
-      <c r="U12" s="73"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="73"/>
-      <c r="X12" s="74"/>
-      <c r="Y12" s="73"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="69"/>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="68"/>
+      <c r="W12" s="69"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="69"/>
       <c r="Z12" s="36"/>
-      <c r="AA12" s="74">
+      <c r="AA12" s="68">
         <f>D12+F12+H12+J12+L12+N12+P12+R12+T12+V12+X12</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="73"/>
+      <c r="AB12" s="69"/>
       <c r="AC12" s="35"/>
       <c r="AD12" s="35">
         <f>0+AA12-(0)</f>
@@ -1960,8 +1981,8 @@
       <c r="AJ12" s="41"/>
     </row>
     <row r="13" spans="1:36" ht="18" customHeight="1">
-      <c r="A13" s="87"/>
-      <c r="B13" s="88"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="83"/>
       <c r="C13" s="42" t="s">
         <v>20</v>
       </c>
@@ -2078,10 +2099,10 @@
       <c r="AJ13" s="47"/>
     </row>
     <row r="14" spans="1:36" ht="18" customHeight="1">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="77"/>
+      <c r="B14" s="74"/>
       <c r="C14" s="22" t="s">
         <v>46</v>
       </c>
@@ -2141,8 +2162,8 @@
       <c r="AJ14" s="29"/>
     </row>
     <row r="15" spans="1:36" ht="18" customHeight="1">
-      <c r="A15" s="78"/>
-      <c r="B15" s="77"/>
+      <c r="A15" s="75"/>
+      <c r="B15" s="74"/>
       <c r="C15" s="22" t="s">
         <v>47</v>
       </c>
@@ -2190,8 +2211,8 @@
       <c r="AJ15" s="29"/>
     </row>
     <row r="16" spans="1:36" ht="18" customHeight="1">
-      <c r="A16" s="78"/>
-      <c r="B16" s="77"/>
+      <c r="A16" s="75"/>
+      <c r="B16" s="74"/>
       <c r="C16" s="22" t="s">
         <v>48</v>
       </c>
@@ -2239,8 +2260,8 @@
       <c r="AJ16" s="29"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="78"/>
-      <c r="B17" s="77"/>
+      <c r="A17" s="75"/>
+      <c r="B17" s="74"/>
       <c r="C17" s="22" t="s">
         <v>49</v>
       </c>
@@ -2288,8 +2309,8 @@
       <c r="AJ17" s="29"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="78"/>
-      <c r="B18" s="77"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="74"/>
       <c r="C18" s="22" t="s">
         <v>50</v>
       </c>
@@ -2402,34 +2423,34 @@
       <c r="C20" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="73"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="73"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="73"/>
-      <c r="P20" s="74"/>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="74"/>
-      <c r="S20" s="73"/>
-      <c r="T20" s="74"/>
-      <c r="U20" s="73"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="73"/>
-      <c r="X20" s="74"/>
-      <c r="Y20" s="73"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="68"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="68"/>
+      <c r="W20" s="69"/>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="69"/>
       <c r="Z20" s="36"/>
-      <c r="AA20" s="74">
+      <c r="AA20" s="68">
         <f>D20+F20+H20+J20+L20+N20+P20+R20+T20+V20+X20</f>
         <v>0</v>
       </c>
-      <c r="AB20" s="73"/>
+      <c r="AB20" s="69"/>
       <c r="AC20" s="35"/>
       <c r="AD20" s="35">
         <f>AD12+AA20-(D103)</f>
@@ -2455,8 +2476,8 @@
       <c r="AJ20" s="41"/>
     </row>
     <row r="21" spans="1:36" ht="18" customHeight="1">
-      <c r="A21" s="87"/>
-      <c r="B21" s="88"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="83"/>
       <c r="C21" s="42" t="s">
         <v>20</v>
       </c>
@@ -2573,10 +2594,10 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="18" customHeight="1">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="77"/>
+      <c r="B22" s="74"/>
       <c r="C22" s="22" t="s">
         <v>46</v>
       </c>
@@ -2636,8 +2657,8 @@
       <c r="AJ22" s="29"/>
     </row>
     <row r="23" spans="1:36" ht="18" customHeight="1">
-      <c r="A23" s="78"/>
-      <c r="B23" s="77"/>
+      <c r="A23" s="75"/>
+      <c r="B23" s="74"/>
       <c r="C23" s="22" t="s">
         <v>47</v>
       </c>
@@ -2685,8 +2706,8 @@
       <c r="AJ23" s="29"/>
     </row>
     <row r="24" spans="1:36" ht="18" customHeight="1">
-      <c r="A24" s="78"/>
-      <c r="B24" s="77"/>
+      <c r="A24" s="75"/>
+      <c r="B24" s="74"/>
       <c r="C24" s="22" t="s">
         <v>48</v>
       </c>
@@ -2734,8 +2755,8 @@
       <c r="AJ24" s="29"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="78"/>
-      <c r="B25" s="77"/>
+      <c r="A25" s="75"/>
+      <c r="B25" s="74"/>
       <c r="C25" s="22" t="s">
         <v>49</v>
       </c>
@@ -2783,8 +2804,8 @@
       <c r="AJ25" s="29"/>
     </row>
     <row r="26" spans="1:36" ht="18" customHeight="1">
-      <c r="A26" s="78"/>
-      <c r="B26" s="77"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="74"/>
       <c r="C26" s="22" t="s">
         <v>50</v>
       </c>
@@ -2897,34 +2918,34 @@
       <c r="C28" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="73"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="74"/>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="74"/>
-      <c r="S28" s="73"/>
-      <c r="T28" s="74"/>
-      <c r="U28" s="73"/>
-      <c r="V28" s="74"/>
-      <c r="W28" s="73"/>
-      <c r="X28" s="74"/>
-      <c r="Y28" s="73"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="69"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="69"/>
+      <c r="T28" s="68"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="68"/>
+      <c r="W28" s="69"/>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="69"/>
       <c r="Z28" s="36"/>
-      <c r="AA28" s="74">
+      <c r="AA28" s="68">
         <f>D28+F28+H28+J28+L28+N28+P28+R28+T28+V28+X28</f>
         <v>0</v>
       </c>
-      <c r="AB28" s="73"/>
+      <c r="AB28" s="69"/>
       <c r="AC28" s="35"/>
       <c r="AD28" s="35">
         <f>AD20+AA28-(F103)</f>
@@ -2950,8 +2971,8 @@
       <c r="AJ28" s="41"/>
     </row>
     <row r="29" spans="1:36" ht="18" customHeight="1">
-      <c r="A29" s="87"/>
-      <c r="B29" s="88"/>
+      <c r="A29" s="82"/>
+      <c r="B29" s="83"/>
       <c r="C29" s="42" t="s">
         <v>20</v>
       </c>
@@ -3068,10 +3089,10 @@
       <c r="AJ29" s="47"/>
     </row>
     <row r="30" spans="1:36" ht="18" customHeight="1">
-      <c r="A30" s="76" t="s">
+      <c r="A30" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="77"/>
+      <c r="B30" s="74"/>
       <c r="C30" s="22" t="s">
         <v>46</v>
       </c>
@@ -3131,8 +3152,8 @@
       <c r="AJ30" s="29"/>
     </row>
     <row r="31" spans="1:36" ht="18" customHeight="1">
-      <c r="A31" s="78"/>
-      <c r="B31" s="77"/>
+      <c r="A31" s="75"/>
+      <c r="B31" s="74"/>
       <c r="C31" s="22" t="s">
         <v>47</v>
       </c>
@@ -3180,8 +3201,8 @@
       <c r="AJ31" s="29"/>
     </row>
     <row r="32" spans="1:36" ht="18" customHeight="1">
-      <c r="A32" s="78"/>
-      <c r="B32" s="77"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="74"/>
       <c r="C32" s="22" t="s">
         <v>48</v>
       </c>
@@ -3229,8 +3250,8 @@
       <c r="AJ32" s="29"/>
     </row>
     <row r="33" spans="1:36" ht="18" customHeight="1">
-      <c r="A33" s="78"/>
-      <c r="B33" s="77"/>
+      <c r="A33" s="75"/>
+      <c r="B33" s="74"/>
       <c r="C33" s="22" t="s">
         <v>49</v>
       </c>
@@ -3278,8 +3299,8 @@
       <c r="AJ33" s="29"/>
     </row>
     <row r="34" spans="1:36" ht="18" customHeight="1">
-      <c r="A34" s="78"/>
-      <c r="B34" s="77"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="74"/>
       <c r="C34" s="22" t="s">
         <v>50</v>
       </c>
@@ -3392,34 +3413,34 @@
       <c r="C36" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="74"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="74"/>
-      <c r="I36" s="73"/>
-      <c r="J36" s="74"/>
-      <c r="K36" s="73"/>
-      <c r="L36" s="74"/>
-      <c r="M36" s="73"/>
-      <c r="N36" s="74"/>
-      <c r="O36" s="73"/>
-      <c r="P36" s="74"/>
-      <c r="Q36" s="73"/>
-      <c r="R36" s="74"/>
-      <c r="S36" s="73"/>
-      <c r="T36" s="74"/>
-      <c r="U36" s="73"/>
-      <c r="V36" s="74"/>
-      <c r="W36" s="73"/>
-      <c r="X36" s="74"/>
-      <c r="Y36" s="73"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="68"/>
+      <c r="K36" s="69"/>
+      <c r="L36" s="68"/>
+      <c r="M36" s="69"/>
+      <c r="N36" s="68"/>
+      <c r="O36" s="69"/>
+      <c r="P36" s="68"/>
+      <c r="Q36" s="69"/>
+      <c r="R36" s="68"/>
+      <c r="S36" s="69"/>
+      <c r="T36" s="68"/>
+      <c r="U36" s="69"/>
+      <c r="V36" s="68"/>
+      <c r="W36" s="69"/>
+      <c r="X36" s="68"/>
+      <c r="Y36" s="69"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="74">
+      <c r="AA36" s="68">
         <f>D36+F36+H36+J36+L36+N36+P36+R36+T36+V36+X36</f>
         <v>0</v>
       </c>
-      <c r="AB36" s="73"/>
+      <c r="AB36" s="69"/>
       <c r="AC36" s="35"/>
       <c r="AD36" s="35">
         <f>AD28+AA36-(H103)</f>
@@ -3445,8 +3466,8 @@
       <c r="AJ36" s="41"/>
     </row>
     <row r="37" spans="1:36" ht="18" customHeight="1">
-      <c r="A37" s="87"/>
-      <c r="B37" s="88"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="83"/>
       <c r="C37" s="42" t="s">
         <v>20</v>
       </c>
@@ -3563,10 +3584,10 @@
       <c r="AJ37" s="47"/>
     </row>
     <row r="38" spans="1:36" ht="18" customHeight="1">
-      <c r="A38" s="76" t="s">
+      <c r="A38" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="77"/>
+      <c r="B38" s="74"/>
       <c r="C38" s="22" t="s">
         <v>46</v>
       </c>
@@ -3626,8 +3647,8 @@
       <c r="AJ38" s="29"/>
     </row>
     <row r="39" spans="1:36" ht="18" customHeight="1">
-      <c r="A39" s="78"/>
-      <c r="B39" s="77"/>
+      <c r="A39" s="75"/>
+      <c r="B39" s="74"/>
       <c r="C39" s="22" t="s">
         <v>47</v>
       </c>
@@ -3675,8 +3696,8 @@
       <c r="AJ39" s="29"/>
     </row>
     <row r="40" spans="1:36" ht="18" customHeight="1">
-      <c r="A40" s="78"/>
-      <c r="B40" s="77"/>
+      <c r="A40" s="75"/>
+      <c r="B40" s="74"/>
       <c r="C40" s="22" t="s">
         <v>48</v>
       </c>
@@ -3724,8 +3745,8 @@
       <c r="AJ40" s="29"/>
     </row>
     <row r="41" spans="1:36" ht="18" customHeight="1">
-      <c r="A41" s="78"/>
-      <c r="B41" s="77"/>
+      <c r="A41" s="75"/>
+      <c r="B41" s="74"/>
       <c r="C41" s="22" t="s">
         <v>49</v>
       </c>
@@ -3773,8 +3794,8 @@
       <c r="AJ41" s="29"/>
     </row>
     <row r="42" spans="1:36" ht="18" customHeight="1">
-      <c r="A42" s="78"/>
-      <c r="B42" s="77"/>
+      <c r="A42" s="75"/>
+      <c r="B42" s="74"/>
       <c r="C42" s="22" t="s">
         <v>50</v>
       </c>
@@ -3887,34 +3908,34 @@
       <c r="C44" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="73"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="73"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="73"/>
-      <c r="J44" s="74"/>
-      <c r="K44" s="73"/>
-      <c r="L44" s="74"/>
-      <c r="M44" s="73"/>
-      <c r="N44" s="74"/>
-      <c r="O44" s="73"/>
-      <c r="P44" s="74"/>
-      <c r="Q44" s="73"/>
-      <c r="R44" s="74"/>
-      <c r="S44" s="73"/>
-      <c r="T44" s="74"/>
-      <c r="U44" s="73"/>
-      <c r="V44" s="74"/>
-      <c r="W44" s="73"/>
-      <c r="X44" s="74"/>
-      <c r="Y44" s="73"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="68"/>
+      <c r="K44" s="69"/>
+      <c r="L44" s="68"/>
+      <c r="M44" s="69"/>
+      <c r="N44" s="68"/>
+      <c r="O44" s="69"/>
+      <c r="P44" s="68"/>
+      <c r="Q44" s="69"/>
+      <c r="R44" s="68"/>
+      <c r="S44" s="69"/>
+      <c r="T44" s="68"/>
+      <c r="U44" s="69"/>
+      <c r="V44" s="68"/>
+      <c r="W44" s="69"/>
+      <c r="X44" s="68"/>
+      <c r="Y44" s="69"/>
       <c r="Z44" s="36"/>
-      <c r="AA44" s="74">
+      <c r="AA44" s="68">
         <f>D44+F44+H44+J44+L44+N44+P44+R44+T44+V44+X44</f>
         <v>0</v>
       </c>
-      <c r="AB44" s="73"/>
+      <c r="AB44" s="69"/>
       <c r="AC44" s="35"/>
       <c r="AD44" s="35">
         <f>AD36+AA44-(J103)</f>
@@ -3940,8 +3961,8 @@
       <c r="AJ44" s="41"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
-      <c r="A45" s="87"/>
-      <c r="B45" s="88"/>
+      <c r="A45" s="82"/>
+      <c r="B45" s="83"/>
       <c r="C45" s="42" t="s">
         <v>20</v>
       </c>
@@ -4058,10 +4079,10 @@
       <c r="AJ45" s="47"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
-      <c r="A46" s="76" t="s">
+      <c r="A46" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="77"/>
+      <c r="B46" s="74"/>
       <c r="C46" s="22" t="s">
         <v>46</v>
       </c>
@@ -4121,8 +4142,8 @@
       <c r="AJ46" s="29"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
-      <c r="A47" s="78"/>
-      <c r="B47" s="77"/>
+      <c r="A47" s="75"/>
+      <c r="B47" s="74"/>
       <c r="C47" s="22" t="s">
         <v>47</v>
       </c>
@@ -4170,8 +4191,8 @@
       <c r="AJ47" s="29"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
-      <c r="A48" s="78"/>
-      <c r="B48" s="77"/>
+      <c r="A48" s="75"/>
+      <c r="B48" s="74"/>
       <c r="C48" s="22" t="s">
         <v>48</v>
       </c>
@@ -4219,8 +4240,8 @@
       <c r="AJ48" s="29"/>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
-      <c r="A49" s="78"/>
-      <c r="B49" s="77"/>
+      <c r="A49" s="75"/>
+      <c r="B49" s="74"/>
       <c r="C49" s="22" t="s">
         <v>49</v>
       </c>
@@ -4268,8 +4289,8 @@
       <c r="AJ49" s="29"/>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
-      <c r="A50" s="78"/>
-      <c r="B50" s="77"/>
+      <c r="A50" s="75"/>
+      <c r="B50" s="74"/>
       <c r="C50" s="22" t="s">
         <v>50</v>
       </c>
@@ -4382,34 +4403,34 @@
       <c r="C52" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="74"/>
-      <c r="E52" s="73"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="73"/>
-      <c r="H52" s="74"/>
-      <c r="I52" s="73"/>
-      <c r="J52" s="74"/>
-      <c r="K52" s="73"/>
-      <c r="L52" s="74"/>
-      <c r="M52" s="73"/>
-      <c r="N52" s="74"/>
-      <c r="O52" s="73"/>
-      <c r="P52" s="74"/>
-      <c r="Q52" s="73"/>
-      <c r="R52" s="74"/>
-      <c r="S52" s="73"/>
-      <c r="T52" s="74"/>
-      <c r="U52" s="73"/>
-      <c r="V52" s="74"/>
-      <c r="W52" s="73"/>
-      <c r="X52" s="74"/>
-      <c r="Y52" s="73"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="68"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="68"/>
+      <c r="K52" s="69"/>
+      <c r="L52" s="68"/>
+      <c r="M52" s="69"/>
+      <c r="N52" s="68"/>
+      <c r="O52" s="69"/>
+      <c r="P52" s="68"/>
+      <c r="Q52" s="69"/>
+      <c r="R52" s="68"/>
+      <c r="S52" s="69"/>
+      <c r="T52" s="68"/>
+      <c r="U52" s="69"/>
+      <c r="V52" s="68"/>
+      <c r="W52" s="69"/>
+      <c r="X52" s="68"/>
+      <c r="Y52" s="69"/>
       <c r="Z52" s="36"/>
-      <c r="AA52" s="74">
+      <c r="AA52" s="68">
         <f>D52+F52+H52+J52+L52+N52+P52+R52+T52+V52+X52</f>
         <v>0</v>
       </c>
-      <c r="AB52" s="73"/>
+      <c r="AB52" s="69"/>
       <c r="AC52" s="35"/>
       <c r="AD52" s="35">
         <f>AD44+AA52-(L103)</f>
@@ -4435,8 +4456,8 @@
       <c r="AJ52" s="41"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
-      <c r="A53" s="87"/>
-      <c r="B53" s="88"/>
+      <c r="A53" s="82"/>
+      <c r="B53" s="83"/>
       <c r="C53" s="42" t="s">
         <v>20</v>
       </c>
@@ -4553,10 +4574,10 @@
       <c r="AJ53" s="47"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="76" t="s">
+      <c r="A54" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="77"/>
+      <c r="B54" s="74"/>
       <c r="C54" s="22" t="s">
         <v>46</v>
       </c>
@@ -4616,8 +4637,8 @@
       <c r="AJ54" s="29"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="78"/>
-      <c r="B55" s="77"/>
+      <c r="A55" s="75"/>
+      <c r="B55" s="74"/>
       <c r="C55" s="22" t="s">
         <v>47</v>
       </c>
@@ -4665,8 +4686,8 @@
       <c r="AJ55" s="29"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="78"/>
-      <c r="B56" s="77"/>
+      <c r="A56" s="75"/>
+      <c r="B56" s="74"/>
       <c r="C56" s="22" t="s">
         <v>48</v>
       </c>
@@ -4714,8 +4735,8 @@
       <c r="AJ56" s="29"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="78"/>
-      <c r="B57" s="77"/>
+      <c r="A57" s="75"/>
+      <c r="B57" s="74"/>
       <c r="C57" s="22" t="s">
         <v>49</v>
       </c>
@@ -4763,8 +4784,8 @@
       <c r="AJ57" s="29"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
-      <c r="A58" s="78"/>
-      <c r="B58" s="77"/>
+      <c r="A58" s="75"/>
+      <c r="B58" s="74"/>
       <c r="C58" s="22" t="s">
         <v>50</v>
       </c>
@@ -4877,34 +4898,34 @@
       <c r="C60" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D60" s="74"/>
-      <c r="E60" s="73"/>
-      <c r="F60" s="74"/>
-      <c r="G60" s="73"/>
-      <c r="H60" s="74"/>
-      <c r="I60" s="73"/>
-      <c r="J60" s="74"/>
-      <c r="K60" s="73"/>
-      <c r="L60" s="74"/>
-      <c r="M60" s="73"/>
-      <c r="N60" s="74"/>
-      <c r="O60" s="73"/>
-      <c r="P60" s="74"/>
-      <c r="Q60" s="73"/>
-      <c r="R60" s="74"/>
-      <c r="S60" s="73"/>
-      <c r="T60" s="74"/>
-      <c r="U60" s="73"/>
-      <c r="V60" s="74"/>
-      <c r="W60" s="73"/>
-      <c r="X60" s="74"/>
-      <c r="Y60" s="73"/>
+      <c r="D60" s="68"/>
+      <c r="E60" s="69"/>
+      <c r="F60" s="68"/>
+      <c r="G60" s="69"/>
+      <c r="H60" s="68"/>
+      <c r="I60" s="69"/>
+      <c r="J60" s="68"/>
+      <c r="K60" s="69"/>
+      <c r="L60" s="68"/>
+      <c r="M60" s="69"/>
+      <c r="N60" s="68"/>
+      <c r="O60" s="69"/>
+      <c r="P60" s="68"/>
+      <c r="Q60" s="69"/>
+      <c r="R60" s="68"/>
+      <c r="S60" s="69"/>
+      <c r="T60" s="68"/>
+      <c r="U60" s="69"/>
+      <c r="V60" s="68"/>
+      <c r="W60" s="69"/>
+      <c r="X60" s="68"/>
+      <c r="Y60" s="69"/>
       <c r="Z60" s="36"/>
-      <c r="AA60" s="74">
+      <c r="AA60" s="68">
         <f>D60+F60+H60+J60+L60+N60+P60+R60+T60+V60+X60</f>
         <v>0</v>
       </c>
-      <c r="AB60" s="73"/>
+      <c r="AB60" s="69"/>
       <c r="AC60" s="35"/>
       <c r="AD60" s="35">
         <f>AD52+AA60-(N103)</f>
@@ -4930,8 +4951,8 @@
       <c r="AJ60" s="41"/>
     </row>
     <row r="61" spans="1:36" ht="18" customHeight="1">
-      <c r="A61" s="87"/>
-      <c r="B61" s="88"/>
+      <c r="A61" s="82"/>
+      <c r="B61" s="83"/>
       <c r="C61" s="42" t="s">
         <v>20</v>
       </c>
@@ -5048,10 +5069,10 @@
       <c r="AJ61" s="47"/>
     </row>
     <row r="62" spans="1:36" ht="18" customHeight="1">
-      <c r="A62" s="76" t="s">
+      <c r="A62" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="B62" s="77"/>
+      <c r="B62" s="74"/>
       <c r="C62" s="22" t="s">
         <v>46</v>
       </c>
@@ -5111,8 +5132,8 @@
       <c r="AJ62" s="29"/>
     </row>
     <row r="63" spans="1:36" ht="18" customHeight="1">
-      <c r="A63" s="78"/>
-      <c r="B63" s="77"/>
+      <c r="A63" s="75"/>
+      <c r="B63" s="74"/>
       <c r="C63" s="22" t="s">
         <v>47</v>
       </c>
@@ -5160,8 +5181,8 @@
       <c r="AJ63" s="29"/>
     </row>
     <row r="64" spans="1:36" ht="18" customHeight="1">
-      <c r="A64" s="78"/>
-      <c r="B64" s="77"/>
+      <c r="A64" s="75"/>
+      <c r="B64" s="74"/>
       <c r="C64" s="22" t="s">
         <v>48</v>
       </c>
@@ -5209,8 +5230,8 @@
       <c r="AJ64" s="29"/>
     </row>
     <row r="65" spans="1:36" ht="18" customHeight="1">
-      <c r="A65" s="78"/>
-      <c r="B65" s="77"/>
+      <c r="A65" s="75"/>
+      <c r="B65" s="74"/>
       <c r="C65" s="22" t="s">
         <v>49</v>
       </c>
@@ -5258,8 +5279,8 @@
       <c r="AJ65" s="29"/>
     </row>
     <row r="66" spans="1:36" ht="18" customHeight="1">
-      <c r="A66" s="78"/>
-      <c r="B66" s="77"/>
+      <c r="A66" s="75"/>
+      <c r="B66" s="74"/>
       <c r="C66" s="22" t="s">
         <v>50</v>
       </c>
@@ -5372,34 +5393,34 @@
       <c r="C68" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D68" s="74"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="74"/>
-      <c r="G68" s="73"/>
-      <c r="H68" s="74"/>
-      <c r="I68" s="73"/>
-      <c r="J68" s="74"/>
-      <c r="K68" s="73"/>
-      <c r="L68" s="74"/>
-      <c r="M68" s="73"/>
-      <c r="N68" s="74"/>
-      <c r="O68" s="73"/>
-      <c r="P68" s="74"/>
-      <c r="Q68" s="73"/>
-      <c r="R68" s="74"/>
-      <c r="S68" s="73"/>
-      <c r="T68" s="74"/>
-      <c r="U68" s="73"/>
-      <c r="V68" s="74"/>
-      <c r="W68" s="73"/>
-      <c r="X68" s="74"/>
-      <c r="Y68" s="73"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="69"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="68"/>
+      <c r="I68" s="69"/>
+      <c r="J68" s="68"/>
+      <c r="K68" s="69"/>
+      <c r="L68" s="68"/>
+      <c r="M68" s="69"/>
+      <c r="N68" s="68"/>
+      <c r="O68" s="69"/>
+      <c r="P68" s="68"/>
+      <c r="Q68" s="69"/>
+      <c r="R68" s="68"/>
+      <c r="S68" s="69"/>
+      <c r="T68" s="68"/>
+      <c r="U68" s="69"/>
+      <c r="V68" s="68"/>
+      <c r="W68" s="69"/>
+      <c r="X68" s="68"/>
+      <c r="Y68" s="69"/>
       <c r="Z68" s="36"/>
-      <c r="AA68" s="74">
+      <c r="AA68" s="68">
         <f>D68+F68+H68+J68+L68+N68+P68+R68+T68+V68+X68</f>
         <v>0</v>
       </c>
-      <c r="AB68" s="73"/>
+      <c r="AB68" s="69"/>
       <c r="AC68" s="35"/>
       <c r="AD68" s="35">
         <f>AD60+AA68-(P103)</f>
@@ -5425,8 +5446,8 @@
       <c r="AJ68" s="41"/>
     </row>
     <row r="69" spans="1:36" ht="18" customHeight="1">
-      <c r="A69" s="87"/>
-      <c r="B69" s="88"/>
+      <c r="A69" s="82"/>
+      <c r="B69" s="83"/>
       <c r="C69" s="42" t="s">
         <v>20</v>
       </c>
@@ -5543,10 +5564,10 @@
       <c r="AJ69" s="47"/>
     </row>
     <row r="70" spans="1:36" ht="18" customHeight="1">
-      <c r="A70" s="76" t="s">
+      <c r="A70" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="77"/>
+      <c r="B70" s="74"/>
       <c r="C70" s="22" t="s">
         <v>46</v>
       </c>
@@ -5606,8 +5627,8 @@
       <c r="AJ70" s="29"/>
     </row>
     <row r="71" spans="1:36" ht="18" customHeight="1">
-      <c r="A71" s="78"/>
-      <c r="B71" s="77"/>
+      <c r="A71" s="75"/>
+      <c r="B71" s="74"/>
       <c r="C71" s="22" t="s">
         <v>47</v>
       </c>
@@ -5655,8 +5676,8 @@
       <c r="AJ71" s="29"/>
     </row>
     <row r="72" spans="1:36" ht="18" customHeight="1">
-      <c r="A72" s="78"/>
-      <c r="B72" s="77"/>
+      <c r="A72" s="75"/>
+      <c r="B72" s="74"/>
       <c r="C72" s="22" t="s">
         <v>48</v>
       </c>
@@ -5704,8 +5725,8 @@
       <c r="AJ72" s="29"/>
     </row>
     <row r="73" spans="1:36" ht="18" customHeight="1">
-      <c r="A73" s="78"/>
-      <c r="B73" s="77"/>
+      <c r="A73" s="75"/>
+      <c r="B73" s="74"/>
       <c r="C73" s="22" t="s">
         <v>49</v>
       </c>
@@ -5753,8 +5774,8 @@
       <c r="AJ73" s="29"/>
     </row>
     <row r="74" spans="1:36" ht="18" customHeight="1">
-      <c r="A74" s="78"/>
-      <c r="B74" s="77"/>
+      <c r="A74" s="75"/>
+      <c r="B74" s="74"/>
       <c r="C74" s="22" t="s">
         <v>50</v>
       </c>
@@ -5867,34 +5888,34 @@
       <c r="C76" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="74"/>
-      <c r="I76" s="73"/>
-      <c r="J76" s="74"/>
-      <c r="K76" s="73"/>
-      <c r="L76" s="74"/>
-      <c r="M76" s="73"/>
-      <c r="N76" s="74"/>
-      <c r="O76" s="73"/>
-      <c r="P76" s="74"/>
-      <c r="Q76" s="73"/>
-      <c r="R76" s="74"/>
-      <c r="S76" s="73"/>
-      <c r="T76" s="74"/>
-      <c r="U76" s="73"/>
-      <c r="V76" s="74"/>
-      <c r="W76" s="73"/>
-      <c r="X76" s="74"/>
-      <c r="Y76" s="73"/>
+      <c r="D76" s="68"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="68"/>
+      <c r="G76" s="69"/>
+      <c r="H76" s="68"/>
+      <c r="I76" s="69"/>
+      <c r="J76" s="68"/>
+      <c r="K76" s="69"/>
+      <c r="L76" s="68"/>
+      <c r="M76" s="69"/>
+      <c r="N76" s="68"/>
+      <c r="O76" s="69"/>
+      <c r="P76" s="68"/>
+      <c r="Q76" s="69"/>
+      <c r="R76" s="68"/>
+      <c r="S76" s="69"/>
+      <c r="T76" s="68"/>
+      <c r="U76" s="69"/>
+      <c r="V76" s="68"/>
+      <c r="W76" s="69"/>
+      <c r="X76" s="68"/>
+      <c r="Y76" s="69"/>
       <c r="Z76" s="36"/>
-      <c r="AA76" s="74">
+      <c r="AA76" s="68">
         <f>D76+F76+H76+J76+L76+N76+P76+R76+T76+V76+X76</f>
         <v>0</v>
       </c>
-      <c r="AB76" s="73"/>
+      <c r="AB76" s="69"/>
       <c r="AC76" s="35"/>
       <c r="AD76" s="35">
         <f>AD68+AA76-(R103)</f>
@@ -5920,8 +5941,8 @@
       <c r="AJ76" s="41"/>
     </row>
     <row r="77" spans="1:36" ht="18" customHeight="1">
-      <c r="A77" s="87"/>
-      <c r="B77" s="88"/>
+      <c r="A77" s="82"/>
+      <c r="B77" s="83"/>
       <c r="C77" s="42" t="s">
         <v>20</v>
       </c>
@@ -6038,10 +6059,10 @@
       <c r="AJ77" s="47"/>
     </row>
     <row r="78" spans="1:36" ht="18" customHeight="1">
-      <c r="A78" s="76" t="s">
+      <c r="A78" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B78" s="77"/>
+      <c r="B78" s="74"/>
       <c r="C78" s="22" t="s">
         <v>46</v>
       </c>
@@ -6101,8 +6122,8 @@
       <c r="AJ78" s="29"/>
     </row>
     <row r="79" spans="1:36" ht="18" customHeight="1">
-      <c r="A79" s="78"/>
-      <c r="B79" s="77"/>
+      <c r="A79" s="75"/>
+      <c r="B79" s="74"/>
       <c r="C79" s="22" t="s">
         <v>47</v>
       </c>
@@ -6150,8 +6171,8 @@
       <c r="AJ79" s="29"/>
     </row>
     <row r="80" spans="1:36" ht="18" customHeight="1">
-      <c r="A80" s="78"/>
-      <c r="B80" s="77"/>
+      <c r="A80" s="75"/>
+      <c r="B80" s="74"/>
       <c r="C80" s="22" t="s">
         <v>48</v>
       </c>
@@ -6199,8 +6220,8 @@
       <c r="AJ80" s="29"/>
     </row>
     <row r="81" spans="1:36" ht="18" customHeight="1">
-      <c r="A81" s="78"/>
-      <c r="B81" s="77"/>
+      <c r="A81" s="75"/>
+      <c r="B81" s="74"/>
       <c r="C81" s="22" t="s">
         <v>49</v>
       </c>
@@ -6248,8 +6269,8 @@
       <c r="AJ81" s="29"/>
     </row>
     <row r="82" spans="1:36" ht="18" customHeight="1">
-      <c r="A82" s="78"/>
-      <c r="B82" s="77"/>
+      <c r="A82" s="75"/>
+      <c r="B82" s="74"/>
       <c r="C82" s="22" t="s">
         <v>50</v>
       </c>
@@ -6362,34 +6383,34 @@
       <c r="C84" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D84" s="74"/>
-      <c r="E84" s="73"/>
-      <c r="F84" s="74"/>
-      <c r="G84" s="73"/>
-      <c r="H84" s="74"/>
-      <c r="I84" s="73"/>
-      <c r="J84" s="74"/>
-      <c r="K84" s="73"/>
-      <c r="L84" s="74"/>
-      <c r="M84" s="73"/>
-      <c r="N84" s="74"/>
-      <c r="O84" s="73"/>
-      <c r="P84" s="74"/>
-      <c r="Q84" s="73"/>
-      <c r="R84" s="74"/>
-      <c r="S84" s="73"/>
-      <c r="T84" s="74"/>
-      <c r="U84" s="73"/>
-      <c r="V84" s="74"/>
-      <c r="W84" s="73"/>
-      <c r="X84" s="74"/>
-      <c r="Y84" s="73"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="69"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="69"/>
+      <c r="H84" s="68"/>
+      <c r="I84" s="69"/>
+      <c r="J84" s="68"/>
+      <c r="K84" s="69"/>
+      <c r="L84" s="68"/>
+      <c r="M84" s="69"/>
+      <c r="N84" s="68"/>
+      <c r="O84" s="69"/>
+      <c r="P84" s="68"/>
+      <c r="Q84" s="69"/>
+      <c r="R84" s="68"/>
+      <c r="S84" s="69"/>
+      <c r="T84" s="68"/>
+      <c r="U84" s="69"/>
+      <c r="V84" s="68"/>
+      <c r="W84" s="69"/>
+      <c r="X84" s="68"/>
+      <c r="Y84" s="69"/>
       <c r="Z84" s="36"/>
-      <c r="AA84" s="74">
+      <c r="AA84" s="68">
         <f>D84+F84+H84+J84+L84+N84+P84+R84+T84+V84+X84</f>
         <v>0</v>
       </c>
-      <c r="AB84" s="73"/>
+      <c r="AB84" s="69"/>
       <c r="AC84" s="35"/>
       <c r="AD84" s="35">
         <f>AD76+AA84-(T103)</f>
@@ -6415,8 +6436,8 @@
       <c r="AJ84" s="41"/>
     </row>
     <row r="85" spans="1:36" ht="18" customHeight="1">
-      <c r="A85" s="87"/>
-      <c r="B85" s="88"/>
+      <c r="A85" s="82"/>
+      <c r="B85" s="83"/>
       <c r="C85" s="42" t="s">
         <v>20</v>
       </c>
@@ -6533,10 +6554,10 @@
       <c r="AJ85" s="47"/>
     </row>
     <row r="86" spans="1:36" ht="18" customHeight="1">
-      <c r="A86" s="76" t="s">
+      <c r="A86" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B86" s="77"/>
+      <c r="B86" s="74"/>
       <c r="C86" s="22" t="s">
         <v>46</v>
       </c>
@@ -6596,8 +6617,8 @@
       <c r="AJ86" s="29"/>
     </row>
     <row r="87" spans="1:36" ht="18" customHeight="1">
-      <c r="A87" s="78"/>
-      <c r="B87" s="77"/>
+      <c r="A87" s="75"/>
+      <c r="B87" s="74"/>
       <c r="C87" s="22" t="s">
         <v>47</v>
       </c>
@@ -6645,8 +6666,8 @@
       <c r="AJ87" s="29"/>
     </row>
     <row r="88" spans="1:36" ht="18" customHeight="1">
-      <c r="A88" s="78"/>
-      <c r="B88" s="77"/>
+      <c r="A88" s="75"/>
+      <c r="B88" s="74"/>
       <c r="C88" s="22" t="s">
         <v>48</v>
       </c>
@@ -6694,8 +6715,8 @@
       <c r="AJ88" s="29"/>
     </row>
     <row r="89" spans="1:36" ht="18" customHeight="1">
-      <c r="A89" s="78"/>
-      <c r="B89" s="77"/>
+      <c r="A89" s="75"/>
+      <c r="B89" s="74"/>
       <c r="C89" s="22" t="s">
         <v>49</v>
       </c>
@@ -6743,8 +6764,8 @@
       <c r="AJ89" s="29"/>
     </row>
     <row r="90" spans="1:36" ht="18" customHeight="1">
-      <c r="A90" s="78"/>
-      <c r="B90" s="77"/>
+      <c r="A90" s="75"/>
+      <c r="B90" s="74"/>
       <c r="C90" s="22" t="s">
         <v>50</v>
       </c>
@@ -6857,34 +6878,34 @@
       <c r="C92" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="73"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="73"/>
-      <c r="H92" s="74"/>
-      <c r="I92" s="73"/>
-      <c r="J92" s="74"/>
-      <c r="K92" s="73"/>
-      <c r="L92" s="74"/>
-      <c r="M92" s="73"/>
-      <c r="N92" s="74"/>
-      <c r="O92" s="73"/>
-      <c r="P92" s="74"/>
-      <c r="Q92" s="73"/>
-      <c r="R92" s="74"/>
-      <c r="S92" s="73"/>
-      <c r="T92" s="74"/>
-      <c r="U92" s="73"/>
-      <c r="V92" s="74"/>
-      <c r="W92" s="73"/>
-      <c r="X92" s="74"/>
-      <c r="Y92" s="73"/>
+      <c r="D92" s="68"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="68"/>
+      <c r="G92" s="69"/>
+      <c r="H92" s="68"/>
+      <c r="I92" s="69"/>
+      <c r="J92" s="68"/>
+      <c r="K92" s="69"/>
+      <c r="L92" s="68"/>
+      <c r="M92" s="69"/>
+      <c r="N92" s="68"/>
+      <c r="O92" s="69"/>
+      <c r="P92" s="68"/>
+      <c r="Q92" s="69"/>
+      <c r="R92" s="68"/>
+      <c r="S92" s="69"/>
+      <c r="T92" s="68"/>
+      <c r="U92" s="69"/>
+      <c r="V92" s="68"/>
+      <c r="W92" s="69"/>
+      <c r="X92" s="68"/>
+      <c r="Y92" s="69"/>
       <c r="Z92" s="36"/>
-      <c r="AA92" s="74">
+      <c r="AA92" s="68">
         <f>D92+F92+H92+J92+L92+N92+P92+R92+T92+V92+X92</f>
         <v>0</v>
       </c>
-      <c r="AB92" s="73"/>
+      <c r="AB92" s="69"/>
       <c r="AC92" s="35"/>
       <c r="AD92" s="35">
         <f>AD84+AA92-(V103)</f>
@@ -6910,8 +6931,8 @@
       <c r="AJ92" s="41"/>
     </row>
     <row r="93" spans="1:36" ht="18" customHeight="1">
-      <c r="A93" s="87"/>
-      <c r="B93" s="88"/>
+      <c r="A93" s="82"/>
+      <c r="B93" s="83"/>
       <c r="C93" s="42" t="s">
         <v>20</v>
       </c>
@@ -7725,67 +7746,67 @@
       <c r="C100" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D100" s="74">
+      <c r="D100" s="68">
         <f>D12+D20+D28+D36+D44+D52+D60+D68+D76+D84+D92</f>
         <v>0</v>
       </c>
-      <c r="E100" s="73"/>
-      <c r="F100" s="74">
+      <c r="E100" s="69"/>
+      <c r="F100" s="68">
         <f>F12+F20+F28+F36+F44+F52+F60+F68+F76+F84+F92</f>
         <v>0</v>
       </c>
-      <c r="G100" s="73"/>
-      <c r="H100" s="74">
+      <c r="G100" s="69"/>
+      <c r="H100" s="68">
         <f>H12+H20+H28+H36+H44+H52+H60+H68+H76+H84+H92</f>
         <v>0</v>
       </c>
-      <c r="I100" s="73"/>
-      <c r="J100" s="74">
+      <c r="I100" s="69"/>
+      <c r="J100" s="68">
         <f>J12+J20+J28+J36+J44+J52+J60+J68+J76+J84+J92</f>
         <v>0</v>
       </c>
-      <c r="K100" s="73"/>
-      <c r="L100" s="74">
+      <c r="K100" s="69"/>
+      <c r="L100" s="68">
         <f>L12+L20+L28+L36+L44+L52+L60+L68+L76+L84+L92</f>
         <v>0</v>
       </c>
-      <c r="M100" s="73"/>
-      <c r="N100" s="74">
+      <c r="M100" s="69"/>
+      <c r="N100" s="68">
         <f>N12+N20+N28+N36+N44+N52+N60+N68+N76+N84+N92</f>
         <v>0</v>
       </c>
-      <c r="O100" s="73"/>
-      <c r="P100" s="74">
+      <c r="O100" s="69"/>
+      <c r="P100" s="68">
         <f>P12+P20+P28+P36+P44+P52+P60+P68+P76+P84+P92</f>
         <v>0</v>
       </c>
-      <c r="Q100" s="73"/>
-      <c r="R100" s="74">
+      <c r="Q100" s="69"/>
+      <c r="R100" s="68">
         <f>R12+R20+R28+R36+R44+R52+R60+R68+R76+R84+R92</f>
         <v>0</v>
       </c>
-      <c r="S100" s="73"/>
-      <c r="T100" s="74">
+      <c r="S100" s="69"/>
+      <c r="T100" s="68">
         <f>T12+T20+T28+T36+T44+T52+T60+T68+T76+T84+T92</f>
         <v>0</v>
       </c>
-      <c r="U100" s="73"/>
-      <c r="V100" s="74">
+      <c r="U100" s="69"/>
+      <c r="V100" s="68">
         <f>V12+V20+V28+V36+V44+V52+V60+V68+V76+V84+V92</f>
         <v>0</v>
       </c>
-      <c r="W100" s="73"/>
-      <c r="X100" s="74">
+      <c r="W100" s="69"/>
+      <c r="X100" s="68">
         <f>X12+X20+X28+X36+X44+X52+X60+X68+X76+X84+X92</f>
         <v>0</v>
       </c>
-      <c r="Y100" s="73"/>
+      <c r="Y100" s="69"/>
       <c r="Z100" s="36"/>
-      <c r="AA100" s="74">
+      <c r="AA100" s="68">
         <f>D100+F100+H100+J100+L100+N100+P100+R100+T100+V100+X100</f>
         <v>0</v>
       </c>
-      <c r="AB100" s="73"/>
+      <c r="AB100" s="69"/>
       <c r="AC100" s="35"/>
       <c r="AD100" s="35"/>
       <c r="AE100" s="37"/>
@@ -7796,8 +7817,8 @@
       <c r="AJ100" s="41"/>
     </row>
     <row r="101" spans="1:36" ht="18" customHeight="1">
-      <c r="A101" s="87"/>
-      <c r="B101" s="88"/>
+      <c r="A101" s="82"/>
+      <c r="B101" s="83"/>
       <c r="C101" s="42" t="s">
         <v>20</v>
       </c>
@@ -7911,488 +7932,488 @@
       <c r="AJ101" s="56"/>
     </row>
     <row r="102" spans="1:36" ht="18" customHeight="1">
-      <c r="A102" s="97" t="s">
+      <c r="A102" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="B102" s="98"/>
-      <c r="C102" s="99"/>
+      <c r="B102" s="93"/>
+      <c r="C102" s="94"/>
       <c r="D102" s="72">
         <f>D94+E94*2+D95+E95*2+D96+E96*2+D97+E97*2+D98+E98*2+D99+E99*2</f>
         <v>0</v>
       </c>
-      <c r="E102" s="73"/>
+      <c r="E102" s="71"/>
       <c r="F102" s="72">
         <f>F94+G94*2+F95+G95*2+F96+G96*2+F97+G97*2+F98+G98*2+F99+G99*2</f>
         <v>0</v>
       </c>
-      <c r="G102" s="73"/>
+      <c r="G102" s="71"/>
       <c r="H102" s="72">
         <f>H94+I94*2+H95+I95*2+H96+I96*2+H97+I97*2+H98+I98*2+H99+I99*2</f>
         <v>0</v>
       </c>
-      <c r="I102" s="73"/>
+      <c r="I102" s="71"/>
       <c r="J102" s="72">
         <f>J94+K94*2+J95+K95*2+J96+K96*2+J97+K97*2+J98+K98*2+J99+K99*2</f>
         <v>0</v>
       </c>
-      <c r="K102" s="73"/>
+      <c r="K102" s="71"/>
       <c r="L102" s="72">
         <f>L94+M94*2+L95+M95*2+L96+M96*2+L97+M97*2+L98+M98*2+L99+M99*2</f>
         <v>0</v>
       </c>
-      <c r="M102" s="73"/>
+      <c r="M102" s="71"/>
       <c r="N102" s="72">
         <f>N94+O94*2+N95+O95*2+N96+O96*2+N97+O97*2+N98+O98*2+N99+O99*2</f>
         <v>0</v>
       </c>
-      <c r="O102" s="73"/>
+      <c r="O102" s="71"/>
       <c r="P102" s="72">
         <f>P94+Q94*2+P95+Q95*2+P96+Q96*2+P97+Q97*2+P98+Q98*2+P99+Q99*2</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="73"/>
+      <c r="Q102" s="71"/>
       <c r="R102" s="72">
         <f>R94+S94*2+R95+S95*2+R96+S96*2+R97+S97*2+R98+S98*2+R99+S99*2</f>
         <v>0</v>
       </c>
-      <c r="S102" s="73"/>
+      <c r="S102" s="71"/>
       <c r="T102" s="72">
         <f>T94+U94*2+T95+U95*2+T96+U96*2+T97+U97*2+T98+U98*2+T99+U99*2</f>
         <v>0</v>
       </c>
-      <c r="U102" s="73"/>
+      <c r="U102" s="71"/>
       <c r="V102" s="72">
         <f>V94+W94*2+V95+W95*2+V96+W96*2+V97+W97*2+V98+W98*2+V99+W99*2</f>
         <v>0</v>
       </c>
-      <c r="W102" s="73"/>
+      <c r="W102" s="71"/>
       <c r="X102" s="72">
         <f>X94+Y94*2+X95+Y95*2+X96+Y96*2+X97+Y97*2+X98+Y98*2+X99+Y99*2</f>
         <v>0</v>
       </c>
-      <c r="Y102" s="73"/>
-      <c r="Z102" s="36"/>
-      <c r="AA102" s="72"/>
-      <c r="AB102" s="73"/>
-      <c r="AC102" s="57"/>
-      <c r="AD102" s="57"/>
+      <c r="Y102" s="71"/>
+      <c r="Z102" s="57"/>
+      <c r="AA102" s="58"/>
+      <c r="AB102" s="57"/>
+      <c r="AC102" s="58"/>
+      <c r="AD102" s="58"/>
       <c r="AE102" s="58"/>
-      <c r="AF102" s="57"/>
+      <c r="AF102" s="58"/>
       <c r="AG102" s="58"/>
-      <c r="AH102" s="57"/>
+      <c r="AH102" s="58"/>
       <c r="AI102" s="59"/>
-      <c r="AJ102" s="60"/>
+      <c r="AJ102" s="58"/>
     </row>
     <row r="103" spans="1:36" ht="18" customHeight="1">
-      <c r="A103" s="97" t="s">
+      <c r="A103" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="B103" s="98"/>
-      <c r="C103" s="99"/>
-      <c r="D103" s="75">
+      <c r="B103" s="93"/>
+      <c r="C103" s="94"/>
+      <c r="D103" s="70">
         <f>D100</f>
         <v>0</v>
       </c>
-      <c r="E103" s="73"/>
-      <c r="F103" s="75">
+      <c r="E103" s="71"/>
+      <c r="F103" s="70">
         <f>F100</f>
         <v>0</v>
       </c>
-      <c r="G103" s="73"/>
-      <c r="H103" s="75">
+      <c r="G103" s="71"/>
+      <c r="H103" s="70">
         <f>H100</f>
         <v>0</v>
       </c>
-      <c r="I103" s="73"/>
-      <c r="J103" s="75">
+      <c r="I103" s="71"/>
+      <c r="J103" s="70">
         <f>J100</f>
         <v>0</v>
       </c>
-      <c r="K103" s="73"/>
-      <c r="L103" s="75">
+      <c r="K103" s="71"/>
+      <c r="L103" s="70">
         <f>L100</f>
         <v>0</v>
       </c>
-      <c r="M103" s="73"/>
-      <c r="N103" s="75">
+      <c r="M103" s="71"/>
+      <c r="N103" s="70">
         <f>N100</f>
         <v>0</v>
       </c>
-      <c r="O103" s="73"/>
-      <c r="P103" s="75">
+      <c r="O103" s="71"/>
+      <c r="P103" s="70">
         <f>P100</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="73"/>
-      <c r="R103" s="75">
+      <c r="Q103" s="71"/>
+      <c r="R103" s="70">
         <f>R100</f>
         <v>0</v>
       </c>
-      <c r="S103" s="73"/>
-      <c r="T103" s="75">
+      <c r="S103" s="71"/>
+      <c r="T103" s="70">
         <f>T100</f>
         <v>0</v>
       </c>
-      <c r="U103" s="73"/>
-      <c r="V103" s="75">
+      <c r="U103" s="71"/>
+      <c r="V103" s="70">
         <f>V100</f>
         <v>0</v>
       </c>
-      <c r="W103" s="73"/>
-      <c r="X103" s="75">
+      <c r="W103" s="71"/>
+      <c r="X103" s="70">
         <f>X100</f>
         <v>0</v>
       </c>
-      <c r="Y103" s="73"/>
-      <c r="Z103" s="36"/>
-      <c r="AA103" s="75"/>
-      <c r="AB103" s="73"/>
-      <c r="AC103" s="61"/>
-      <c r="AD103" s="61"/>
-      <c r="AE103" s="62"/>
-      <c r="AF103" s="57"/>
+      <c r="Y103" s="71"/>
+      <c r="Z103" s="57"/>
+      <c r="AA103" s="59"/>
+      <c r="AB103" s="57"/>
+      <c r="AC103" s="59"/>
+      <c r="AD103" s="59"/>
+      <c r="AE103" s="59"/>
+      <c r="AF103" s="58"/>
       <c r="AG103" s="58"/>
-      <c r="AH103" s="61"/>
+      <c r="AH103" s="59"/>
       <c r="AI103" s="59"/>
-      <c r="AJ103" s="63"/>
+      <c r="AJ103" s="59"/>
     </row>
     <row r="104" spans="1:36" ht="18" customHeight="1">
-      <c r="A104" s="64"/>
-      <c r="B104" s="49"/>
-      <c r="C104" s="65"/>
-      <c r="D104" s="50"/>
-      <c r="E104" s="51"/>
-      <c r="F104" s="50"/>
-      <c r="G104" s="51"/>
-      <c r="H104" s="50"/>
-      <c r="I104" s="51"/>
-      <c r="J104" s="50"/>
-      <c r="K104" s="51"/>
-      <c r="L104" s="50"/>
-      <c r="M104" s="51"/>
-      <c r="N104" s="50"/>
-      <c r="O104" s="51"/>
-      <c r="P104" s="50"/>
-      <c r="Q104" s="51"/>
-      <c r="R104" s="50"/>
-      <c r="S104" s="51"/>
-      <c r="T104" s="50"/>
-      <c r="U104" s="51"/>
-      <c r="V104" s="50"/>
-      <c r="W104" s="51"/>
-      <c r="X104" s="50"/>
-      <c r="Y104" s="51"/>
-      <c r="Z104" s="66"/>
-      <c r="AA104" s="50"/>
-      <c r="AB104" s="51"/>
-      <c r="AC104" s="50"/>
-      <c r="AD104" s="50"/>
-      <c r="AE104" s="51"/>
-      <c r="AF104" s="50"/>
-      <c r="AG104" s="51"/>
-      <c r="AH104" s="50"/>
-      <c r="AI104" s="40"/>
-      <c r="AJ104" s="67"/>
+      <c r="A104" s="60"/>
+      <c r="B104" s="60"/>
+      <c r="C104" s="61"/>
+      <c r="D104" s="62"/>
+      <c r="E104" s="62"/>
+      <c r="F104" s="62"/>
+      <c r="G104" s="62"/>
+      <c r="H104" s="62"/>
+      <c r="I104" s="62"/>
+      <c r="J104" s="62"/>
+      <c r="K104" s="62"/>
+      <c r="L104" s="62"/>
+      <c r="M104" s="62"/>
+      <c r="N104" s="62"/>
+      <c r="O104" s="62"/>
+      <c r="P104" s="62"/>
+      <c r="Q104" s="62"/>
+      <c r="R104" s="62"/>
+      <c r="S104" s="62"/>
+      <c r="T104" s="62"/>
+      <c r="U104" s="62"/>
+      <c r="V104" s="62"/>
+      <c r="W104" s="62"/>
+      <c r="X104" s="62"/>
+      <c r="Y104" s="62"/>
+      <c r="Z104" s="60"/>
+      <c r="AA104" s="62"/>
+      <c r="AB104" s="62"/>
+      <c r="AC104" s="62"/>
+      <c r="AD104" s="62"/>
+      <c r="AE104" s="62"/>
+      <c r="AF104" s="62"/>
+      <c r="AG104" s="62"/>
+      <c r="AH104" s="62"/>
+      <c r="AI104" s="63"/>
+      <c r="AJ104" s="62"/>
     </row>
     <row r="105" spans="1:36" ht="18" customHeight="1">
-      <c r="A105" s="64"/>
-      <c r="B105" s="49"/>
-      <c r="C105" s="65"/>
-      <c r="D105" s="50"/>
-      <c r="E105" s="51"/>
-      <c r="F105" s="50"/>
-      <c r="G105" s="51"/>
-      <c r="H105" s="50"/>
-      <c r="I105" s="51"/>
-      <c r="J105" s="50"/>
-      <c r="K105" s="51"/>
-      <c r="L105" s="50"/>
-      <c r="M105" s="51"/>
-      <c r="N105" s="50"/>
-      <c r="O105" s="51"/>
-      <c r="P105" s="50"/>
-      <c r="Q105" s="51"/>
-      <c r="R105" s="50"/>
-      <c r="S105" s="51"/>
-      <c r="T105" s="50"/>
-      <c r="U105" s="51"/>
-      <c r="V105" s="50"/>
-      <c r="W105" s="51"/>
-      <c r="X105" s="50"/>
-      <c r="Y105" s="51"/>
-      <c r="Z105" s="66"/>
-      <c r="AA105" s="50"/>
-      <c r="AB105" s="51"/>
-      <c r="AC105" s="50"/>
-      <c r="AD105" s="50"/>
-      <c r="AE105" s="51"/>
-      <c r="AF105" s="50"/>
-      <c r="AG105" s="51"/>
-      <c r="AH105" s="50"/>
-      <c r="AI105" s="40"/>
-      <c r="AJ105" s="67"/>
+      <c r="A105" s="60"/>
+      <c r="B105" s="60"/>
+      <c r="C105" s="61"/>
+      <c r="D105" s="62"/>
+      <c r="E105" s="62"/>
+      <c r="F105" s="62"/>
+      <c r="G105" s="62"/>
+      <c r="H105" s="62"/>
+      <c r="I105" s="62"/>
+      <c r="J105" s="62"/>
+      <c r="K105" s="62"/>
+      <c r="L105" s="62"/>
+      <c r="M105" s="62"/>
+      <c r="N105" s="62"/>
+      <c r="O105" s="62"/>
+      <c r="P105" s="62"/>
+      <c r="Q105" s="62"/>
+      <c r="R105" s="62"/>
+      <c r="S105" s="62"/>
+      <c r="T105" s="62"/>
+      <c r="U105" s="62"/>
+      <c r="V105" s="62"/>
+      <c r="W105" s="62"/>
+      <c r="X105" s="62"/>
+      <c r="Y105" s="62"/>
+      <c r="Z105" s="60"/>
+      <c r="AA105" s="62"/>
+      <c r="AB105" s="62"/>
+      <c r="AC105" s="62"/>
+      <c r="AD105" s="62"/>
+      <c r="AE105" s="62"/>
+      <c r="AF105" s="62"/>
+      <c r="AG105" s="62"/>
+      <c r="AH105" s="62"/>
+      <c r="AI105" s="63"/>
+      <c r="AJ105" s="62"/>
     </row>
     <row r="106" spans="1:36" ht="18" customHeight="1">
-      <c r="A106" s="97" t="s">
+      <c r="A106" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="B106" s="98"/>
-      <c r="C106" s="99"/>
+      <c r="B106" s="93"/>
+      <c r="C106" s="94"/>
       <c r="D106" s="72">
         <f>D101+E101+AA21+AB21</f>
         <v>0</v>
       </c>
-      <c r="E106" s="73"/>
+      <c r="E106" s="71"/>
       <c r="F106" s="72">
         <f>F101+G101+AA29+AB29</f>
         <v>0</v>
       </c>
-      <c r="G106" s="73"/>
+      <c r="G106" s="71"/>
       <c r="H106" s="72">
         <f>H101+I101+AA37+AB37</f>
         <v>0</v>
       </c>
-      <c r="I106" s="73"/>
+      <c r="I106" s="71"/>
       <c r="J106" s="72">
         <f>J101+K101+AA45+AB45</f>
         <v>0</v>
       </c>
-      <c r="K106" s="73"/>
+      <c r="K106" s="71"/>
       <c r="L106" s="72">
         <f>L101+M101+AA53+AB53</f>
         <v>0</v>
       </c>
-      <c r="M106" s="73"/>
+      <c r="M106" s="71"/>
       <c r="N106" s="72">
         <f>N101+O101+AA61+AB61</f>
         <v>0</v>
       </c>
-      <c r="O106" s="73"/>
+      <c r="O106" s="71"/>
       <c r="P106" s="72">
         <f>P101+Q101+AA69+AB69</f>
         <v>0</v>
       </c>
-      <c r="Q106" s="73"/>
+      <c r="Q106" s="71"/>
       <c r="R106" s="72">
         <f>R101+S101+AA77+AB77</f>
         <v>0</v>
       </c>
-      <c r="S106" s="73"/>
+      <c r="S106" s="71"/>
       <c r="T106" s="72">
         <f>T101+U101+AA85+AB85</f>
         <v>0</v>
       </c>
-      <c r="U106" s="73"/>
+      <c r="U106" s="71"/>
       <c r="V106" s="72">
         <f>V101+W101+AA93+AB93</f>
         <v>0</v>
       </c>
-      <c r="W106" s="73"/>
+      <c r="W106" s="71"/>
       <c r="X106" s="72">
         <f>X101+Y101+0</f>
         <v>0</v>
       </c>
-      <c r="Y106" s="73"/>
-      <c r="Z106" s="36"/>
-      <c r="AA106" s="72"/>
-      <c r="AB106" s="73"/>
-      <c r="AC106" s="57"/>
-      <c r="AD106" s="57"/>
+      <c r="Y106" s="71"/>
+      <c r="Z106" s="57"/>
+      <c r="AA106" s="58"/>
+      <c r="AB106" s="57"/>
+      <c r="AC106" s="58"/>
+      <c r="AD106" s="58"/>
       <c r="AE106" s="58"/>
-      <c r="AF106" s="57"/>
+      <c r="AF106" s="58"/>
       <c r="AG106" s="58"/>
-      <c r="AH106" s="57"/>
+      <c r="AH106" s="58"/>
       <c r="AI106" s="59"/>
-      <c r="AJ106" s="60"/>
+      <c r="AJ106" s="58"/>
     </row>
     <row r="107" spans="1:36" ht="18" customHeight="1">
-      <c r="A107" s="97" t="s">
+      <c r="A107" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="B107" s="98"/>
-      <c r="C107" s="99"/>
+      <c r="B107" s="93"/>
+      <c r="C107" s="94"/>
       <c r="D107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,D3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,D3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="E107" s="73"/>
+      <c r="E107" s="71"/>
       <c r="F107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,F3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,F3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="G107" s="73"/>
+      <c r="G107" s="71"/>
       <c r="H107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,H3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,H3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="I107" s="73"/>
+      <c r="I107" s="71"/>
       <c r="J107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,J3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,J3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="K107" s="73"/>
+      <c r="K107" s="71"/>
       <c r="L107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,L3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,L3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="M107" s="73"/>
+      <c r="M107" s="71"/>
       <c r="N107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,N3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,N3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="O107" s="73"/>
+      <c r="O107" s="71"/>
       <c r="P107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,P3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,P3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="Q107" s="73"/>
+      <c r="Q107" s="71"/>
       <c r="R107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,R3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,R3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="S107" s="73"/>
+      <c r="S107" s="71"/>
       <c r="T107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,T3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,T3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="U107" s="73"/>
+      <c r="U107" s="71"/>
       <c r="V107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,V3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,V3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="W107" s="73"/>
+      <c r="W107" s="71"/>
       <c r="X107" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,X3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,X3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="Y107" s="73"/>
-      <c r="Z107" s="36"/>
-      <c r="AA107" s="72"/>
-      <c r="AB107" s="73"/>
-      <c r="AC107" s="57"/>
-      <c r="AD107" s="57"/>
+      <c r="Y107" s="71"/>
+      <c r="Z107" s="57"/>
+      <c r="AA107" s="58"/>
+      <c r="AB107" s="57"/>
+      <c r="AC107" s="58"/>
+      <c r="AD107" s="58"/>
       <c r="AE107" s="58"/>
-      <c r="AF107" s="57"/>
+      <c r="AF107" s="58"/>
       <c r="AG107" s="58"/>
-      <c r="AH107" s="57"/>
+      <c r="AH107" s="58"/>
       <c r="AI107" s="59"/>
-      <c r="AJ107" s="60"/>
+      <c r="AJ107" s="58"/>
     </row>
     <row r="108" spans="1:36" ht="18" customHeight="1">
-      <c r="A108" s="97" t="s">
+      <c r="A108" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="B108" s="98"/>
-      <c r="C108" s="99"/>
+      <c r="B108" s="93"/>
+      <c r="C108" s="94"/>
       <c r="D108" s="72"/>
-      <c r="E108" s="73"/>
+      <c r="E108" s="71"/>
       <c r="F108" s="72"/>
-      <c r="G108" s="73"/>
+      <c r="G108" s="71"/>
       <c r="H108" s="72"/>
-      <c r="I108" s="73"/>
+      <c r="I108" s="71"/>
       <c r="J108" s="72"/>
-      <c r="K108" s="73"/>
+      <c r="K108" s="71"/>
       <c r="L108" s="72"/>
-      <c r="M108" s="73"/>
+      <c r="M108" s="71"/>
       <c r="N108" s="72"/>
-      <c r="O108" s="73"/>
+      <c r="O108" s="71"/>
       <c r="P108" s="72"/>
-      <c r="Q108" s="73"/>
+      <c r="Q108" s="71"/>
       <c r="R108" s="72"/>
-      <c r="S108" s="73"/>
+      <c r="S108" s="71"/>
       <c r="T108" s="72"/>
-      <c r="U108" s="73"/>
+      <c r="U108" s="71"/>
       <c r="V108" s="72"/>
-      <c r="W108" s="73"/>
+      <c r="W108" s="71"/>
       <c r="X108" s="72"/>
-      <c r="Y108" s="73"/>
-      <c r="Z108" s="36"/>
-      <c r="AA108" s="72"/>
-      <c r="AB108" s="73"/>
-      <c r="AC108" s="57"/>
-      <c r="AD108" s="57"/>
+      <c r="Y108" s="71"/>
+      <c r="Z108" s="57"/>
+      <c r="AA108" s="58"/>
+      <c r="AB108" s="57"/>
+      <c r="AC108" s="58"/>
+      <c r="AD108" s="58"/>
       <c r="AE108" s="58"/>
-      <c r="AF108" s="57"/>
+      <c r="AF108" s="58"/>
       <c r="AG108" s="58"/>
-      <c r="AH108" s="57"/>
+      <c r="AH108" s="58"/>
       <c r="AI108" s="59"/>
-      <c r="AJ108" s="60"/>
+      <c r="AJ108" s="58"/>
     </row>
     <row r="109" spans="1:36" ht="18" customHeight="1">
-      <c r="A109" s="87" t="s">
+      <c r="A109" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="B109" s="88"/>
-      <c r="C109" s="102"/>
-      <c r="D109" s="85">
+      <c r="B109" s="93"/>
+      <c r="C109" s="94"/>
+      <c r="D109" s="72">
         <f>D108-D107</f>
         <v>0</v>
       </c>
-      <c r="E109" s="86"/>
-      <c r="F109" s="85">
+      <c r="E109" s="71"/>
+      <c r="F109" s="72">
         <f>F108-F107</f>
         <v>0</v>
       </c>
-      <c r="G109" s="86"/>
-      <c r="H109" s="85">
+      <c r="G109" s="71"/>
+      <c r="H109" s="72">
         <f>H108-H107</f>
         <v>0</v>
       </c>
-      <c r="I109" s="86"/>
-      <c r="J109" s="85">
+      <c r="I109" s="71"/>
+      <c r="J109" s="72">
         <f>J108-J107</f>
         <v>0</v>
       </c>
-      <c r="K109" s="86"/>
-      <c r="L109" s="85">
+      <c r="K109" s="71"/>
+      <c r="L109" s="72">
         <f>L108-L107</f>
         <v>0</v>
       </c>
-      <c r="M109" s="86"/>
-      <c r="N109" s="85">
+      <c r="M109" s="71"/>
+      <c r="N109" s="72">
         <f>N108-N107</f>
         <v>0</v>
       </c>
-      <c r="O109" s="86"/>
-      <c r="P109" s="85">
+      <c r="O109" s="71"/>
+      <c r="P109" s="72">
         <f>P108-P107</f>
         <v>0</v>
       </c>
-      <c r="Q109" s="86"/>
-      <c r="R109" s="85">
+      <c r="Q109" s="71"/>
+      <c r="R109" s="72">
         <f>R108-R107</f>
         <v>0</v>
       </c>
-      <c r="S109" s="86"/>
-      <c r="T109" s="85">
+      <c r="S109" s="71"/>
+      <c r="T109" s="72">
         <f>T108-T107</f>
         <v>0</v>
       </c>
-      <c r="U109" s="86"/>
-      <c r="V109" s="85">
+      <c r="U109" s="71"/>
+      <c r="V109" s="72">
         <f>V108-V107</f>
         <v>0</v>
       </c>
-      <c r="W109" s="86"/>
-      <c r="X109" s="85">
+      <c r="W109" s="71"/>
+      <c r="X109" s="72">
         <f>X108-X107</f>
         <v>0</v>
       </c>
-      <c r="Y109" s="86"/>
-      <c r="Z109" s="68"/>
-      <c r="AA109" s="85"/>
-      <c r="AB109" s="86"/>
-      <c r="AC109" s="52"/>
-      <c r="AD109" s="52"/>
-      <c r="AE109" s="53"/>
-      <c r="AF109" s="52"/>
-      <c r="AG109" s="53"/>
-      <c r="AH109" s="52"/>
-      <c r="AI109" s="55"/>
-      <c r="AJ109" s="56"/>
+      <c r="Y109" s="71"/>
+      <c r="Z109" s="57"/>
+      <c r="AA109" s="58"/>
+      <c r="AB109" s="57"/>
+      <c r="AC109" s="58"/>
+      <c r="AD109" s="58"/>
+      <c r="AE109" s="58"/>
+      <c r="AF109" s="58"/>
+      <c r="AG109" s="58"/>
+      <c r="AH109" s="58"/>
+      <c r="AI109" s="59"/>
+      <c r="AJ109" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="284">
+  <mergeCells count="278">
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="F106:G106"/>
     <mergeCell ref="A102:C102"/>
@@ -8413,6 +8434,26 @@
     <mergeCell ref="A62:B66"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="L108:M108"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="N108:O108"/>
+    <mergeCell ref="D109:E109"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="R103:S103"/>
+    <mergeCell ref="T103:U103"/>
+    <mergeCell ref="V106:W106"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="X103:Y103"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A108:C108"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D52:E52"/>
     <mergeCell ref="T106:U106"/>
@@ -8431,53 +8472,6 @@
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="P12:Q12"/>
     <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="J106:K106"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="A14:B18"/>
-    <mergeCell ref="AA76:AB76"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="L108:M108"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="N108:O108"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="R103:S103"/>
-    <mergeCell ref="T103:U103"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="V106:W106"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="X103:Y103"/>
-    <mergeCell ref="R109:S109"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="T109:U109"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="L84:M84"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="N84:O84"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="X109:Y109"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="D109:E109"/>
-    <mergeCell ref="V109:W109"/>
-    <mergeCell ref="R107:S107"/>
-    <mergeCell ref="T107:U107"/>
-    <mergeCell ref="V76:W76"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="X107:Y107"/>
     <mergeCell ref="P60:Q60"/>
@@ -8496,6 +8490,40 @@
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="T92:U92"/>
     <mergeCell ref="L92:M92"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="R100:S100"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="T100:U100"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="AA84:AB84"/>
+    <mergeCell ref="R106:S106"/>
+    <mergeCell ref="V109:W109"/>
+    <mergeCell ref="R107:S107"/>
+    <mergeCell ref="T107:U107"/>
+    <mergeCell ref="V76:W76"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="R109:S109"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="T109:U109"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="L84:M84"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N84:O84"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="X109:Y109"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="A14:B18"/>
+    <mergeCell ref="AA76:AB76"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="V28:W28"/>
     <mergeCell ref="X28:Y28"/>
     <mergeCell ref="A54:B58"/>
     <mergeCell ref="AA60:AB60"/>
@@ -8512,26 +8540,26 @@
     <mergeCell ref="AA68:AB68"/>
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="AA84:AB84"/>
-    <mergeCell ref="R106:S106"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="R100:S100"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="T100:U100"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="AA44:AB44"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="J28:K28"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="J68:K68"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="L68:M68"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="T3:U3"/>
     <mergeCell ref="V3:W3"/>
+    <mergeCell ref="H4:I4"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AF3:AG3"/>
     <mergeCell ref="H20:I20"/>
@@ -8559,7 +8587,6 @@
     <mergeCell ref="R44:S44"/>
     <mergeCell ref="AF4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AA103:AB103"/>
     <mergeCell ref="V107:W107"/>
     <mergeCell ref="A6:B10"/>
     <mergeCell ref="N107:O107"/>
@@ -8581,9 +8608,7 @@
     <mergeCell ref="X100:Y100"/>
     <mergeCell ref="X84:Y84"/>
     <mergeCell ref="H92:I92"/>
-    <mergeCell ref="AA107:AB107"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="X102:Y102"/>
     <mergeCell ref="AA4:AB4"/>
     <mergeCell ref="A78:B82"/>
     <mergeCell ref="X3:Y3"/>
@@ -8605,6 +8630,9 @@
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="H106:I106"/>
     <mergeCell ref="A38:B42"/>
+    <mergeCell ref="AA100:AB100"/>
+    <mergeCell ref="L103:M103"/>
+    <mergeCell ref="N106:O106"/>
     <mergeCell ref="AA1:AJ1"/>
     <mergeCell ref="L102:M102"/>
     <mergeCell ref="J4:K4"/>
@@ -8612,12 +8640,10 @@
     <mergeCell ref="V108:W108"/>
     <mergeCell ref="X108:Y108"/>
     <mergeCell ref="L109:M109"/>
-    <mergeCell ref="AA108:AB108"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="AA2:AB2"/>
     <mergeCell ref="H1:Y1"/>
     <mergeCell ref="F107:G107"/>
-    <mergeCell ref="AA109:AB109"/>
     <mergeCell ref="H107:I107"/>
     <mergeCell ref="AA92:AB92"/>
     <mergeCell ref="R60:S60"/>
@@ -8629,6 +8655,8 @@
     <mergeCell ref="N36:O36"/>
     <mergeCell ref="T68:U68"/>
     <mergeCell ref="A37:B37"/>
+    <mergeCell ref="N102:O102"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="F108:G108"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="P84:Q84"/>
@@ -8641,9 +8669,7 @@
     <mergeCell ref="T44:U44"/>
     <mergeCell ref="V84:W84"/>
     <mergeCell ref="V44:W44"/>
-    <mergeCell ref="N102:O102"/>
-    <mergeCell ref="L103:M103"/>
-    <mergeCell ref="N106:O106"/>
+    <mergeCell ref="N52:O52"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="P108:Q108"/>
@@ -8653,7 +8679,8 @@
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="F60:G60"/>
     <mergeCell ref="A22:B26"/>
-    <mergeCell ref="AA106:AB106"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D100:E100"/>
     <mergeCell ref="R92:S92"/>
     <mergeCell ref="D60:E60"/>
     <mergeCell ref="N20:O20"/>
@@ -8663,32 +8690,20 @@
     <mergeCell ref="V100:W100"/>
     <mergeCell ref="N100:O100"/>
     <mergeCell ref="F103:G103"/>
-    <mergeCell ref="AA100:AB100"/>
-    <mergeCell ref="AA102:AB102"/>
-    <mergeCell ref="X102:Y102"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D100:E100"/>
     <mergeCell ref="F68:G68"/>
     <mergeCell ref="D84:E84"/>
-    <mergeCell ref="AA44:AB44"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="J28:K28"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="AF6:AG101">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH6:AI101">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8714,66 +8729,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A1" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="89" t="s">
+      <c r="A1" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="69"/>
-      <c r="AE1" s="105"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="82"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="64"/>
+      <c r="AE1" s="99"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
+      <c r="AM1" s="78"/>
+      <c r="AN1" s="79"/>
     </row>
     <row r="2" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A2" s="101" t="str">
+      <c r="A2" s="96" t="str">
         <f>WB!A2</f>
         <v>Service Lane : CGX/0005</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="79" t="str">
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="76" t="str">
         <f>WB!D2</f>
         <v>EXPRESS BERLIN / XPBL2625WE</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -8796,10 +8811,10 @@
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
-      <c r="AE2" s="79" t="s">
+      <c r="AE2" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="AF2" s="80"/>
+      <c r="AF2" s="77"/>
       <c r="AG2" s="5">
         <f>WB!AC2</f>
         <v>0</v>
@@ -8825,163 +8840,163 @@
       <c r="AN2" s="7"/>
     </row>
     <row r="3" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="92" t="s">
+      <c r="B3" s="78"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="92" t="s">
+      <c r="E3" s="78"/>
+      <c r="F3" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="81"/>
-      <c r="H3" s="92" t="s">
+      <c r="G3" s="78"/>
+      <c r="H3" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="81"/>
-      <c r="J3" s="92" t="s">
+      <c r="I3" s="78"/>
+      <c r="J3" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="81"/>
-      <c r="L3" s="92" t="s">
+      <c r="K3" s="78"/>
+      <c r="L3" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="81"/>
-      <c r="N3" s="92" t="s">
+      <c r="M3" s="78"/>
+      <c r="N3" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="81"/>
-      <c r="P3" s="92" t="s">
+      <c r="O3" s="78"/>
+      <c r="P3" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="92" t="s">
+      <c r="Q3" s="78"/>
+      <c r="R3" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="81"/>
-      <c r="T3" s="92" t="s">
+      <c r="S3" s="78"/>
+      <c r="T3" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="81"/>
-      <c r="V3" s="92" t="s">
+      <c r="U3" s="78"/>
+      <c r="V3" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="81"/>
-      <c r="X3" s="92" t="s">
+      <c r="W3" s="78"/>
+      <c r="X3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="92" t="s">
+      <c r="Y3" s="78"/>
+      <c r="Z3" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="92" t="s">
+      <c r="AA3" s="78"/>
+      <c r="AB3" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="69"/>
-      <c r="AE3" s="92" t="s">
+      <c r="AC3" s="78"/>
+      <c r="AD3" s="64"/>
+      <c r="AE3" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="AF3" s="81"/>
+      <c r="AF3" s="78"/>
       <c r="AG3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AH3" s="92" t="s">
+      <c r="AH3" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="92" t="s">
+      <c r="AI3" s="78"/>
+      <c r="AJ3" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="92" t="s">
+      <c r="AK3" s="78"/>
+      <c r="AL3" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="AM3" s="82"/>
+      <c r="AM3" s="79"/>
       <c r="AN3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="83" t="s">
+      <c r="B4" s="81"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="83" t="s">
+      <c r="E4" s="81"/>
+      <c r="F4" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="83" t="s">
+      <c r="G4" s="81"/>
+      <c r="H4" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="84"/>
-      <c r="J4" s="83" t="s">
+      <c r="I4" s="81"/>
+      <c r="J4" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="84"/>
-      <c r="L4" s="83" t="s">
+      <c r="K4" s="81"/>
+      <c r="L4" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="M4" s="84"/>
-      <c r="N4" s="83" t="s">
+      <c r="M4" s="81"/>
+      <c r="N4" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="84"/>
-      <c r="P4" s="83" t="s">
+      <c r="O4" s="81"/>
+      <c r="P4" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="84"/>
-      <c r="R4" s="83" t="s">
+      <c r="Q4" s="81"/>
+      <c r="R4" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="S4" s="84"/>
-      <c r="T4" s="83" t="s">
+      <c r="S4" s="81"/>
+      <c r="T4" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="U4" s="84"/>
-      <c r="V4" s="100" t="s">
+      <c r="U4" s="81"/>
+      <c r="V4" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="W4" s="84"/>
-      <c r="X4" s="83" t="s">
+      <c r="W4" s="81"/>
+      <c r="X4" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="Y4" s="84"/>
-      <c r="Z4" s="83" t="s">
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" s="84"/>
-      <c r="AB4" s="83" t="s">
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="AC4" s="84"/>
-      <c r="AD4" s="70"/>
-      <c r="AE4" s="90"/>
-      <c r="AF4" s="84"/>
+      <c r="AC4" s="81"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="81"/>
       <c r="AG4" s="11"/>
-      <c r="AH4" s="90"/>
-      <c r="AI4" s="84"/>
-      <c r="AJ4" s="90"/>
-      <c r="AK4" s="84"/>
-      <c r="AL4" s="90"/>
-      <c r="AM4" s="91"/>
+      <c r="AH4" s="85"/>
+      <c r="AI4" s="81"/>
+      <c r="AJ4" s="85"/>
+      <c r="AK4" s="81"/>
+      <c r="AL4" s="85"/>
+      <c r="AM4" s="86"/>
       <c r="AN4" s="14"/>
     </row>
     <row r="5" spans="1:40" ht="19.95" customHeight="1">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="96"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="91"/>
       <c r="D5" s="15" t="s">
         <v>38</v>
       </c>
@@ -9091,10 +9106,10 @@
       <c r="AN5" s="19"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="77"/>
+      <c r="B6" s="74"/>
       <c r="C6" s="22" t="s">
         <v>46</v>
       </c>
@@ -9158,8 +9173,8 @@
       <c r="AN6" s="29"/>
     </row>
     <row r="7" spans="1:40" ht="18" customHeight="1">
-      <c r="A7" s="78"/>
-      <c r="B7" s="77"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="74"/>
       <c r="C7" s="22" t="s">
         <v>47</v>
       </c>
@@ -9211,8 +9226,8 @@
       <c r="AN7" s="29"/>
     </row>
     <row r="8" spans="1:40" ht="18" customHeight="1">
-      <c r="A8" s="78"/>
-      <c r="B8" s="77"/>
+      <c r="A8" s="75"/>
+      <c r="B8" s="74"/>
       <c r="C8" s="22" t="s">
         <v>48</v>
       </c>
@@ -9264,8 +9279,8 @@
       <c r="AN8" s="29"/>
     </row>
     <row r="9" spans="1:40" ht="18" customHeight="1">
-      <c r="A9" s="78"/>
-      <c r="B9" s="77"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="74"/>
       <c r="C9" s="22" t="s">
         <v>49</v>
       </c>
@@ -9317,8 +9332,8 @@
       <c r="AN9" s="29"/>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="77"/>
+      <c r="A10" s="75"/>
+      <c r="B10" s="74"/>
       <c r="C10" s="22" t="s">
         <v>50</v>
       </c>
@@ -9431,38 +9446,38 @@
       <c r="C12" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="103"/>
-      <c r="O12" s="73"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="73"/>
-      <c r="R12" s="74"/>
-      <c r="S12" s="73"/>
-      <c r="T12" s="74"/>
-      <c r="U12" s="73"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="73"/>
-      <c r="X12" s="74"/>
-      <c r="Y12" s="73"/>
-      <c r="Z12" s="74"/>
-      <c r="AA12" s="73"/>
-      <c r="AB12" s="74"/>
-      <c r="AC12" s="73"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="97"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="69"/>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="68"/>
+      <c r="W12" s="69"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="69"/>
+      <c r="Z12" s="68"/>
+      <c r="AA12" s="69"/>
+      <c r="AB12" s="68"/>
+      <c r="AC12" s="69"/>
       <c r="AD12" s="66"/>
-      <c r="AE12" s="74">
+      <c r="AE12" s="68">
         <f>D12+F12+H12+J12+L12+N12+P12+R12+T12+V12+X12+Z12+AB12</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="73"/>
+      <c r="AF12" s="69"/>
       <c r="AG12" s="35"/>
       <c r="AH12" s="35">
         <f>0+AE12-(0)</f>
@@ -9488,8 +9503,8 @@
       <c r="AN12" s="41"/>
     </row>
     <row r="13" spans="1:40" ht="18" customHeight="1">
-      <c r="A13" s="87"/>
-      <c r="B13" s="88"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="83"/>
       <c r="C13" s="42" t="s">
         <v>20</v>
       </c>
@@ -9622,10 +9637,10 @@
       <c r="AN13" s="47"/>
     </row>
     <row r="14" spans="1:40" ht="18" customHeight="1">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="77"/>
+      <c r="B14" s="74"/>
       <c r="C14" s="22" t="s">
         <v>46</v>
       </c>
@@ -9689,8 +9704,8 @@
       <c r="AN14" s="29"/>
     </row>
     <row r="15" spans="1:40" ht="18" customHeight="1">
-      <c r="A15" s="78"/>
-      <c r="B15" s="77"/>
+      <c r="A15" s="75"/>
+      <c r="B15" s="74"/>
       <c r="C15" s="22" t="s">
         <v>47</v>
       </c>
@@ -9742,8 +9757,8 @@
       <c r="AN15" s="29"/>
     </row>
     <row r="16" spans="1:40" ht="18" customHeight="1">
-      <c r="A16" s="78"/>
-      <c r="B16" s="77"/>
+      <c r="A16" s="75"/>
+      <c r="B16" s="74"/>
       <c r="C16" s="22" t="s">
         <v>48</v>
       </c>
@@ -9795,8 +9810,8 @@
       <c r="AN16" s="29"/>
     </row>
     <row r="17" spans="1:40" ht="18" customHeight="1">
-      <c r="A17" s="78"/>
-      <c r="B17" s="77"/>
+      <c r="A17" s="75"/>
+      <c r="B17" s="74"/>
       <c r="C17" s="22" t="s">
         <v>49</v>
       </c>
@@ -9848,8 +9863,8 @@
       <c r="AN17" s="29"/>
     </row>
     <row r="18" spans="1:40" ht="18" customHeight="1">
-      <c r="A18" s="78"/>
-      <c r="B18" s="77"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="74"/>
       <c r="C18" s="22" t="s">
         <v>50</v>
       </c>
@@ -9970,38 +9985,38 @@
       <c r="C20" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="73"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="73"/>
-      <c r="N20" s="103"/>
-      <c r="O20" s="73"/>
-      <c r="P20" s="74"/>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="74"/>
-      <c r="S20" s="73"/>
-      <c r="T20" s="74"/>
-      <c r="U20" s="73"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="73"/>
-      <c r="X20" s="74"/>
-      <c r="Y20" s="73"/>
-      <c r="Z20" s="74"/>
-      <c r="AA20" s="73"/>
-      <c r="AB20" s="74"/>
-      <c r="AC20" s="73"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="68"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="68"/>
+      <c r="W20" s="69"/>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="69"/>
+      <c r="Z20" s="68"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="68"/>
+      <c r="AC20" s="69"/>
       <c r="AD20" s="66"/>
-      <c r="AE20" s="74">
+      <c r="AE20" s="68">
         <f>D20+F20+H20+J20+L20+N20+P20+R20+T20+V20+X20+Z20+AB20</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="73"/>
+      <c r="AF20" s="69"/>
       <c r="AG20" s="35"/>
       <c r="AH20" s="35">
         <f>AH12+AE20-(D55)</f>
@@ -10027,8 +10042,8 @@
       <c r="AN20" s="41"/>
     </row>
     <row r="21" spans="1:40" ht="18" customHeight="1">
-      <c r="A21" s="87"/>
-      <c r="B21" s="88"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="83"/>
       <c r="C21" s="42" t="s">
         <v>20</v>
       </c>
@@ -10161,10 +10176,10 @@
       <c r="AN21" s="47"/>
     </row>
     <row r="22" spans="1:40" ht="18" customHeight="1">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="77"/>
+      <c r="B22" s="74"/>
       <c r="C22" s="22" t="s">
         <v>46</v>
       </c>
@@ -10228,8 +10243,8 @@
       <c r="AN22" s="29"/>
     </row>
     <row r="23" spans="1:40" ht="18" customHeight="1">
-      <c r="A23" s="78"/>
-      <c r="B23" s="77"/>
+      <c r="A23" s="75"/>
+      <c r="B23" s="74"/>
       <c r="C23" s="22" t="s">
         <v>47</v>
       </c>
@@ -10281,8 +10296,8 @@
       <c r="AN23" s="29"/>
     </row>
     <row r="24" spans="1:40" ht="18" customHeight="1">
-      <c r="A24" s="78"/>
-      <c r="B24" s="77"/>
+      <c r="A24" s="75"/>
+      <c r="B24" s="74"/>
       <c r="C24" s="22" t="s">
         <v>48</v>
       </c>
@@ -10334,8 +10349,8 @@
       <c r="AN24" s="29"/>
     </row>
     <row r="25" spans="1:40" ht="18" customHeight="1">
-      <c r="A25" s="78"/>
-      <c r="B25" s="77"/>
+      <c r="A25" s="75"/>
+      <c r="B25" s="74"/>
       <c r="C25" s="22" t="s">
         <v>49</v>
       </c>
@@ -10387,8 +10402,8 @@
       <c r="AN25" s="29"/>
     </row>
     <row r="26" spans="1:40" ht="18" customHeight="1">
-      <c r="A26" s="78"/>
-      <c r="B26" s="77"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="74"/>
       <c r="C26" s="22" t="s">
         <v>50</v>
       </c>
@@ -10509,38 +10524,38 @@
       <c r="C28" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="73"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="103"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="74"/>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="74"/>
-      <c r="S28" s="73"/>
-      <c r="T28" s="74"/>
-      <c r="U28" s="73"/>
-      <c r="V28" s="74"/>
-      <c r="W28" s="73"/>
-      <c r="X28" s="74"/>
-      <c r="Y28" s="73"/>
-      <c r="Z28" s="74"/>
-      <c r="AA28" s="73"/>
-      <c r="AB28" s="74"/>
-      <c r="AC28" s="73"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="69"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="69"/>
+      <c r="T28" s="68"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="68"/>
+      <c r="W28" s="69"/>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="69"/>
+      <c r="Z28" s="68"/>
+      <c r="AA28" s="69"/>
+      <c r="AB28" s="68"/>
+      <c r="AC28" s="69"/>
       <c r="AD28" s="66"/>
-      <c r="AE28" s="74">
+      <c r="AE28" s="68">
         <f>D28+F28+H28+J28+L28+N28+P28+R28+T28+V28+X28+Z28+AB28</f>
         <v>0</v>
       </c>
-      <c r="AF28" s="73"/>
+      <c r="AF28" s="69"/>
       <c r="AG28" s="35"/>
       <c r="AH28" s="35">
         <f>AH20+AE28-(F55)</f>
@@ -10566,8 +10581,8 @@
       <c r="AN28" s="41"/>
     </row>
     <row r="29" spans="1:40" ht="18" customHeight="1">
-      <c r="A29" s="87"/>
-      <c r="B29" s="88"/>
+      <c r="A29" s="82"/>
+      <c r="B29" s="83"/>
       <c r="C29" s="42" t="s">
         <v>20</v>
       </c>
@@ -10700,10 +10715,10 @@
       <c r="AN29" s="47"/>
     </row>
     <row r="30" spans="1:40" ht="18" customHeight="1">
-      <c r="A30" s="76" t="s">
+      <c r="A30" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="77"/>
+      <c r="B30" s="74"/>
       <c r="C30" s="22" t="s">
         <v>46</v>
       </c>
@@ -10767,8 +10782,8 @@
       <c r="AN30" s="29"/>
     </row>
     <row r="31" spans="1:40" ht="18" customHeight="1">
-      <c r="A31" s="78"/>
-      <c r="B31" s="77"/>
+      <c r="A31" s="75"/>
+      <c r="B31" s="74"/>
       <c r="C31" s="22" t="s">
         <v>47</v>
       </c>
@@ -10820,8 +10835,8 @@
       <c r="AN31" s="29"/>
     </row>
     <row r="32" spans="1:40" ht="18" customHeight="1">
-      <c r="A32" s="78"/>
-      <c r="B32" s="77"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="74"/>
       <c r="C32" s="22" t="s">
         <v>48</v>
       </c>
@@ -10873,8 +10888,8 @@
       <c r="AN32" s="29"/>
     </row>
     <row r="33" spans="1:40" ht="18" customHeight="1">
-      <c r="A33" s="78"/>
-      <c r="B33" s="77"/>
+      <c r="A33" s="75"/>
+      <c r="B33" s="74"/>
       <c r="C33" s="22" t="s">
         <v>49</v>
       </c>
@@ -10926,8 +10941,8 @@
       <c r="AN33" s="29"/>
     </row>
     <row r="34" spans="1:40" ht="18" customHeight="1">
-      <c r="A34" s="78"/>
-      <c r="B34" s="77"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="74"/>
       <c r="C34" s="22" t="s">
         <v>50</v>
       </c>
@@ -11048,38 +11063,38 @@
       <c r="C36" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="74"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="74"/>
-      <c r="I36" s="73"/>
-      <c r="J36" s="74"/>
-      <c r="K36" s="73"/>
-      <c r="L36" s="74"/>
-      <c r="M36" s="73"/>
-      <c r="N36" s="103"/>
-      <c r="O36" s="73"/>
-      <c r="P36" s="74"/>
-      <c r="Q36" s="73"/>
-      <c r="R36" s="74"/>
-      <c r="S36" s="73"/>
-      <c r="T36" s="74"/>
-      <c r="U36" s="73"/>
-      <c r="V36" s="74"/>
-      <c r="W36" s="73"/>
-      <c r="X36" s="74"/>
-      <c r="Y36" s="73"/>
-      <c r="Z36" s="74"/>
-      <c r="AA36" s="73"/>
-      <c r="AB36" s="74"/>
-      <c r="AC36" s="73"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="68"/>
+      <c r="K36" s="69"/>
+      <c r="L36" s="68"/>
+      <c r="M36" s="69"/>
+      <c r="N36" s="97"/>
+      <c r="O36" s="69"/>
+      <c r="P36" s="68"/>
+      <c r="Q36" s="69"/>
+      <c r="R36" s="68"/>
+      <c r="S36" s="69"/>
+      <c r="T36" s="68"/>
+      <c r="U36" s="69"/>
+      <c r="V36" s="68"/>
+      <c r="W36" s="69"/>
+      <c r="X36" s="68"/>
+      <c r="Y36" s="69"/>
+      <c r="Z36" s="68"/>
+      <c r="AA36" s="69"/>
+      <c r="AB36" s="68"/>
+      <c r="AC36" s="69"/>
       <c r="AD36" s="66"/>
-      <c r="AE36" s="74">
+      <c r="AE36" s="68">
         <f>D36+F36+H36+J36+L36+N36+P36+R36+T36+V36+X36+Z36+AB36</f>
         <v>0</v>
       </c>
-      <c r="AF36" s="73"/>
+      <c r="AF36" s="69"/>
       <c r="AG36" s="35"/>
       <c r="AH36" s="35">
         <f>AH28+AE36-(H55)</f>
@@ -11105,8 +11120,8 @@
       <c r="AN36" s="41"/>
     </row>
     <row r="37" spans="1:40" ht="18" customHeight="1">
-      <c r="A37" s="87"/>
-      <c r="B37" s="88"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="83"/>
       <c r="C37" s="42" t="s">
         <v>20</v>
       </c>
@@ -11239,10 +11254,10 @@
       <c r="AN37" s="47"/>
     </row>
     <row r="38" spans="1:40" ht="18" customHeight="1">
-      <c r="A38" s="76" t="s">
+      <c r="A38" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="77"/>
+      <c r="B38" s="74"/>
       <c r="C38" s="22" t="s">
         <v>46</v>
       </c>
@@ -11306,8 +11321,8 @@
       <c r="AN38" s="29"/>
     </row>
     <row r="39" spans="1:40" ht="18" customHeight="1">
-      <c r="A39" s="78"/>
-      <c r="B39" s="77"/>
+      <c r="A39" s="75"/>
+      <c r="B39" s="74"/>
       <c r="C39" s="22" t="s">
         <v>47</v>
       </c>
@@ -11359,8 +11374,8 @@
       <c r="AN39" s="29"/>
     </row>
     <row r="40" spans="1:40" ht="18" customHeight="1">
-      <c r="A40" s="78"/>
-      <c r="B40" s="77"/>
+      <c r="A40" s="75"/>
+      <c r="B40" s="74"/>
       <c r="C40" s="22" t="s">
         <v>48</v>
       </c>
@@ -11412,8 +11427,8 @@
       <c r="AN40" s="29"/>
     </row>
     <row r="41" spans="1:40" ht="18" customHeight="1">
-      <c r="A41" s="78"/>
-      <c r="B41" s="77"/>
+      <c r="A41" s="75"/>
+      <c r="B41" s="74"/>
       <c r="C41" s="22" t="s">
         <v>49</v>
       </c>
@@ -11465,8 +11480,8 @@
       <c r="AN41" s="29"/>
     </row>
     <row r="42" spans="1:40" ht="18" customHeight="1">
-      <c r="A42" s="78"/>
-      <c r="B42" s="77"/>
+      <c r="A42" s="75"/>
+      <c r="B42" s="74"/>
       <c r="C42" s="22" t="s">
         <v>50</v>
       </c>
@@ -11587,38 +11602,38 @@
       <c r="C44" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="73"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="73"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="73"/>
-      <c r="J44" s="74"/>
-      <c r="K44" s="73"/>
-      <c r="L44" s="74"/>
-      <c r="M44" s="73"/>
-      <c r="N44" s="103"/>
-      <c r="O44" s="73"/>
-      <c r="P44" s="74"/>
-      <c r="Q44" s="73"/>
-      <c r="R44" s="74"/>
-      <c r="S44" s="73"/>
-      <c r="T44" s="74"/>
-      <c r="U44" s="73"/>
-      <c r="V44" s="74"/>
-      <c r="W44" s="73"/>
-      <c r="X44" s="74"/>
-      <c r="Y44" s="73"/>
-      <c r="Z44" s="74"/>
-      <c r="AA44" s="73"/>
-      <c r="AB44" s="74"/>
-      <c r="AC44" s="73"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="68"/>
+      <c r="K44" s="69"/>
+      <c r="L44" s="68"/>
+      <c r="M44" s="69"/>
+      <c r="N44" s="97"/>
+      <c r="O44" s="69"/>
+      <c r="P44" s="68"/>
+      <c r="Q44" s="69"/>
+      <c r="R44" s="68"/>
+      <c r="S44" s="69"/>
+      <c r="T44" s="68"/>
+      <c r="U44" s="69"/>
+      <c r="V44" s="68"/>
+      <c r="W44" s="69"/>
+      <c r="X44" s="68"/>
+      <c r="Y44" s="69"/>
+      <c r="Z44" s="68"/>
+      <c r="AA44" s="69"/>
+      <c r="AB44" s="68"/>
+      <c r="AC44" s="69"/>
       <c r="AD44" s="66"/>
-      <c r="AE44" s="74">
+      <c r="AE44" s="68">
         <f>D44+F44+H44+J44+L44+N44+P44+R44+T44+V44+X44+Z44+AB44</f>
         <v>0</v>
       </c>
-      <c r="AF44" s="73"/>
+      <c r="AF44" s="69"/>
       <c r="AG44" s="35"/>
       <c r="AH44" s="35">
         <f>AH36+AE44-(J55)</f>
@@ -11644,8 +11659,8 @@
       <c r="AN44" s="41"/>
     </row>
     <row r="45" spans="1:40" ht="18" customHeight="1">
-      <c r="A45" s="87"/>
-      <c r="B45" s="88"/>
+      <c r="A45" s="82"/>
+      <c r="B45" s="83"/>
       <c r="C45" s="42" t="s">
         <v>20</v>
       </c>
@@ -12571,77 +12586,77 @@
       <c r="C52" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="74">
+      <c r="D52" s="68">
         <f>D12+D20+D28+D36+D44</f>
         <v>0</v>
       </c>
-      <c r="E52" s="73"/>
-      <c r="F52" s="74">
+      <c r="E52" s="69"/>
+      <c r="F52" s="68">
         <f>F12+F20+F28+F36+F44</f>
         <v>0</v>
       </c>
-      <c r="G52" s="73"/>
-      <c r="H52" s="74">
+      <c r="G52" s="69"/>
+      <c r="H52" s="68">
         <f>H12+H20+H28+H36+H44</f>
         <v>0</v>
       </c>
-      <c r="I52" s="73"/>
-      <c r="J52" s="74">
+      <c r="I52" s="69"/>
+      <c r="J52" s="68">
         <f>J12+J20+J28+J36+J44</f>
         <v>0</v>
       </c>
-      <c r="K52" s="73"/>
-      <c r="L52" s="74">
+      <c r="K52" s="69"/>
+      <c r="L52" s="68">
         <f>L12+L20+L28+L36+L44</f>
         <v>0</v>
       </c>
-      <c r="M52" s="73"/>
-      <c r="N52" s="104">
+      <c r="M52" s="69"/>
+      <c r="N52" s="98">
         <f>N12+N20+N28+N36+N44</f>
         <v>0</v>
       </c>
-      <c r="O52" s="73"/>
-      <c r="P52" s="74">
+      <c r="O52" s="69"/>
+      <c r="P52" s="68">
         <f>P12+P20+P28+P36+P44</f>
         <v>0</v>
       </c>
-      <c r="Q52" s="73"/>
-      <c r="R52" s="74">
+      <c r="Q52" s="69"/>
+      <c r="R52" s="68">
         <f>R12+R20+R28+R36+R44</f>
         <v>0</v>
       </c>
-      <c r="S52" s="73"/>
-      <c r="T52" s="74">
+      <c r="S52" s="69"/>
+      <c r="T52" s="68">
         <f>T12+T20+T28+T36+T44</f>
         <v>0</v>
       </c>
-      <c r="U52" s="73"/>
-      <c r="V52" s="74">
+      <c r="U52" s="69"/>
+      <c r="V52" s="68">
         <f>V12+V20+V28+V36+V44</f>
         <v>0</v>
       </c>
-      <c r="W52" s="73"/>
-      <c r="X52" s="74">
+      <c r="W52" s="69"/>
+      <c r="X52" s="68">
         <f>X12+X20+X28+X36+X44</f>
         <v>0</v>
       </c>
-      <c r="Y52" s="73"/>
-      <c r="Z52" s="74">
+      <c r="Y52" s="69"/>
+      <c r="Z52" s="68">
         <f>Z12+Z20+Z28+Z36+Z44</f>
         <v>0</v>
       </c>
-      <c r="AA52" s="73"/>
-      <c r="AB52" s="74">
+      <c r="AA52" s="69"/>
+      <c r="AB52" s="68">
         <f>AB12+AB20+AB28+AB36+AB44</f>
         <v>0</v>
       </c>
-      <c r="AC52" s="73"/>
+      <c r="AC52" s="69"/>
       <c r="AD52" s="66"/>
-      <c r="AE52" s="74">
+      <c r="AE52" s="68">
         <f>D52+F52+H52+J52+L52+N52+P52+R52+T52+V52+X52+Z52+AB52</f>
         <v>0</v>
       </c>
-      <c r="AF52" s="73"/>
+      <c r="AF52" s="69"/>
       <c r="AG52" s="35"/>
       <c r="AH52" s="35"/>
       <c r="AI52" s="37"/>
@@ -12652,8 +12667,8 @@
       <c r="AN52" s="41"/>
     </row>
     <row r="53" spans="1:40" ht="18" customHeight="1">
-      <c r="A53" s="87"/>
-      <c r="B53" s="88"/>
+      <c r="A53" s="82"/>
+      <c r="B53" s="83"/>
       <c r="C53" s="42" t="s">
         <v>20</v>
       </c>
@@ -12783,559 +12798,550 @@
       <c r="AN53" s="56"/>
     </row>
     <row r="54" spans="1:40" ht="18" customHeight="1">
-      <c r="A54" s="97" t="s">
+      <c r="A54" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="98"/>
-      <c r="C54" s="99"/>
+      <c r="B54" s="93"/>
+      <c r="C54" s="94"/>
       <c r="D54" s="72">
         <f>D46+E46*2+D47+E47*2+D48+E48*2+D49+E49*2+D50+E50*2+D51+E51*2</f>
         <v>0</v>
       </c>
-      <c r="E54" s="73"/>
+      <c r="E54" s="71"/>
       <c r="F54" s="72">
         <f>F46+G46*2+F47+G47*2+F48+G48*2+F49+G49*2+F50+G50*2+F51+G51*2</f>
         <v>0</v>
       </c>
-      <c r="G54" s="73"/>
+      <c r="G54" s="71"/>
       <c r="H54" s="72">
         <f>H46+I46*2+H47+I47*2+H48+I48*2+H49+I49*2+H50+I50*2+H51+I51*2</f>
         <v>0</v>
       </c>
-      <c r="I54" s="73"/>
+      <c r="I54" s="71"/>
       <c r="J54" s="72">
         <f>J46+K46*2+J47+K47*2+J48+K48*2+J49+K49*2+J50+K50*2+J51+K51*2</f>
         <v>0</v>
       </c>
-      <c r="K54" s="73"/>
+      <c r="K54" s="71"/>
       <c r="L54" s="72">
         <f>L46+M46*2+L47+M47*2+L48+M48*2+L49+M49*2+L50+M50*2+L51+M51*2</f>
         <v>0</v>
       </c>
-      <c r="M54" s="73"/>
+      <c r="M54" s="71"/>
       <c r="N54" s="72">
         <f>N46+O46*2+N47+O47*2+N48+O48*2+N49+O49*2+N50+O50*2+N51+O51*2</f>
         <v>0</v>
       </c>
-      <c r="O54" s="73"/>
+      <c r="O54" s="71"/>
       <c r="P54" s="72">
         <f>P46+Q46*2+P47+Q47*2+P48+Q48*2+P49+Q49*2+P50+Q50*2+P51+Q51*2</f>
         <v>0</v>
       </c>
-      <c r="Q54" s="73"/>
+      <c r="Q54" s="71"/>
       <c r="R54" s="72">
         <f>R46+S46*2+R47+S47*2+R48+S48*2+R49+S49*2+R50+S50*2+R51+S51*2</f>
         <v>0</v>
       </c>
-      <c r="S54" s="73"/>
+      <c r="S54" s="71"/>
       <c r="T54" s="72">
         <f>T46+U46*2+T47+U47*2+T48+U48*2+T49+U49*2+T50+U50*2+T51+U51*2</f>
         <v>0</v>
       </c>
-      <c r="U54" s="73"/>
+      <c r="U54" s="71"/>
       <c r="V54" s="72">
         <f>V46+W46*2+V47+W47*2+V48+W48*2+V49+W49*2+V50+W50*2+V51+W51*2</f>
         <v>0</v>
       </c>
-      <c r="W54" s="73"/>
+      <c r="W54" s="71"/>
       <c r="X54" s="72">
         <f>X46+Y46*2+X47+Y47*2+X48+Y48*2+X49+Y49*2+X50+Y50*2+X51+Y51*2</f>
         <v>0</v>
       </c>
-      <c r="Y54" s="73"/>
+      <c r="Y54" s="71"/>
       <c r="Z54" s="72">
         <f>Z46+AA46*2+Z47+AA47*2+Z48+AA48*2+Z49+AA49*2+Z50+AA50*2+Z51+AA51*2</f>
         <v>0</v>
       </c>
-      <c r="AA54" s="73"/>
+      <c r="AA54" s="71"/>
       <c r="AB54" s="72">
         <f>AB46+AC46*2+AB47+AC47*2+AB48+AC48*2+AB49+AC49*2+AB50+AC50*2+AB51+AC51*2</f>
         <v>0</v>
       </c>
-      <c r="AC54" s="73"/>
-      <c r="AD54" s="71"/>
-      <c r="AE54" s="72"/>
-      <c r="AF54" s="73"/>
-      <c r="AG54" s="57"/>
-      <c r="AH54" s="57"/>
+      <c r="AC54" s="71"/>
+      <c r="AD54" s="67"/>
+      <c r="AE54" s="58"/>
+      <c r="AF54" s="57"/>
+      <c r="AG54" s="58"/>
+      <c r="AH54" s="58"/>
       <c r="AI54" s="58"/>
-      <c r="AJ54" s="57"/>
+      <c r="AJ54" s="58"/>
       <c r="AK54" s="58"/>
-      <c r="AL54" s="57"/>
+      <c r="AL54" s="58"/>
       <c r="AM54" s="59"/>
-      <c r="AN54" s="60"/>
+      <c r="AN54" s="58"/>
     </row>
     <row r="55" spans="1:40" ht="18" customHeight="1">
-      <c r="A55" s="97" t="s">
+      <c r="A55" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="98"/>
-      <c r="C55" s="99"/>
-      <c r="D55" s="75">
+      <c r="B55" s="93"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="70">
         <f>D52</f>
         <v>0</v>
       </c>
-      <c r="E55" s="73"/>
-      <c r="F55" s="75">
+      <c r="E55" s="71"/>
+      <c r="F55" s="70">
         <f>F52</f>
         <v>0</v>
       </c>
-      <c r="G55" s="73"/>
-      <c r="H55" s="75">
+      <c r="G55" s="71"/>
+      <c r="H55" s="70">
         <f>H52</f>
         <v>0</v>
       </c>
-      <c r="I55" s="73"/>
-      <c r="J55" s="75">
+      <c r="I55" s="71"/>
+      <c r="J55" s="70">
         <f>J52</f>
         <v>0</v>
       </c>
-      <c r="K55" s="73"/>
-      <c r="L55" s="75">
+      <c r="K55" s="71"/>
+      <c r="L55" s="70">
         <f>L52</f>
         <v>0</v>
       </c>
-      <c r="M55" s="73"/>
-      <c r="N55" s="75">
+      <c r="M55" s="71"/>
+      <c r="N55" s="70">
         <f>N52</f>
         <v>0</v>
       </c>
-      <c r="O55" s="73"/>
-      <c r="P55" s="75">
+      <c r="O55" s="71"/>
+      <c r="P55" s="70">
         <f>P52</f>
         <v>0</v>
       </c>
-      <c r="Q55" s="73"/>
-      <c r="R55" s="75">
+      <c r="Q55" s="71"/>
+      <c r="R55" s="70">
         <f>R52</f>
         <v>0</v>
       </c>
-      <c r="S55" s="73"/>
-      <c r="T55" s="75">
+      <c r="S55" s="71"/>
+      <c r="T55" s="70">
         <f>T52</f>
         <v>0</v>
       </c>
-      <c r="U55" s="73"/>
-      <c r="V55" s="75">
+      <c r="U55" s="71"/>
+      <c r="V55" s="70">
         <f>V52</f>
         <v>0</v>
       </c>
-      <c r="W55" s="73"/>
-      <c r="X55" s="75">
+      <c r="W55" s="71"/>
+      <c r="X55" s="70">
         <f>X52</f>
         <v>0</v>
       </c>
-      <c r="Y55" s="73"/>
-      <c r="Z55" s="75">
+      <c r="Y55" s="71"/>
+      <c r="Z55" s="70">
         <f>Z52</f>
         <v>0</v>
       </c>
-      <c r="AA55" s="73"/>
-      <c r="AB55" s="75">
+      <c r="AA55" s="71"/>
+      <c r="AB55" s="70">
         <f>AB52</f>
         <v>0</v>
       </c>
-      <c r="AC55" s="73"/>
-      <c r="AD55" s="71"/>
-      <c r="AE55" s="75"/>
-      <c r="AF55" s="73"/>
-      <c r="AG55" s="61"/>
-      <c r="AH55" s="61"/>
-      <c r="AI55" s="62"/>
-      <c r="AJ55" s="57"/>
+      <c r="AC55" s="71"/>
+      <c r="AD55" s="67"/>
+      <c r="AE55" s="59"/>
+      <c r="AF55" s="57"/>
+      <c r="AG55" s="59"/>
+      <c r="AH55" s="59"/>
+      <c r="AI55" s="59"/>
+      <c r="AJ55" s="58"/>
       <c r="AK55" s="58"/>
-      <c r="AL55" s="61"/>
+      <c r="AL55" s="59"/>
       <c r="AM55" s="59"/>
-      <c r="AN55" s="63"/>
+      <c r="AN55" s="59"/>
     </row>
     <row r="56" spans="1:40" ht="18" customHeight="1">
-      <c r="A56" s="64"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="50"/>
-      <c r="I56" s="51"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="51"/>
-      <c r="L56" s="50"/>
-      <c r="M56" s="51"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="51"/>
-      <c r="P56" s="50"/>
-      <c r="Q56" s="51"/>
-      <c r="R56" s="50"/>
-      <c r="S56" s="51"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="51"/>
-      <c r="V56" s="50"/>
-      <c r="W56" s="51"/>
-      <c r="X56" s="50"/>
-      <c r="Y56" s="51"/>
-      <c r="Z56" s="50"/>
-      <c r="AA56" s="51"/>
-      <c r="AB56" s="50"/>
-      <c r="AC56" s="51"/>
-      <c r="AD56" s="66"/>
-      <c r="AE56" s="50"/>
-      <c r="AF56" s="51"/>
-      <c r="AG56" s="50"/>
-      <c r="AH56" s="50"/>
-      <c r="AI56" s="51"/>
-      <c r="AJ56" s="50"/>
-      <c r="AK56" s="51"/>
-      <c r="AL56" s="50"/>
-      <c r="AM56" s="40"/>
-      <c r="AN56" s="67"/>
+      <c r="A56" s="60"/>
+      <c r="B56" s="60"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="62"/>
+      <c r="I56" s="62"/>
+      <c r="J56" s="62"/>
+      <c r="K56" s="62"/>
+      <c r="L56" s="62"/>
+      <c r="M56" s="62"/>
+      <c r="N56" s="62"/>
+      <c r="O56" s="62"/>
+      <c r="P56" s="62"/>
+      <c r="Q56" s="62"/>
+      <c r="R56" s="62"/>
+      <c r="S56" s="62"/>
+      <c r="T56" s="62"/>
+      <c r="U56" s="62"/>
+      <c r="V56" s="62"/>
+      <c r="W56" s="62"/>
+      <c r="X56" s="62"/>
+      <c r="Y56" s="62"/>
+      <c r="Z56" s="62"/>
+      <c r="AA56" s="62"/>
+      <c r="AB56" s="62"/>
+      <c r="AC56" s="62"/>
+      <c r="AD56" s="60"/>
+      <c r="AE56" s="62"/>
+      <c r="AF56" s="62"/>
+      <c r="AG56" s="62"/>
+      <c r="AH56" s="62"/>
+      <c r="AI56" s="62"/>
+      <c r="AJ56" s="62"/>
+      <c r="AK56" s="62"/>
+      <c r="AL56" s="62"/>
+      <c r="AM56" s="63"/>
+      <c r="AN56" s="62"/>
     </row>
     <row r="57" spans="1:40" ht="18" customHeight="1">
-      <c r="A57" s="64"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="65"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="51"/>
-      <c r="J57" s="50"/>
-      <c r="K57" s="51"/>
-      <c r="L57" s="50"/>
-      <c r="M57" s="51"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="51"/>
-      <c r="P57" s="50"/>
-      <c r="Q57" s="51"/>
-      <c r="R57" s="50"/>
-      <c r="S57" s="51"/>
-      <c r="T57" s="50"/>
-      <c r="U57" s="51"/>
-      <c r="V57" s="50"/>
-      <c r="W57" s="51"/>
-      <c r="X57" s="50"/>
-      <c r="Y57" s="51"/>
-      <c r="Z57" s="50"/>
-      <c r="AA57" s="51"/>
-      <c r="AB57" s="50"/>
-      <c r="AC57" s="51"/>
-      <c r="AD57" s="66"/>
-      <c r="AE57" s="50"/>
-      <c r="AF57" s="51"/>
-      <c r="AG57" s="50"/>
-      <c r="AH57" s="50"/>
-      <c r="AI57" s="51"/>
-      <c r="AJ57" s="50"/>
-      <c r="AK57" s="51"/>
-      <c r="AL57" s="50"/>
-      <c r="AM57" s="40"/>
-      <c r="AN57" s="67"/>
+      <c r="A57" s="60"/>
+      <c r="B57" s="60"/>
+      <c r="C57" s="61"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="62"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="62"/>
+      <c r="H57" s="62"/>
+      <c r="I57" s="62"/>
+      <c r="J57" s="62"/>
+      <c r="K57" s="62"/>
+      <c r="L57" s="62"/>
+      <c r="M57" s="62"/>
+      <c r="N57" s="62"/>
+      <c r="O57" s="62"/>
+      <c r="P57" s="62"/>
+      <c r="Q57" s="62"/>
+      <c r="R57" s="62"/>
+      <c r="S57" s="62"/>
+      <c r="T57" s="62"/>
+      <c r="U57" s="62"/>
+      <c r="V57" s="62"/>
+      <c r="W57" s="62"/>
+      <c r="X57" s="62"/>
+      <c r="Y57" s="62"/>
+      <c r="Z57" s="62"/>
+      <c r="AA57" s="62"/>
+      <c r="AB57" s="62"/>
+      <c r="AC57" s="62"/>
+      <c r="AD57" s="60"/>
+      <c r="AE57" s="62"/>
+      <c r="AF57" s="62"/>
+      <c r="AG57" s="62"/>
+      <c r="AH57" s="62"/>
+      <c r="AI57" s="62"/>
+      <c r="AJ57" s="62"/>
+      <c r="AK57" s="62"/>
+      <c r="AL57" s="62"/>
+      <c r="AM57" s="63"/>
+      <c r="AN57" s="62"/>
     </row>
     <row r="58" spans="1:40" ht="18" customHeight="1">
-      <c r="A58" s="97" t="s">
+      <c r="A58" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="98"/>
-      <c r="C58" s="99"/>
+      <c r="B58" s="93"/>
+      <c r="C58" s="94"/>
       <c r="D58" s="72">
         <f>D53+E53+AE21+AF21</f>
         <v>0</v>
       </c>
-      <c r="E58" s="73"/>
+      <c r="E58" s="71"/>
       <c r="F58" s="72">
         <f>F53+G53+AE29+AF29</f>
         <v>0</v>
       </c>
-      <c r="G58" s="73"/>
+      <c r="G58" s="71"/>
       <c r="H58" s="72">
         <f>H53+I53+AE37+AF37</f>
         <v>0</v>
       </c>
-      <c r="I58" s="73"/>
+      <c r="I58" s="71"/>
       <c r="J58" s="72">
         <f>J53+K53+AE45+AF45</f>
         <v>0</v>
       </c>
-      <c r="K58" s="73"/>
+      <c r="K58" s="71"/>
       <c r="L58" s="72">
         <f>L53+M53+0</f>
         <v>0</v>
       </c>
-      <c r="M58" s="73"/>
+      <c r="M58" s="71"/>
       <c r="N58" s="72">
         <f>N53+O53+0</f>
         <v>0</v>
       </c>
-      <c r="O58" s="73"/>
+      <c r="O58" s="71"/>
       <c r="P58" s="72">
         <f>P53+Q53+0</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="73"/>
+      <c r="Q58" s="71"/>
       <c r="R58" s="72">
         <f>R53+S53+0</f>
         <v>0</v>
       </c>
-      <c r="S58" s="73"/>
+      <c r="S58" s="71"/>
       <c r="T58" s="72">
         <f>T53+U53+0</f>
         <v>0</v>
       </c>
-      <c r="U58" s="73"/>
+      <c r="U58" s="71"/>
       <c r="V58" s="72">
         <f>V53+W53+0</f>
         <v>0</v>
       </c>
-      <c r="W58" s="73"/>
+      <c r="W58" s="71"/>
       <c r="X58" s="72">
         <f>X53+Y53+0</f>
         <v>0</v>
       </c>
-      <c r="Y58" s="73"/>
+      <c r="Y58" s="71"/>
       <c r="Z58" s="72">
         <f>Z53+AA53+0</f>
         <v>0</v>
       </c>
-      <c r="AA58" s="73"/>
+      <c r="AA58" s="71"/>
       <c r="AB58" s="72">
         <f>AB53+AC53+0</f>
         <v>0</v>
       </c>
-      <c r="AC58" s="73"/>
-      <c r="AD58" s="71"/>
-      <c r="AE58" s="72"/>
-      <c r="AF58" s="73"/>
-      <c r="AG58" s="57"/>
-      <c r="AH58" s="57"/>
+      <c r="AC58" s="71"/>
+      <c r="AD58" s="67"/>
+      <c r="AE58" s="58"/>
+      <c r="AF58" s="57"/>
+      <c r="AG58" s="58"/>
+      <c r="AH58" s="58"/>
       <c r="AI58" s="58"/>
-      <c r="AJ58" s="57"/>
+      <c r="AJ58" s="58"/>
       <c r="AK58" s="58"/>
-      <c r="AL58" s="57"/>
+      <c r="AL58" s="58"/>
       <c r="AM58" s="59"/>
-      <c r="AN58" s="60"/>
+      <c r="AN58" s="58"/>
     </row>
     <row r="59" spans="1:40" ht="18" customHeight="1">
-      <c r="A59" s="97" t="s">
+      <c r="A59" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="98"/>
-      <c r="C59" s="99"/>
+      <c r="B59" s="93"/>
+      <c r="C59" s="94"/>
       <c r="D59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,D3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,D3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="E59" s="73"/>
+      <c r="E59" s="71"/>
       <c r="F59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,F3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,F3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="G59" s="73"/>
+      <c r="G59" s="71"/>
       <c r="H59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,H3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,H3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="I59" s="73"/>
+      <c r="I59" s="71"/>
       <c r="J59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,J3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,J3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="K59" s="73"/>
+      <c r="K59" s="71"/>
       <c r="L59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,L3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,L3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="M59" s="73"/>
+      <c r="M59" s="71"/>
       <c r="N59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,N3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,N3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="O59" s="73"/>
+      <c r="O59" s="71"/>
       <c r="P59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,P3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,P3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="73"/>
+      <c r="Q59" s="71"/>
       <c r="R59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,R3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,R3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="S59" s="73"/>
+      <c r="S59" s="71"/>
       <c r="T59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,T3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,T3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="U59" s="73"/>
+      <c r="U59" s="71"/>
       <c r="V59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,V3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,V3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="W59" s="73"/>
+      <c r="W59" s="71"/>
       <c r="X59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,X3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,X3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="Y59" s="73"/>
+      <c r="Y59" s="71"/>
       <c r="Z59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,Z3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,Z3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="AA59" s="73"/>
+      <c r="AA59" s="71"/>
       <c r="AB59" s="72">
         <f>SUMIF(WB!$D$3:$Y$3,AB3,WB!$D$106:$Y$106)+SUMIF(EB!$D$3:$AC$3,AB3,EB!$D$58:$AC$58)</f>
         <v>0</v>
       </c>
-      <c r="AC59" s="73"/>
-      <c r="AD59" s="71"/>
-      <c r="AE59" s="72"/>
-      <c r="AF59" s="73"/>
-      <c r="AG59" s="57"/>
-      <c r="AH59" s="57"/>
+      <c r="AC59" s="71"/>
+      <c r="AD59" s="67"/>
+      <c r="AE59" s="58"/>
+      <c r="AF59" s="57"/>
+      <c r="AG59" s="58"/>
+      <c r="AH59" s="58"/>
       <c r="AI59" s="58"/>
-      <c r="AJ59" s="57"/>
+      <c r="AJ59" s="58"/>
       <c r="AK59" s="58"/>
-      <c r="AL59" s="57"/>
+      <c r="AL59" s="58"/>
       <c r="AM59" s="59"/>
-      <c r="AN59" s="60"/>
+      <c r="AN59" s="58"/>
     </row>
     <row r="60" spans="1:40" ht="18" customHeight="1">
-      <c r="A60" s="97" t="s">
+      <c r="A60" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="98"/>
-      <c r="C60" s="99"/>
+      <c r="B60" s="93"/>
+      <c r="C60" s="94"/>
       <c r="D60" s="72"/>
-      <c r="E60" s="73"/>
+      <c r="E60" s="71"/>
       <c r="F60" s="72"/>
-      <c r="G60" s="73"/>
+      <c r="G60" s="71"/>
       <c r="H60" s="72"/>
-      <c r="I60" s="73"/>
+      <c r="I60" s="71"/>
       <c r="J60" s="72"/>
-      <c r="K60" s="73"/>
+      <c r="K60" s="71"/>
       <c r="L60" s="72"/>
-      <c r="M60" s="73"/>
+      <c r="M60" s="71"/>
       <c r="N60" s="72"/>
-      <c r="O60" s="73"/>
+      <c r="O60" s="71"/>
       <c r="P60" s="72"/>
-      <c r="Q60" s="73"/>
+      <c r="Q60" s="71"/>
       <c r="R60" s="72"/>
-      <c r="S60" s="73"/>
+      <c r="S60" s="71"/>
       <c r="T60" s="72"/>
-      <c r="U60" s="73"/>
+      <c r="U60" s="71"/>
       <c r="V60" s="72"/>
-      <c r="W60" s="73"/>
+      <c r="W60" s="71"/>
       <c r="X60" s="72"/>
-      <c r="Y60" s="73"/>
+      <c r="Y60" s="71"/>
       <c r="Z60" s="72"/>
-      <c r="AA60" s="73"/>
+      <c r="AA60" s="71"/>
       <c r="AB60" s="72"/>
-      <c r="AC60" s="73"/>
-      <c r="AD60" s="71"/>
-      <c r="AE60" s="72"/>
-      <c r="AF60" s="73"/>
-      <c r="AG60" s="57"/>
-      <c r="AH60" s="57"/>
+      <c r="AC60" s="71"/>
+      <c r="AD60" s="67"/>
+      <c r="AE60" s="58"/>
+      <c r="AF60" s="57"/>
+      <c r="AG60" s="58"/>
+      <c r="AH60" s="58"/>
       <c r="AI60" s="58"/>
-      <c r="AJ60" s="57"/>
+      <c r="AJ60" s="58"/>
       <c r="AK60" s="58"/>
-      <c r="AL60" s="57"/>
+      <c r="AL60" s="58"/>
       <c r="AM60" s="59"/>
-      <c r="AN60" s="60"/>
+      <c r="AN60" s="58"/>
     </row>
     <row r="61" spans="1:40" ht="18" customHeight="1">
-      <c r="A61" s="87" t="s">
+      <c r="A61" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="88"/>
-      <c r="C61" s="102"/>
-      <c r="D61" s="85">
+      <c r="B61" s="93"/>
+      <c r="C61" s="94"/>
+      <c r="D61" s="72">
         <f>D60-D59</f>
         <v>0</v>
       </c>
-      <c r="E61" s="86"/>
-      <c r="F61" s="85">
+      <c r="E61" s="71"/>
+      <c r="F61" s="72">
         <f>F60-F59</f>
         <v>0</v>
       </c>
-      <c r="G61" s="86"/>
-      <c r="H61" s="85">
+      <c r="G61" s="71"/>
+      <c r="H61" s="72">
         <f>H60-H59</f>
         <v>0</v>
       </c>
-      <c r="I61" s="86"/>
-      <c r="J61" s="85">
+      <c r="I61" s="71"/>
+      <c r="J61" s="72">
         <f>J60-J59</f>
         <v>0</v>
       </c>
-      <c r="K61" s="86"/>
-      <c r="L61" s="85">
+      <c r="K61" s="71"/>
+      <c r="L61" s="72">
         <f>L60-L59</f>
         <v>0</v>
       </c>
-      <c r="M61" s="86"/>
-      <c r="N61" s="85">
+      <c r="M61" s="71"/>
+      <c r="N61" s="72">
         <f>N60-N59</f>
         <v>0</v>
       </c>
-      <c r="O61" s="86"/>
-      <c r="P61" s="85">
+      <c r="O61" s="71"/>
+      <c r="P61" s="72">
         <f>P60-P59</f>
         <v>0</v>
       </c>
-      <c r="Q61" s="86"/>
-      <c r="R61" s="85">
+      <c r="Q61" s="71"/>
+      <c r="R61" s="72">
         <f>R60-R59</f>
         <v>0</v>
       </c>
-      <c r="S61" s="86"/>
-      <c r="T61" s="85">
+      <c r="S61" s="71"/>
+      <c r="T61" s="72">
         <f>T60-T59</f>
         <v>0</v>
       </c>
-      <c r="U61" s="86"/>
-      <c r="V61" s="85">
+      <c r="U61" s="71"/>
+      <c r="V61" s="72">
         <f>V60-V59</f>
         <v>0</v>
       </c>
-      <c r="W61" s="86"/>
-      <c r="X61" s="85">
+      <c r="W61" s="71"/>
+      <c r="X61" s="72">
         <f>X60-X59</f>
         <v>0</v>
       </c>
-      <c r="Y61" s="86"/>
-      <c r="Z61" s="85">
+      <c r="Y61" s="71"/>
+      <c r="Z61" s="72">
         <f>Z60-Z59</f>
         <v>0</v>
       </c>
-      <c r="AA61" s="86"/>
-      <c r="AB61" s="85">
+      <c r="AA61" s="71"/>
+      <c r="AB61" s="72">
         <f>AB60-AB59</f>
         <v>0</v>
       </c>
-      <c r="AC61" s="86"/>
-      <c r="AD61" s="54"/>
-      <c r="AE61" s="85"/>
-      <c r="AF61" s="86"/>
-      <c r="AG61" s="52"/>
-      <c r="AH61" s="52"/>
-      <c r="AI61" s="53"/>
-      <c r="AJ61" s="52"/>
-      <c r="AK61" s="53"/>
-      <c r="AL61" s="52"/>
-      <c r="AM61" s="55"/>
-      <c r="AN61" s="56"/>
+      <c r="AC61" s="71"/>
+      <c r="AD61" s="67"/>
+      <c r="AE61" s="58"/>
+      <c r="AF61" s="57"/>
+      <c r="AG61" s="58"/>
+      <c r="AH61" s="58"/>
+      <c r="AI61" s="58"/>
+      <c r="AJ61" s="58"/>
+      <c r="AK61" s="58"/>
+      <c r="AL61" s="58"/>
+      <c r="AM61" s="59"/>
+      <c r="AN61" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="228">
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="AE55:AF55"/>
-    <mergeCell ref="AB3:AC3"/>
+  <mergeCells count="222">
     <mergeCell ref="AE2:AF2"/>
     <mergeCell ref="V59:W59"/>
     <mergeCell ref="H61:I61"/>
@@ -13350,41 +13356,33 @@
     <mergeCell ref="V54:W54"/>
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="N44:O44"/>
-    <mergeCell ref="X61:Y61"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="AB20:AC20"/>
+    <mergeCell ref="T20:U20"/>
     <mergeCell ref="P44:Q44"/>
     <mergeCell ref="H44:I44"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="Z61:AA61"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="R4:S4"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="AE58:AF58"/>
-    <mergeCell ref="F55:G55"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="T59:U59"/>
-    <mergeCell ref="F58:G58"/>
     <mergeCell ref="F52:G52"/>
-    <mergeCell ref="AE61:AF61"/>
-    <mergeCell ref="Z58:AA58"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="Z44:AA44"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="AB28:AC28"/>
     <mergeCell ref="T28:U28"/>
@@ -13392,7 +13390,30 @@
     <mergeCell ref="R52:S52"/>
     <mergeCell ref="R61:S61"/>
     <mergeCell ref="V55:W55"/>
-    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="X61:Y61"/>
+    <mergeCell ref="Z61:AA61"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="V61:W61"/>
+    <mergeCell ref="AE20:AF20"/>
+    <mergeCell ref="AB55:AC55"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="Z54:AA54"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="AB54:AC54"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="D52:E52"/>
     <mergeCell ref="AE3:AF3"/>
     <mergeCell ref="T54:U54"/>
     <mergeCell ref="A22:B26"/>
@@ -13401,21 +13422,35 @@
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="A6:B10"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="Z36:AA36"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="Z58:AA58"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="Z60:AA60"/>
+    <mergeCell ref="X60:Y60"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="A14:B18"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="A38:B42"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="P55:Q55"/>
     <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="AJ3:AK3"/>
     <mergeCell ref="AE1:AN1"/>
@@ -13430,16 +13465,24 @@
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
     <mergeCell ref="L44:M44"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="A14:B18"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="Z55:AA55"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="Z44:AA44"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="AB61:AC61"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="AJ4:AK4"/>
     <mergeCell ref="AL4:AM4"/>
     <mergeCell ref="X54:Y54"/>
     <mergeCell ref="P58:Q58"/>
@@ -13449,45 +13492,13 @@
     <mergeCell ref="R60:S60"/>
     <mergeCell ref="F54:G54"/>
     <mergeCell ref="H54:I54"/>
-    <mergeCell ref="AE59:AF59"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="R59:S59"/>
     <mergeCell ref="P60:Q60"/>
     <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="P52:Q52"/>
     <mergeCell ref="N36:O36"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="AB36:AC36"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="AB61:AC61"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="AE60:AF60"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="AB12:AC12"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="Z60:AA60"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="J61:K61"/>
     <mergeCell ref="D61:E61"/>
     <mergeCell ref="T44:U44"/>
     <mergeCell ref="V44:W44"/>
@@ -13500,49 +13511,48 @@
     <mergeCell ref="R55:S55"/>
     <mergeCell ref="T12:U12"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="N52:O52"/>
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="Z55:AA55"/>
-    <mergeCell ref="V61:W61"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="Z54:AA54"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="Z12:AA12"/>
     <mergeCell ref="A30:B34"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="AB60:AC60"/>
     <mergeCell ref="V20:W20"/>
+    <mergeCell ref="N12:O12"/>
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="N12:O12"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="V28:W28"/>
     <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="P59:Q59"/>
     <mergeCell ref="AB44:AC44"/>
     <mergeCell ref="AB59:AC59"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A38:B42"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="AB54:AC54"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="AB20:AC20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="AB36:AC36"/>
+    <mergeCell ref="AB12:AC12"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="P12:Q12"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D60:E60"/>
     <mergeCell ref="R44:S44"/>
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="P20:Q20"/>
     <mergeCell ref="AB58:AC58"/>
-    <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="V58:W58"/>
     <mergeCell ref="R28:S28"/>
     <mergeCell ref="J59:K59"/>
@@ -13553,20 +13563,19 @@
     <mergeCell ref="X52:Y52"/>
     <mergeCell ref="H55:I55"/>
     <mergeCell ref="J60:K60"/>
-    <mergeCell ref="AE20:AF20"/>
-    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="Z28:AA28"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="AJ6:AK53">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL6:AM53">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
